--- a/output/Data and Chart Outputs/pakistan_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/pakistan_power_generation_daily.xlsx
@@ -159,7 +159,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Pakistan power generation by fuel, incl. K-Electric (CPPA-G / NEPRA FCA filings; KE partly estimated) (to Aug/26)</a:t>
+              <a:t>Pakistan power generation by fuel, national grid + K-Electric where filed (CPPA-G / NEPRA FCA filings; KE from NEPRA KE decisions) (to Aug/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -766,7 +766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -803,14 +803,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>K-Electric: KE_own_Gas_MWh (indigenous gas), KE_own_RLNG_MWh, KE_own_Oil_MWh (furnace oil at BQPS-I + HSD at KCCPP), KE_own_unsplit_MWh (months known only from NEPRA's KE decision, which gives own sent-out without a fuel split; counted under Gas, as KE's plants run mainly on gas/RLNG), KE_own_MWh = their sum (sent-out, net of auxiliaries); KE_IPP_&lt;fuel&gt;_MWh = purchases from IPPs on KE's network (Oil: Gul Ahmed / Tapal; Gas: SNPC I/II, Lucky, ISL; Coal: FPCL; Solar: Oursun, Gharo solar and net metering), KE_purchases_nonCPPA_MWh their sum; KE_from_CPPA_MWh = drawn from the national grid (detail / check only); KE_external_MWh = NEPRA's 'external purchases' (CPPA-G + IPPs) where that is the source.</t>
+          <t>K-Electric: KE_own_Gas_MWh (indigenous gas), KE_own_RLNG_MWh, KE_own_Oil_MWh (furnace oil at BQPS-I + HSD at KCCPP), KE_own_unsplit_MWh (KE's own sent-out where the source gives no fuel split - counted under Gas, as KE's plants run mainly on gas/RLNG; this overstates gas and understates oil in those months), KE_own_MWh = their sum (sent-out, net of auxiliaries); KE_IPP_&lt;fuel&gt;_MWh = purchases from plants on KE's network outside the CPPA-G pool (Oil: Gul Ahmed / Tapal; Gas: SNPC I/II, Lucky, ISL, Lotte; Coal: FFBL/FPCL; Nuclear: KANUPP until Aug 2021; Solar: Oursun, Gharo and net metering), KE_purchases_other_MWh = such purchases without a fuel split (counted under Other), KE_purchases_nonCPPA_MWh = their sum; KE_from_CPPA_MWh = drawn from the national grid (detail / check only, never added); KE_external_MWh = all of KE's purchases.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KE_basis says how each month's KE figures were obtained. KE's own sent-out comes from NEPRA's KE FCA decision; its fuel split from KE's own filing for that month when the filing's plant blocks add up to the decision's total within 5% (otherwise KE_own_unsplit, counted under Gas); KE's purchases from IPPs on its network from KE's filing when consistent with NEPRA's 'external purchases', otherwise copied from the same calendar month of the nearest year with a good filing (ESTIMATE). Months with no KE decision (KE's consumers moved to the uniform national FCA in 2025, so none after March 2025, plus the odd gap) are ESTIMATED: KE's own sent-out is copied from the same calendar month of the nearest year that has one. KE_from_CPPA_MWh = NEPRA's external purchases minus the IPP purchases (blank in estimated months).</t>
+          <t>KE_basis: where each month's KE figures come from - REAL FIGURES ONLY, nothing copied or estimated. First NEPRA's State of Industry Report (KE's fuel-wise own-generation and power-purchase tables, by month, one report per fiscal year); else NEPRA's monthly KE FCA decision (own sent-out; its 'Company Wide Mix' table where given) with the fuel split from KE's own filing when its plant blocks add up within 5%; IPP purchases only where filed (else blank). KE_included = True where KE's own sent-out is known. Months with no KE figure (KE_basis 'no KE figure', KE_included False): KE columns blank and Total_MWh / the fuel columns are the national grid only - the master fills such months for the whole country from Ember.</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Monthly from Feb 2021 to Aug 2026 (63 months; national-grid sources: {'NEPRA FCA decision': 37, 'CPPA-G workbook': 24, 'CPPA-G PDF': 2}; KE basis: {'own': 63}). Calendar-year totals, TWh (Pakistan incl. KE, national grid alone): {2023: (np.float64(138.1), np.float64(129.4)), 2025: (np.float64(136.6), np.float64(127.5))}.</t>
+          <t>Monthly from Feb 2021 to Aug 2026 (63 months; national-grid sources: {'NEPRA FCA decision': 37, 'CPPA-G workbook': 24, 'CPPA-G PDF': 2}; KE basis: {'no': 39, 'own': 24}). Calendar-year totals, TWh (Pakistan incl. KE, national grid alone): {2023: (np.float64(131.8), np.float64(129.4)), 2025: (np.float64(127.5), np.float64(127.5))}.</t>
         </is>
       </c>
     </row>
@@ -867,6 +867,13 @@
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
+        <is>
+          <t>NEPRA State of Industry Reports (statistical tables: K-Electric fuel-wise own generation and fuel-wise power purchases, monthly): https://nepra.org.pk/publications/State%20of%20Industry%20Reports.php</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>K-Electric's monthly 'Provisional request for monthly fuel cost variation' filings (Annexure B sent-out by fuel; power purchase details), NEPRA Admission Notices: https://nepra.org.pk/news.php ; NEPRA's monthly FCA decisions for K-Electric (own sent-out and external purchases): https://nepra.org.pk/tariff/Distribution%20K-Electric.php</t>
         </is>
@@ -939,22 +946,22 @@
         <v>2033.93</v>
       </c>
       <c r="C2" t="n">
-        <v>2486.1</v>
+        <v>2177.41</v>
       </c>
       <c r="D2" t="n">
         <v>98.11</v>
       </c>
       <c r="E2" t="n">
-        <v>99.31999999999999</v>
+        <v>57.06</v>
       </c>
       <c r="F2" t="n">
-        <v>1933.66</v>
+        <v>1902.98</v>
       </c>
       <c r="G2" t="n">
         <v>791.91</v>
       </c>
       <c r="H2" t="n">
-        <v>191.07</v>
+        <v>189.95</v>
       </c>
     </row>
     <row r="3">
@@ -965,22 +972,22 @@
         <v>1740.58</v>
       </c>
       <c r="C3" t="n">
-        <v>3577.68</v>
+        <v>2928.99</v>
       </c>
       <c r="D3" t="n">
         <v>169.52</v>
       </c>
       <c r="E3" t="n">
-        <v>108.63</v>
+        <v>66.37</v>
       </c>
       <c r="F3" t="n">
-        <v>2765.07</v>
+        <v>2734.39</v>
       </c>
       <c r="G3" t="n">
         <v>940.16</v>
       </c>
       <c r="H3" t="n">
-        <v>347.2</v>
+        <v>346.08</v>
       </c>
     </row>
     <row r="4">
@@ -991,22 +998,22 @@
         <v>2572.58</v>
       </c>
       <c r="C4" t="n">
-        <v>4798.16</v>
+        <v>3849.47</v>
       </c>
       <c r="D4" t="n">
         <v>197.3</v>
       </c>
       <c r="E4" t="n">
-        <v>110.29</v>
+        <v>68.03</v>
       </c>
       <c r="F4" t="n">
-        <v>2470.56</v>
+        <v>2439.88</v>
       </c>
       <c r="G4" t="n">
         <v>1067.09</v>
       </c>
       <c r="H4" t="n">
-        <v>242.89</v>
+        <v>241.77</v>
       </c>
     </row>
     <row r="5">
@@ -1017,22 +1024,22 @@
         <v>3465.46</v>
       </c>
       <c r="C5" t="n">
-        <v>5223.63</v>
+        <v>4282.94</v>
       </c>
       <c r="D5" t="n">
         <v>403.21</v>
       </c>
       <c r="E5" t="n">
-        <v>108.8</v>
+        <v>66.54000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>2649.65</v>
+        <v>2618.97</v>
       </c>
       <c r="G5" t="n">
         <v>1271.35</v>
       </c>
       <c r="H5" t="n">
-        <v>854.77</v>
+        <v>853.65</v>
       </c>
     </row>
     <row r="6">
@@ -1043,22 +1050,22 @@
         <v>4222.15</v>
       </c>
       <c r="C6" t="n">
-        <v>5022.87</v>
+        <v>4965.18</v>
       </c>
       <c r="D6" t="n">
         <v>510.76</v>
       </c>
       <c r="E6" t="n">
-        <v>105.35</v>
+        <v>63.09</v>
       </c>
       <c r="F6" t="n">
-        <v>2620.47</v>
+        <v>2589.79</v>
       </c>
       <c r="G6" t="n">
         <v>1618.06</v>
       </c>
       <c r="H6" t="n">
-        <v>1303.36</v>
+        <v>1302.24</v>
       </c>
     </row>
     <row r="7">
@@ -1069,22 +1076,22 @@
         <v>4695.76</v>
       </c>
       <c r="C7" t="n">
-        <v>5410.5</v>
+        <v>5353.89</v>
       </c>
       <c r="D7" t="n">
         <v>550.37</v>
       </c>
       <c r="E7" t="n">
-        <v>79.02</v>
+        <v>61.82</v>
       </c>
       <c r="F7" t="n">
-        <v>2421.9</v>
+        <v>2383.33</v>
       </c>
       <c r="G7" t="n">
         <v>1659.86</v>
       </c>
       <c r="H7" t="n">
-        <v>1829.85</v>
+        <v>1790.65</v>
       </c>
     </row>
     <row r="8">
@@ -1095,22 +1102,22 @@
         <v>5594.3</v>
       </c>
       <c r="C8" t="n">
-        <v>4936.82</v>
+        <v>4209.13</v>
       </c>
       <c r="D8" t="n">
         <v>549.95</v>
       </c>
       <c r="E8" t="n">
-        <v>109.27</v>
+        <v>67.01000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>2324.54</v>
+        <v>2293.86</v>
       </c>
       <c r="G8" t="n">
         <v>1630.19</v>
       </c>
       <c r="H8" t="n">
-        <v>1689.56</v>
+        <v>1688.44</v>
       </c>
     </row>
     <row r="9">
@@ -1121,22 +1128,22 @@
         <v>5085.48</v>
       </c>
       <c r="C9" t="n">
-        <v>4853.56</v>
+        <v>4803.23</v>
       </c>
       <c r="D9" t="n">
         <v>230.4</v>
       </c>
       <c r="E9" t="n">
-        <v>82.01000000000001</v>
+        <v>60.75</v>
       </c>
       <c r="F9" t="n">
-        <v>2427.54</v>
+        <v>2392.52</v>
       </c>
       <c r="G9" t="n">
         <v>1281.8</v>
       </c>
       <c r="H9" t="n">
-        <v>1043.19</v>
+        <v>1032.44</v>
       </c>
     </row>
     <row r="10">
@@ -1147,22 +1154,22 @@
         <v>2627.25</v>
       </c>
       <c r="C10" t="n">
-        <v>4611.82</v>
+        <v>4554.13</v>
       </c>
       <c r="D10" t="n">
         <v>184.82</v>
       </c>
       <c r="E10" t="n">
-        <v>105.43</v>
+        <v>63.17</v>
       </c>
       <c r="F10" t="n">
-        <v>1916.46</v>
+        <v>1885.78</v>
       </c>
       <c r="G10" t="n">
         <v>1392.92</v>
       </c>
       <c r="H10" t="n">
-        <v>1305.89</v>
+        <v>1304.77</v>
       </c>
     </row>
     <row r="11">
@@ -1173,22 +1180,22 @@
         <v>2816.49</v>
       </c>
       <c r="C11" t="n">
-        <v>2824.55</v>
+        <v>2766.86</v>
       </c>
       <c r="D11" t="n">
         <v>175.19</v>
       </c>
       <c r="E11" t="n">
-        <v>92.88</v>
+        <v>50.62</v>
       </c>
       <c r="F11" t="n">
-        <v>1409.8</v>
+        <v>1379.12</v>
       </c>
       <c r="G11" t="n">
         <v>1485.19</v>
       </c>
       <c r="H11" t="n">
-        <v>237.68</v>
+        <v>236.56</v>
       </c>
     </row>
     <row r="12">
@@ -1199,22 +1206,22 @@
         <v>1768.84</v>
       </c>
       <c r="C12" t="n">
-        <v>2766.05</v>
+        <v>2708.36</v>
       </c>
       <c r="D12" t="n">
         <v>210.08</v>
       </c>
       <c r="E12" t="n">
-        <v>87.44</v>
+        <v>45.18</v>
       </c>
       <c r="F12" t="n">
-        <v>2134.33</v>
+        <v>2103.65</v>
       </c>
       <c r="G12" t="n">
         <v>1549.06</v>
       </c>
       <c r="H12" t="n">
-        <v>711.2900000000001</v>
+        <v>710.1700000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1225,22 +1232,22 @@
         <v>512.9299999999999</v>
       </c>
       <c r="C13" t="n">
-        <v>2189.13</v>
+        <v>2131.44</v>
       </c>
       <c r="D13" t="n">
         <v>194.88</v>
       </c>
       <c r="E13" t="n">
-        <v>88.84</v>
+        <v>46.58</v>
       </c>
       <c r="F13" t="n">
-        <v>2947.38</v>
+        <v>2916.7</v>
       </c>
       <c r="G13" t="n">
         <v>1264.57</v>
       </c>
       <c r="H13" t="n">
-        <v>1940.63</v>
+        <v>1939.51</v>
       </c>
     </row>
     <row r="14">
@@ -1251,22 +1258,22 @@
         <v>1703.91</v>
       </c>
       <c r="C14" t="n">
-        <v>3607.09</v>
+        <v>3549.4</v>
       </c>
       <c r="D14" t="n">
         <v>267.92</v>
       </c>
       <c r="E14" t="n">
-        <v>110.99</v>
+        <v>68.73</v>
       </c>
       <c r="F14" t="n">
-        <v>2617.3</v>
+        <v>2586.62</v>
       </c>
       <c r="G14" t="n">
         <v>1563.66</v>
       </c>
       <c r="H14" t="n">
-        <v>1227.54</v>
+        <v>1226.42</v>
       </c>
     </row>
     <row r="15">
@@ -1277,22 +1284,22 @@
         <v>2404.35</v>
       </c>
       <c r="C15" t="n">
-        <v>4742.11</v>
+        <v>4684.42</v>
       </c>
       <c r="D15" t="n">
         <v>464.78</v>
       </c>
       <c r="E15" t="n">
-        <v>129.57</v>
+        <v>87.31</v>
       </c>
       <c r="F15" t="n">
-        <v>2199.61</v>
+        <v>2168.93</v>
       </c>
       <c r="G15" t="n">
         <v>2251.19</v>
       </c>
       <c r="H15" t="n">
-        <v>1739.59</v>
+        <v>1738.47</v>
       </c>
     </row>
     <row r="16">
@@ -1303,22 +1310,22 @@
         <v>3590.82</v>
       </c>
       <c r="C16" t="n">
-        <v>5760.51</v>
+        <v>4819.82</v>
       </c>
       <c r="D16" t="n">
         <v>779.13</v>
       </c>
       <c r="E16" t="n">
-        <v>132.15</v>
+        <v>89.89</v>
       </c>
       <c r="F16" t="n">
-        <v>2049.17</v>
+        <v>2018.49</v>
       </c>
       <c r="G16" t="n">
         <v>1890.38</v>
       </c>
       <c r="H16" t="n">
-        <v>1414.96</v>
+        <v>1413.84</v>
       </c>
     </row>
     <row r="17">
@@ -1329,22 +1336,22 @@
         <v>3361.21</v>
       </c>
       <c r="C17" t="n">
-        <v>5459.8651</v>
+        <v>5402.175099999999</v>
       </c>
       <c r="D17" t="n">
         <v>811.59</v>
       </c>
       <c r="E17" t="n">
-        <v>128.53</v>
+        <v>86.27</v>
       </c>
       <c r="F17" t="n">
-        <v>1913.81</v>
+        <v>1883.13</v>
       </c>
       <c r="G17" t="n">
         <v>1265.67</v>
       </c>
       <c r="H17" t="n">
-        <v>1936.6549</v>
+        <v>1935.5349</v>
       </c>
     </row>
     <row r="18">
@@ -1355,22 +1362,22 @@
         <v>4976.93</v>
       </c>
       <c r="C18" t="n">
-        <v>4434.57</v>
+        <v>4377.96</v>
       </c>
       <c r="D18" t="n">
         <v>521.72</v>
       </c>
       <c r="E18" t="n">
-        <v>87.97</v>
+        <v>70.77</v>
       </c>
       <c r="F18" t="n">
-        <v>1840.76</v>
+        <v>1802.19</v>
       </c>
       <c r="G18" t="n">
         <v>2009.54</v>
       </c>
       <c r="H18" t="n">
-        <v>1179.64</v>
+        <v>1140.44</v>
       </c>
     </row>
     <row r="19">
@@ -1381,22 +1388,22 @@
         <v>5353.69</v>
       </c>
       <c r="C19" t="n">
-        <v>3798.7</v>
+        <v>3741.01</v>
       </c>
       <c r="D19" t="n">
         <v>390.71</v>
       </c>
       <c r="E19" t="n">
-        <v>115.7</v>
+        <v>73.44</v>
       </c>
       <c r="F19" t="n">
-        <v>2193.69</v>
+        <v>2163.01</v>
       </c>
       <c r="G19" t="n">
         <v>1873.98</v>
       </c>
       <c r="H19" t="n">
-        <v>1073.62</v>
+        <v>1072.5</v>
       </c>
     </row>
     <row r="20">
@@ -1407,22 +1414,22 @@
         <v>3143.62</v>
       </c>
       <c r="C20" t="n">
-        <v>3860.8</v>
+        <v>3803.11</v>
       </c>
       <c r="D20" t="n">
         <v>209.7</v>
       </c>
       <c r="E20" t="n">
-        <v>121.34</v>
+        <v>79.08</v>
       </c>
       <c r="F20" t="n">
-        <v>1687.2</v>
+        <v>1656.52</v>
       </c>
       <c r="G20" t="n">
         <v>2206.33</v>
       </c>
       <c r="H20" t="n">
-        <v>210.27</v>
+        <v>209.15</v>
       </c>
     </row>
     <row r="21">
@@ -1433,22 +1440,22 @@
         <v>1720.43</v>
       </c>
       <c r="C21" t="n">
-        <v>2816.22</v>
+        <v>2758.53</v>
       </c>
       <c r="D21" t="n">
         <v>211.57</v>
       </c>
       <c r="E21" t="n">
-        <v>111.72</v>
+        <v>69.45999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>1551.61</v>
+        <v>1520.93</v>
       </c>
       <c r="G21" t="n">
         <v>2284.86</v>
       </c>
       <c r="H21" t="n">
-        <v>143.3</v>
+        <v>142.18</v>
       </c>
     </row>
     <row r="22">
@@ -1459,22 +1466,22 @@
         <v>800.33</v>
       </c>
       <c r="C22" t="n">
-        <v>2730.37</v>
+        <v>2431.68</v>
       </c>
       <c r="D22" t="n">
         <v>287.21</v>
       </c>
       <c r="E22" t="n">
-        <v>114.42</v>
+        <v>72.16</v>
       </c>
       <c r="F22" t="n">
-        <v>2474.45</v>
+        <v>2443.77</v>
       </c>
       <c r="G22" t="n">
         <v>1875.65</v>
       </c>
       <c r="H22" t="n">
-        <v>568.03</v>
+        <v>566.91</v>
       </c>
     </row>
     <row r="23">
@@ -1485,22 +1492,22 @@
         <v>2052.16</v>
       </c>
       <c r="C23" t="n">
-        <v>2665.2</v>
+        <v>2607.51</v>
       </c>
       <c r="D23" t="n">
         <v>92.2</v>
       </c>
       <c r="E23" t="n">
-        <v>124.52</v>
+        <v>82.26000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>1121.82</v>
+        <v>1091.14</v>
       </c>
       <c r="G23" t="n">
         <v>1883.09</v>
       </c>
       <c r="H23" t="n">
-        <v>210.88</v>
+        <v>209.76</v>
       </c>
     </row>
     <row r="24">
@@ -1511,22 +1518,22 @@
         <v>2001.61</v>
       </c>
       <c r="C24" t="n">
-        <v>3469.29</v>
+        <v>3411.6</v>
       </c>
       <c r="D24" t="n">
         <v>221.33</v>
       </c>
       <c r="E24" t="n">
-        <v>152.99</v>
+        <v>110.73</v>
       </c>
       <c r="F24" t="n">
-        <v>1364.2</v>
+        <v>1333.52</v>
       </c>
       <c r="G24" t="n">
         <v>2002.01</v>
       </c>
       <c r="H24" t="n">
-        <v>150.06</v>
+        <v>148.94</v>
       </c>
     </row>
     <row r="25">
@@ -1537,22 +1544,22 @@
         <v>1873.19</v>
       </c>
       <c r="C25" t="n">
-        <v>4332.73</v>
+        <v>4275.04</v>
       </c>
       <c r="D25" t="n">
         <v>322.93</v>
       </c>
       <c r="E25" t="n">
-        <v>168.06</v>
+        <v>125.8</v>
       </c>
       <c r="F25" t="n">
-        <v>1849.41</v>
+        <v>1818.73</v>
       </c>
       <c r="G25" t="n">
         <v>1916.07</v>
       </c>
       <c r="H25" t="n">
-        <v>318.21</v>
+        <v>317.09</v>
       </c>
     </row>
     <row r="26">
@@ -1563,22 +1570,22 @@
         <v>3312.2</v>
       </c>
       <c r="C26" t="n">
-        <v>5199.64</v>
+        <v>5141.95</v>
       </c>
       <c r="D26" t="n">
         <v>606.58</v>
       </c>
       <c r="E26" t="n">
-        <v>131.76</v>
+        <v>89.5</v>
       </c>
       <c r="F26" t="n">
-        <v>2091.98</v>
+        <v>2061.3</v>
       </c>
       <c r="G26" t="n">
         <v>1542.59</v>
       </c>
       <c r="H26" t="n">
-        <v>316.96</v>
+        <v>315.84</v>
       </c>
     </row>
     <row r="27">
@@ -1589,22 +1596,22 @@
         <v>4133.45</v>
       </c>
       <c r="C27" t="n">
-        <v>4692.52</v>
+        <v>3713.83</v>
       </c>
       <c r="D27" t="n">
         <v>597.4400000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>127.78</v>
+        <v>85.52</v>
       </c>
       <c r="F27" t="n">
-        <v>2465.11</v>
+        <v>2434.43</v>
       </c>
       <c r="G27" t="n">
         <v>1857.11</v>
       </c>
       <c r="H27" t="n">
-        <v>822.27</v>
+        <v>821.15</v>
       </c>
     </row>
     <row r="28">
@@ -1615,22 +1622,22 @@
         <v>5517.77</v>
       </c>
       <c r="C28" t="n">
-        <v>4895.42</v>
+        <v>4046.81</v>
       </c>
       <c r="D28" t="n">
         <v>548.76</v>
       </c>
       <c r="E28" t="n">
-        <v>92.39</v>
+        <v>75.19</v>
       </c>
       <c r="F28" t="n">
-        <v>2218.46</v>
+        <v>2179.89</v>
       </c>
       <c r="G28" t="n">
         <v>2106.93</v>
       </c>
       <c r="H28" t="n">
-        <v>372.9767000000001</v>
+        <v>333.7767</v>
       </c>
     </row>
     <row r="29">
@@ -1641,22 +1648,22 @@
         <v>6005.5</v>
       </c>
       <c r="C29" t="n">
-        <v>4681.89</v>
+        <v>3954.2</v>
       </c>
       <c r="D29" t="n">
         <v>804.7</v>
       </c>
       <c r="E29" t="n">
-        <v>126.33</v>
+        <v>84.06999999999999</v>
       </c>
       <c r="F29" t="n">
-        <v>2387.91</v>
+        <v>2357.23</v>
       </c>
       <c r="G29" t="n">
         <v>2040.45</v>
       </c>
       <c r="H29" t="n">
-        <v>688.04</v>
+        <v>686.92</v>
       </c>
     </row>
     <row r="30">
@@ -1667,22 +1674,22 @@
         <v>5008.52</v>
       </c>
       <c r="C30" t="n">
-        <v>3847.41</v>
+        <v>3133.08</v>
       </c>
       <c r="D30" t="n">
         <v>410.23</v>
       </c>
       <c r="E30" t="n">
-        <v>100.05</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>2157.88</v>
+        <v>2122.86</v>
       </c>
       <c r="G30" t="n">
         <v>2286.35</v>
       </c>
       <c r="H30" t="n">
-        <v>285.88</v>
+        <v>275.13</v>
       </c>
     </row>
     <row r="31">
@@ -1693,22 +1700,22 @@
         <v>3114.14</v>
       </c>
       <c r="C31" t="n">
-        <v>3363.18</v>
+        <v>2642.49</v>
       </c>
       <c r="D31" t="n">
         <v>191.14</v>
       </c>
       <c r="E31" t="n">
-        <v>118.26</v>
+        <v>76</v>
       </c>
       <c r="F31" t="n">
-        <v>1700.85</v>
+        <v>1670.17</v>
       </c>
       <c r="G31" t="n">
         <v>1826.26</v>
       </c>
       <c r="H31" t="n">
-        <v>29.95</v>
+        <v>28.83</v>
       </c>
     </row>
     <row r="32">
@@ -1719,22 +1726,22 @@
         <v>2754.86</v>
       </c>
       <c r="C32" t="n">
-        <v>2013.45</v>
+        <v>1492.76</v>
       </c>
       <c r="D32" t="n">
         <v>147.84</v>
       </c>
       <c r="E32" t="n">
-        <v>92.04000000000001</v>
+        <v>49.78</v>
       </c>
       <c r="F32" t="n">
-        <v>1503.8</v>
+        <v>1473.12</v>
       </c>
       <c r="G32" t="n">
         <v>1571.66</v>
       </c>
       <c r="H32" t="n">
-        <v>28.08</v>
+        <v>26.96</v>
       </c>
     </row>
     <row r="33">
@@ -1745,22 +1752,22 @@
         <v>1859.01</v>
       </c>
       <c r="C33" t="n">
-        <v>2482.59</v>
+        <v>2093.9</v>
       </c>
       <c r="D33" t="n">
         <v>150.37</v>
       </c>
       <c r="E33" t="n">
-        <v>104.08</v>
+        <v>61.82</v>
       </c>
       <c r="F33" t="n">
-        <v>1723.86</v>
+        <v>1693.18</v>
       </c>
       <c r="G33" t="n">
         <v>1464.43</v>
       </c>
       <c r="H33" t="n">
-        <v>276.89</v>
+        <v>275.77</v>
       </c>
     </row>
     <row r="34">
@@ -1771,22 +1778,22 @@
         <v>924.22</v>
       </c>
       <c r="C34" t="n">
-        <v>2848.44</v>
+        <v>2549.75</v>
       </c>
       <c r="D34" t="n">
         <v>127.55</v>
       </c>
       <c r="E34" t="n">
-        <v>90.2</v>
+        <v>47.94</v>
       </c>
       <c r="F34" t="n">
-        <v>1979.61</v>
+        <v>1948.93</v>
       </c>
       <c r="G34" t="n">
         <v>1727.8</v>
       </c>
       <c r="H34" t="n">
-        <v>959.58</v>
+        <v>958.46</v>
       </c>
     </row>
     <row r="35">
@@ -1797,22 +1804,22 @@
         <v>1766.29</v>
       </c>
       <c r="C35" t="n">
-        <v>2589.51</v>
+        <v>2236.82</v>
       </c>
       <c r="D35" t="n">
         <v>107.6335</v>
       </c>
       <c r="E35" t="n">
-        <v>132.43</v>
+        <v>90.17</v>
       </c>
       <c r="F35" t="n">
-        <v>1159.39</v>
+        <v>1128.71</v>
       </c>
       <c r="G35" t="n">
         <v>1660.25</v>
       </c>
       <c r="H35" t="n">
-        <v>101.65</v>
+        <v>100.53</v>
       </c>
     </row>
     <row r="36">
@@ -1823,22 +1830,22 @@
         <v>2216.81</v>
       </c>
       <c r="C36" t="n">
-        <v>3031.21</v>
+        <v>2453.52</v>
       </c>
       <c r="D36" t="n">
         <v>204.7</v>
       </c>
       <c r="E36" t="n">
-        <v>152.24</v>
+        <v>109.98</v>
       </c>
       <c r="F36" t="n">
-        <v>892.45</v>
+        <v>861.77</v>
       </c>
       <c r="G36" t="n">
         <v>2069.6</v>
       </c>
       <c r="H36" t="n">
-        <v>79.62</v>
+        <v>78.5</v>
       </c>
     </row>
     <row r="37">
@@ -1849,22 +1856,22 @@
         <v>3906.27</v>
       </c>
       <c r="C37" t="n">
-        <v>4803.32</v>
+        <v>4745.63</v>
       </c>
       <c r="D37" t="n">
         <v>445.44</v>
       </c>
       <c r="E37" t="n">
-        <v>167.13</v>
+        <v>124.87</v>
       </c>
       <c r="F37" t="n">
-        <v>1784.95</v>
+        <v>1754.27</v>
       </c>
       <c r="G37" t="n">
         <v>2360.02</v>
       </c>
       <c r="H37" t="n">
-        <v>120</v>
+        <v>118.88</v>
       </c>
     </row>
     <row r="38">
@@ -1875,22 +1882,22 @@
         <v>4728.5</v>
       </c>
       <c r="C38" t="n">
-        <v>4615.84</v>
+        <v>4559.23</v>
       </c>
       <c r="D38" t="n">
         <v>515.73</v>
       </c>
       <c r="E38" t="n">
-        <v>134.74</v>
+        <v>117.54</v>
       </c>
       <c r="F38" t="n">
-        <v>2164.64</v>
+        <v>2126.07</v>
       </c>
       <c r="G38" t="n">
         <v>1998.39</v>
       </c>
       <c r="H38" t="n">
-        <v>361.9</v>
+        <v>322.7</v>
       </c>
     </row>
     <row r="39">
@@ -1927,22 +1934,22 @@
         <v>5361.562599999999</v>
       </c>
       <c r="C40" t="n">
-        <v>3912.2308</v>
+        <v>3861.9008</v>
       </c>
       <c r="D40" t="n">
         <v>398.2539</v>
       </c>
       <c r="E40" t="n">
-        <v>119.6333</v>
+        <v>98.3733</v>
       </c>
       <c r="F40" t="n">
-        <v>2021.3729</v>
+        <v>1986.3529</v>
       </c>
       <c r="G40" t="n">
         <v>2190.305</v>
       </c>
       <c r="H40" t="n">
-        <v>63.12260000000001</v>
+        <v>52.37260000000001</v>
       </c>
     </row>
     <row r="41">
@@ -1979,22 +1986,22 @@
         <v>3187.387</v>
       </c>
       <c r="C42" t="n">
-        <v>3668.2931</v>
+        <v>3617.9631</v>
       </c>
       <c r="D42" t="n">
         <v>189.9809</v>
       </c>
       <c r="E42" t="n">
-        <v>120.3267</v>
+        <v>99.0667</v>
       </c>
       <c r="F42" t="n">
-        <v>2455.8144</v>
+        <v>2420.7944</v>
       </c>
       <c r="G42" t="n">
         <v>1441.938</v>
       </c>
       <c r="H42" t="n">
-        <v>75.607</v>
+        <v>64.857</v>
       </c>
     </row>
     <row r="43">
@@ -2005,22 +2012,22 @@
         <v>2859.994</v>
       </c>
       <c r="C43" t="n">
-        <v>2277.865</v>
+        <v>1764.535</v>
       </c>
       <c r="D43" t="n">
         <v>98.00360000000001</v>
       </c>
       <c r="E43" t="n">
-        <v>90.34410000000001</v>
+        <v>69.08410000000001</v>
       </c>
       <c r="F43" t="n">
-        <v>1530.6692</v>
+        <v>1495.6492</v>
       </c>
       <c r="G43" t="n">
         <v>1655.204</v>
       </c>
       <c r="H43" t="n">
-        <v>62.9765</v>
+        <v>52.2265</v>
       </c>
     </row>
     <row r="44">
@@ -2031,22 +2038,22 @@
         <v>1778.2807</v>
       </c>
       <c r="C44" t="n">
-        <v>2955.8249</v>
+        <v>2574.4949</v>
       </c>
       <c r="D44" t="n">
         <v>261.6238</v>
       </c>
       <c r="E44" t="n">
-        <v>97.07610000000001</v>
+        <v>75.81610000000001</v>
       </c>
       <c r="F44" t="n">
-        <v>942.9352</v>
+        <v>907.9151999999999</v>
       </c>
       <c r="G44" t="n">
         <v>2065.1</v>
       </c>
       <c r="H44" t="n">
-        <v>114.4523</v>
+        <v>103.7023</v>
       </c>
     </row>
     <row r="45">
@@ -2057,22 +2064,22 @@
         <v>866.3856</v>
       </c>
       <c r="C45" t="n">
-        <v>2902.6672</v>
+        <v>2611.3372</v>
       </c>
       <c r="D45" t="n">
         <v>218.0394</v>
       </c>
       <c r="E45" t="n">
-        <v>107.2846</v>
+        <v>86.02460000000001</v>
       </c>
       <c r="F45" t="n">
-        <v>1999.1386</v>
+        <v>1964.1186</v>
       </c>
       <c r="G45" t="n">
         <v>2169.373</v>
       </c>
       <c r="H45" t="n">
-        <v>215.165</v>
+        <v>204.415</v>
       </c>
     </row>
     <row r="46">
@@ -2083,22 +2090,22 @@
         <v>1883.3866</v>
       </c>
       <c r="C46" t="n">
-        <v>2042.0648</v>
+        <v>1696.7348</v>
       </c>
       <c r="D46" t="n">
         <v>173.5375</v>
       </c>
       <c r="E46" t="n">
-        <v>105.9754</v>
+        <v>84.71539999999999</v>
       </c>
       <c r="F46" t="n">
-        <v>1186.5822</v>
+        <v>1151.5622</v>
       </c>
       <c r="G46" t="n">
         <v>1846.937</v>
       </c>
       <c r="H46" t="n">
-        <v>89.63380000000001</v>
+        <v>78.88380000000001</v>
       </c>
     </row>
     <row r="47">
@@ -2109,22 +2116,22 @@
         <v>1296.7704</v>
       </c>
       <c r="C47" t="n">
-        <v>3077.0846</v>
+        <v>2506.7546</v>
       </c>
       <c r="D47" t="n">
         <v>230.496</v>
       </c>
       <c r="E47" t="n">
-        <v>141.2016</v>
+        <v>119.9416</v>
       </c>
       <c r="F47" t="n">
-        <v>1972.9622</v>
+        <v>1937.9422</v>
       </c>
       <c r="G47" t="n">
         <v>2222.792</v>
       </c>
       <c r="H47" t="n">
-        <v>65.69760000000001</v>
+        <v>54.9476</v>
       </c>
     </row>
     <row r="48">
@@ -2135,22 +2142,22 @@
         <v>2306.4274</v>
       </c>
       <c r="C48" t="n">
-        <v>3637.548</v>
+        <v>2998.858</v>
       </c>
       <c r="D48" t="n">
         <v>478.3781</v>
       </c>
       <c r="E48" t="n">
-        <v>157.6383</v>
+        <v>115.3783</v>
       </c>
       <c r="F48" t="n">
-        <v>2609.5888</v>
+        <v>2578.9088</v>
       </c>
       <c r="G48" t="n">
         <v>1882.431</v>
       </c>
       <c r="H48" t="n">
-        <v>121.4963</v>
+        <v>120.3763</v>
       </c>
     </row>
     <row r="49">
@@ -2161,22 +2168,22 @@
         <v>4843.855</v>
       </c>
       <c r="C49" t="n">
-        <v>3990.0145</v>
+        <v>3050.6845</v>
       </c>
       <c r="D49" t="n">
         <v>432.5818</v>
       </c>
       <c r="E49" t="n">
-        <v>137.2784</v>
+        <v>116.0184</v>
       </c>
       <c r="F49" t="n">
-        <v>2244.6924</v>
+        <v>2209.6724</v>
       </c>
       <c r="G49" t="n">
         <v>2011.778</v>
       </c>
       <c r="H49" t="n">
-        <v>64.58199999999999</v>
+        <v>53.83199999999999</v>
       </c>
     </row>
     <row r="50">
@@ -2187,22 +2194,22 @@
         <v>5409.7255</v>
       </c>
       <c r="C50" t="n">
-        <v>4190.0862</v>
+        <v>3183.7562</v>
       </c>
       <c r="D50" t="n">
         <v>522.0157</v>
       </c>
       <c r="E50" t="n">
-        <v>127.5038</v>
+        <v>106.2438</v>
       </c>
       <c r="F50" t="n">
-        <v>2941.8356</v>
+        <v>2906.8156</v>
       </c>
       <c r="G50" t="n">
         <v>1382.836</v>
       </c>
       <c r="H50" t="n">
-        <v>196.7965</v>
+        <v>186.0465</v>
       </c>
     </row>
     <row r="51">
@@ -2213,22 +2220,22 @@
         <v>5668.138400000001</v>
       </c>
       <c r="C51" t="n">
-        <v>4663.474</v>
+        <v>3530.864</v>
       </c>
       <c r="D51" t="n">
         <v>591.9218000000001</v>
       </c>
       <c r="E51" t="n">
-        <v>122.1813</v>
+        <v>104.9813</v>
       </c>
       <c r="F51" t="n">
-        <v>2680.6797</v>
+        <v>2642.1097</v>
       </c>
       <c r="G51" t="n">
         <v>1405.452</v>
       </c>
       <c r="H51" t="n">
-        <v>182.8597</v>
+        <v>143.6597</v>
       </c>
     </row>
     <row r="52">
@@ -2239,22 +2246,22 @@
         <v>5517.3455</v>
       </c>
       <c r="C52" t="n">
-        <v>4071.0542</v>
+        <v>3214.7242</v>
       </c>
       <c r="D52" t="n">
         <v>512.1828</v>
       </c>
       <c r="E52" t="n">
-        <v>125.2556</v>
+        <v>103.9956</v>
       </c>
       <c r="F52" t="n">
-        <v>2615.0377</v>
+        <v>2580.0177</v>
       </c>
       <c r="G52" t="n">
         <v>2145.255</v>
       </c>
       <c r="H52" t="n">
-        <v>138.2036</v>
+        <v>127.4536</v>
       </c>
     </row>
     <row r="53">
@@ -2265,22 +2272,22 @@
         <v>4783.282099999999</v>
       </c>
       <c r="C53" t="n">
-        <v>3525.8437</v>
+        <v>2755.5137</v>
       </c>
       <c r="D53" t="n">
         <v>341.6499</v>
       </c>
       <c r="E53" t="n">
-        <v>129.0691</v>
+        <v>107.8091</v>
       </c>
       <c r="F53" t="n">
-        <v>2256.1795</v>
+        <v>2221.1595</v>
       </c>
       <c r="G53" t="n">
         <v>2227.359</v>
       </c>
       <c r="H53" t="n">
-        <v>142.2121</v>
+        <v>131.4621</v>
       </c>
     </row>
     <row r="54">
@@ -2291,22 +2298,22 @@
         <v>2704.7235</v>
       </c>
       <c r="C54" t="n">
-        <v>3706.7596</v>
+        <v>2854.4296</v>
       </c>
       <c r="D54" t="n">
         <v>185.1985</v>
       </c>
       <c r="E54" t="n">
-        <v>117.5236</v>
+        <v>96.26360000000001</v>
       </c>
       <c r="F54" t="n">
-        <v>1761.6579</v>
+        <v>1726.6379</v>
       </c>
       <c r="G54" t="n">
         <v>2187.854</v>
       </c>
       <c r="H54" t="n">
-        <v>98.1626</v>
+        <v>87.4126</v>
       </c>
     </row>
     <row r="55">
@@ -2317,22 +2324,22 @@
         <v>3152.6328</v>
       </c>
       <c r="C55" t="n">
-        <v>1889.0284</v>
+        <v>1375.6984</v>
       </c>
       <c r="D55" t="n">
         <v>135.6288</v>
       </c>
       <c r="E55" t="n">
-        <v>107.3394</v>
+        <v>86.07939999999999</v>
       </c>
       <c r="F55" t="n">
-        <v>1194.2396</v>
+        <v>1159.2196</v>
       </c>
       <c r="G55" t="n">
         <v>2030.922</v>
       </c>
       <c r="H55" t="n">
-        <v>86.1298</v>
+        <v>75.3798</v>
       </c>
     </row>
     <row r="56">
@@ -2343,22 +2350,22 @@
         <v>1534.0313</v>
       </c>
       <c r="C56" t="n">
-        <v>2795.6272</v>
+        <v>2414.2972</v>
       </c>
       <c r="D56" t="n">
         <v>162.2485</v>
       </c>
       <c r="E56" t="n">
-        <v>94.8647</v>
+        <v>73.60469999999999</v>
       </c>
       <c r="F56" t="n">
-        <v>2082.1082</v>
+        <v>2047.0882</v>
       </c>
       <c r="G56" t="n">
         <v>2125.797</v>
       </c>
       <c r="H56" t="n">
-        <v>107.7788</v>
+        <v>97.0288</v>
       </c>
     </row>
     <row r="57">
@@ -2369,22 +2376,22 @@
         <v>713.2711999999999</v>
       </c>
       <c r="C57" t="n">
-        <v>3410.7324</v>
+        <v>3119.4024</v>
       </c>
       <c r="D57" t="n">
         <v>241.3181</v>
       </c>
       <c r="E57" t="n">
-        <v>94.7938</v>
+        <v>73.5338</v>
       </c>
       <c r="F57" t="n">
-        <v>3018.4799</v>
+        <v>2983.4599</v>
       </c>
       <c r="G57" t="n">
         <v>1598.833</v>
       </c>
       <c r="H57" t="n">
-        <v>386.4921</v>
+        <v>375.7421</v>
       </c>
     </row>
     <row r="58">
@@ -2395,22 +2402,22 @@
         <v>1782.5146</v>
       </c>
       <c r="C58" t="n">
-        <v>1960.6131</v>
+        <v>1615.2831</v>
       </c>
       <c r="D58" t="n">
         <v>250.5021</v>
       </c>
       <c r="E58" t="n">
-        <v>112.9769</v>
+        <v>91.7169</v>
       </c>
       <c r="F58" t="n">
-        <v>2416.0287</v>
+        <v>2381.0087</v>
       </c>
       <c r="G58" t="n">
         <v>1448.9644</v>
       </c>
       <c r="H58" t="n">
-        <v>101.704</v>
+        <v>90.95399999999999</v>
       </c>
     </row>
     <row r="59">
@@ -2421,22 +2428,22 @@
         <v>2105.1773</v>
       </c>
       <c r="C59" t="n">
-        <v>2087.8689</v>
+        <v>1517.5389</v>
       </c>
       <c r="D59" t="n">
         <v>308.9725</v>
       </c>
       <c r="E59" t="n">
-        <v>126.8873</v>
+        <v>105.6273</v>
       </c>
       <c r="F59" t="n">
-        <v>2766.9997</v>
+        <v>2731.9797</v>
       </c>
       <c r="G59" t="n">
         <v>1962.29</v>
       </c>
       <c r="H59" t="n">
-        <v>179.1592</v>
+        <v>168.4092</v>
       </c>
     </row>
     <row r="60">
@@ -2447,22 +2454,22 @@
         <v>2078.9754</v>
       </c>
       <c r="C60" t="n">
-        <v>1987.0137</v>
+        <v>1348.3237</v>
       </c>
       <c r="D60" t="n">
         <v>409.1017</v>
       </c>
       <c r="E60" t="n">
-        <v>153.6898</v>
+        <v>111.4298</v>
       </c>
       <c r="F60" t="n">
-        <v>2855.9568</v>
+        <v>2825.2768</v>
       </c>
       <c r="G60" t="n">
         <v>2096.831</v>
       </c>
       <c r="H60" t="n">
-        <v>597.6172</v>
+        <v>596.4972</v>
       </c>
     </row>
     <row r="61">
@@ -2473,22 +2480,22 @@
         <v>4204.9879</v>
       </c>
       <c r="C61" t="n">
-        <v>3481.9203</v>
+        <v>2542.5903</v>
       </c>
       <c r="D61" t="n">
         <v>665.157</v>
       </c>
       <c r="E61" t="n">
-        <v>140.3943</v>
+        <v>119.1343</v>
       </c>
       <c r="F61" t="n">
-        <v>3220.5207</v>
+        <v>3185.5007</v>
       </c>
       <c r="G61" t="n">
         <v>1801.332</v>
       </c>
       <c r="H61" t="n">
-        <v>93.99299999999999</v>
+        <v>83.24299999999999</v>
       </c>
     </row>
     <row r="62">
@@ -2499,22 +2506,22 @@
         <v>5241.7973</v>
       </c>
       <c r="C62" t="n">
-        <v>3352.8355</v>
+        <v>2346.5055</v>
       </c>
       <c r="D62" t="n">
         <v>675.9476</v>
       </c>
       <c r="E62" t="n">
-        <v>131.6682</v>
+        <v>110.4082</v>
       </c>
       <c r="F62" t="n">
-        <v>3092.5564</v>
+        <v>3057.5364</v>
       </c>
       <c r="G62" t="n">
         <v>1800.261</v>
       </c>
       <c r="H62" t="n">
-        <v>162.5165</v>
+        <v>151.7665</v>
       </c>
     </row>
     <row r="63">
@@ -2525,22 +2532,22 @@
         <v>6019.491599999999</v>
       </c>
       <c r="C63" t="n">
-        <v>3751.5769</v>
+        <v>2618.9669</v>
       </c>
       <c r="D63" t="n">
         <v>681.8073000000001</v>
       </c>
       <c r="E63" t="n">
-        <v>123.3364</v>
+        <v>106.1364</v>
       </c>
       <c r="F63" t="n">
-        <v>3856.9232</v>
+        <v>3818.3532</v>
       </c>
       <c r="G63" t="n">
         <v>1526.708</v>
       </c>
       <c r="H63" t="n">
-        <v>331.2988999999999</v>
+        <v>292.0989</v>
       </c>
     </row>
     <row r="64">
@@ -2551,22 +2558,22 @@
         <v>5654.882</v>
       </c>
       <c r="C64" t="n">
-        <v>3219.8241</v>
+        <v>2363.4941</v>
       </c>
       <c r="D64" t="n">
         <v>833.2471999999999</v>
       </c>
       <c r="E64" t="n">
-        <v>133.2817</v>
+        <v>112.0217</v>
       </c>
       <c r="F64" t="n">
-        <v>3990.0718</v>
+        <v>3955.0518</v>
       </c>
       <c r="G64" t="n">
         <v>1531.552</v>
       </c>
       <c r="H64" t="n">
-        <v>448.5114</v>
+        <v>437.7614</v>
       </c>
     </row>
   </sheetData>
@@ -2581,7 +2588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO64"/>
+  <dimension ref="A1:AP64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2727,65 +2734,70 @@
       </c>
       <c r="AC1" t="inlineStr">
         <is>
+          <t>KE_basis</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>KE_included</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
           <t>KE_own_unsplit_MWh</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>KE_external_MWh</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>KE_own_Oil_MWh</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>KE_own_Gas_MWh</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>KE_own_RLNG_MWh</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>KE_IPP_Oil_MWh</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>KE_IPP_Gas_MWh</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>KE_IPP_Coal_MWh</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>KE_IPP_Solar_MWh</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>KE_basis</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>KE_external_MWh</t>
-        </is>
-      </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>KE_from_CPPA_MWh</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>KE_own_Oil_MWh</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
-        <is>
-          <t>KE_own_Gas_MWh</t>
-        </is>
-      </c>
-      <c r="AM1" t="inlineStr">
-        <is>
-          <t>KE_own_RLNG_MWh</t>
-        </is>
-      </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>KE_own_MWh</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>KE_purchases_nonCPPA_MWh</t>
         </is>
@@ -2799,13 +2811,13 @@
         <v>2033930</v>
       </c>
       <c r="C2" t="n">
-        <v>1933660</v>
+        <v>1902980</v>
       </c>
       <c r="D2" t="n">
-        <v>2486100</v>
+        <v>2177410</v>
       </c>
       <c r="E2" t="n">
-        <v>78430</v>
+        <v>77310</v>
       </c>
       <c r="F2" t="n">
         <v>791910</v>
@@ -2814,7 +2826,7 @@
         <v>98110</v>
       </c>
       <c r="H2" t="n">
-        <v>99320</v>
+        <v>57060</v>
       </c>
       <c r="I2" t="n">
         <v>99270</v>
@@ -2823,7 +2835,7 @@
         <v>13370</v>
       </c>
       <c r="K2" t="n">
-        <v>7634100</v>
+        <v>7251350</v>
       </c>
       <c r="L2" t="n">
         <v>29650</v>
@@ -2870,31 +2882,13 @@
       <c r="AB2" t="n">
         <v>0</v>
       </c>
-      <c r="AC2" t="n">
-        <v>251000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1120</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>57690</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>30680</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>42260</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>own: ESTIMATE copied from 2022-02; IPP purchases: ESTIMATE copied from 2024-04</t>
-        </is>
-      </c>
-      <c r="AN2" t="n">
-        <v>251000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>131750</v>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>no KE figure</t>
+        </is>
+      </c>
+      <c r="AD2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -2905,13 +2899,13 @@
         <v>1740580</v>
       </c>
       <c r="C3" t="n">
-        <v>2765070</v>
+        <v>2734390</v>
       </c>
       <c r="D3" t="n">
-        <v>3577680</v>
+        <v>2928990</v>
       </c>
       <c r="E3" t="n">
-        <v>236240</v>
+        <v>235120</v>
       </c>
       <c r="F3" t="n">
         <v>940160</v>
@@ -2920,7 +2914,7 @@
         <v>169520</v>
       </c>
       <c r="H3" t="n">
-        <v>108630</v>
+        <v>66370</v>
       </c>
       <c r="I3" t="n">
         <v>90080</v>
@@ -2929,7 +2923,7 @@
         <v>20880</v>
       </c>
       <c r="K3" t="n">
-        <v>9648840</v>
+        <v>8926090</v>
       </c>
       <c r="L3" t="n">
         <v>38700</v>
@@ -2976,31 +2970,13 @@
       <c r="AB3" t="n">
         <v>0</v>
       </c>
-      <c r="AC3" t="n">
-        <v>591000</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1120</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>57690</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>30680</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>42260</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>own: ESTIMATE copied from 2022-03; IPP purchases: ESTIMATE copied from 2024-04</t>
-        </is>
-      </c>
-      <c r="AN3" t="n">
-        <v>591000</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>131750</v>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>no KE figure</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -3011,13 +2987,13 @@
         <v>2572580</v>
       </c>
       <c r="C4" t="n">
-        <v>2470560</v>
+        <v>2439880</v>
       </c>
       <c r="D4" t="n">
-        <v>4798160</v>
+        <v>3849470</v>
       </c>
       <c r="E4" t="n">
-        <v>148970</v>
+        <v>147850</v>
       </c>
       <c r="F4" t="n">
         <v>1067090</v>
@@ -3026,7 +3002,7 @@
         <v>197300</v>
       </c>
       <c r="H4" t="n">
-        <v>110290</v>
+        <v>68030</v>
       </c>
       <c r="I4" t="n">
         <v>71180</v>
@@ -3035,7 +3011,7 @@
         <v>22740</v>
       </c>
       <c r="K4" t="n">
-        <v>11458870</v>
+        <v>10436120</v>
       </c>
       <c r="L4" t="n">
         <v>44840</v>
@@ -3082,31 +3058,13 @@
       <c r="AB4" t="n">
         <v>0</v>
       </c>
-      <c r="AC4" t="n">
-        <v>891000</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1120</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>57690</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>30680</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>42260</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>own: ESTIMATE copied from 2022-04; IPP purchases: ESTIMATE copied from 2024-04</t>
-        </is>
-      </c>
-      <c r="AN4" t="n">
-        <v>891000</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>131750</v>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>no KE figure</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -3117,13 +3075,13 @@
         <v>3465460</v>
       </c>
       <c r="C5" t="n">
-        <v>2649650</v>
+        <v>2618970</v>
       </c>
       <c r="D5" t="n">
-        <v>5223630</v>
+        <v>4282940</v>
       </c>
       <c r="E5" t="n">
-        <v>792930</v>
+        <v>791810</v>
       </c>
       <c r="F5" t="n">
         <v>1271350</v>
@@ -3132,7 +3090,7 @@
         <v>403210</v>
       </c>
       <c r="H5" t="n">
-        <v>108800</v>
+        <v>66540</v>
       </c>
       <c r="I5" t="n">
         <v>45450</v>
@@ -3141,7 +3099,7 @@
         <v>16390</v>
       </c>
       <c r="K5" t="n">
-        <v>13976870</v>
+        <v>12962120</v>
       </c>
       <c r="L5" t="n">
         <v>47390</v>
@@ -3188,31 +3146,13 @@
       <c r="AB5" t="n">
         <v>20320</v>
       </c>
-      <c r="AC5" t="n">
-        <v>883000</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1120</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>57690</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>30680</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>42260</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>own: ESTIMATE copied from 2023-05; IPP purchases: ESTIMATE copied from 2024-04</t>
-        </is>
-      </c>
-      <c r="AN5" t="n">
-        <v>883000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>131750</v>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>no KE figure</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -3223,13 +3163,13 @@
         <v>4222150</v>
       </c>
       <c r="C6" t="n">
-        <v>2620470</v>
+        <v>2589790</v>
       </c>
       <c r="D6" t="n">
-        <v>5022870</v>
+        <v>4965180</v>
       </c>
       <c r="E6" t="n">
-        <v>1236670</v>
+        <v>1235550</v>
       </c>
       <c r="F6" t="n">
         <v>1618060</v>
@@ -3238,7 +3178,7 @@
         <v>510760</v>
       </c>
       <c r="H6" t="n">
-        <v>105350</v>
+        <v>63090</v>
       </c>
       <c r="I6" t="n">
         <v>56480</v>
@@ -3247,7 +3187,7 @@
         <v>10210</v>
       </c>
       <c r="K6" t="n">
-        <v>15403020</v>
+        <v>15271270</v>
       </c>
       <c r="L6" t="n">
         <v>49910</v>
@@ -3294,37 +3234,22 @@
       <c r="AB6" t="n">
         <v>61350</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>own: NEPRA KE decision, no fuel split (counted as gas); IPP purchases: no figure</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE6" t="n">
         <v>960000</v>
       </c>
-      <c r="AD6" t="n">
-        <v>1120</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>57690</v>
-      </c>
       <c r="AF6" t="n">
-        <v>30680</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>42260</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>own: NEPRA KE decision (no fuel split); IPP purchases: ESTIMATE copied from 2024-04</t>
-        </is>
-      </c>
-      <c r="AI6" t="n">
         <v>1131000</v>
       </c>
-      <c r="AJ6" t="n">
-        <v>999250</v>
-      </c>
-      <c r="AN6" t="n">
+      <c r="AO6" t="n">
         <v>960000</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>131750</v>
       </c>
     </row>
     <row r="7">
@@ -3335,13 +3260,13 @@
         <v>4695760</v>
       </c>
       <c r="C7" t="n">
-        <v>2421900</v>
+        <v>2383330</v>
       </c>
       <c r="D7" t="n">
-        <v>5410500</v>
+        <v>5353890</v>
       </c>
       <c r="E7" t="n">
-        <v>1774950</v>
+        <v>1735750</v>
       </c>
       <c r="F7" t="n">
         <v>1659860</v>
@@ -3350,7 +3275,7 @@
         <v>550370</v>
       </c>
       <c r="H7" t="n">
-        <v>79020</v>
+        <v>61820</v>
       </c>
       <c r="I7" t="n">
         <v>45020</v>
@@ -3359,7 +3284,7 @@
         <v>9880</v>
       </c>
       <c r="K7" t="n">
-        <v>16647260</v>
+        <v>16495680</v>
       </c>
       <c r="L7" t="n">
         <v>40090</v>
@@ -3406,37 +3331,22 @@
       <c r="AB7" t="n">
         <v>123490</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>own: NEPRA KE decision, no fuel split (counted as gas); IPP purchases: no figure</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE7" t="n">
         <v>854000</v>
       </c>
-      <c r="AD7" t="n">
-        <v>39200</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>56610</v>
-      </c>
       <c r="AF7" t="n">
-        <v>38570</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>17200</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>own: NEPRA KE decision (no fuel split); IPP purchases: ESTIMATE copied from 2024-07</t>
-        </is>
-      </c>
-      <c r="AI7" t="n">
         <v>1113000</v>
       </c>
-      <c r="AJ7" t="n">
-        <v>961420</v>
-      </c>
-      <c r="AN7" t="n">
+      <c r="AO7" t="n">
         <v>854000</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>151580</v>
       </c>
     </row>
     <row r="8">
@@ -3447,13 +3357,13 @@
         <v>5594300</v>
       </c>
       <c r="C8" t="n">
-        <v>2324540</v>
+        <v>2293860</v>
       </c>
       <c r="D8" t="n">
-        <v>4936820</v>
+        <v>4209130</v>
       </c>
       <c r="E8" t="n">
-        <v>1648520</v>
+        <v>1647400</v>
       </c>
       <c r="F8" t="n">
         <v>1630190</v>
@@ -3462,7 +3372,7 @@
         <v>549950</v>
       </c>
       <c r="H8" t="n">
-        <v>109270</v>
+        <v>67010</v>
       </c>
       <c r="I8" t="n">
         <v>24060</v>
@@ -3471,7 +3381,7 @@
         <v>16980</v>
       </c>
       <c r="K8" t="n">
-        <v>16834630</v>
+        <v>16032880</v>
       </c>
       <c r="L8" t="n">
         <v>45240</v>
@@ -3518,31 +3428,13 @@
       <c r="AB8" t="n">
         <v>19840</v>
       </c>
-      <c r="AC8" t="n">
-        <v>670000</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1120</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>57690</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>30680</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>42260</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>own: ESTIMATE copied from 2022-08; IPP purchases: ESTIMATE copied from 2024-04</t>
-        </is>
-      </c>
-      <c r="AN8" t="n">
-        <v>670000</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>131750</v>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>no KE figure</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -3553,13 +3445,13 @@
         <v>5085480</v>
       </c>
       <c r="C9" t="n">
-        <v>2427540</v>
+        <v>2392520</v>
       </c>
       <c r="D9" t="n">
-        <v>4853560</v>
+        <v>4803230</v>
       </c>
       <c r="E9" t="n">
-        <v>1010530</v>
+        <v>999780</v>
       </c>
       <c r="F9" t="n">
         <v>1281800</v>
@@ -3568,7 +3460,7 @@
         <v>230400</v>
       </c>
       <c r="H9" t="n">
-        <v>82010</v>
+        <v>60750</v>
       </c>
       <c r="I9" t="n">
         <v>16480</v>
@@ -3577,7 +3469,7 @@
         <v>16180</v>
       </c>
       <c r="K9" t="n">
-        <v>15003980</v>
+        <v>14886620</v>
       </c>
       <c r="L9" t="n">
         <v>48270</v>
@@ -3624,37 +3516,22 @@
       <c r="AB9" t="n">
         <v>2340</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>own: NEPRA KE decision, no fuel split (counted as gas); IPP purchases: no figure</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE9" t="n">
         <v>903000</v>
       </c>
-      <c r="AD9" t="n">
-        <v>10750</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>50330</v>
-      </c>
       <c r="AF9" t="n">
-        <v>35020</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>21260</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>own: NEPRA KE decision (no fuel split); IPP purchases: ESTIMATE copied from 2024-09</t>
-        </is>
-      </c>
-      <c r="AI9" t="n">
         <v>1019000</v>
       </c>
-      <c r="AJ9" t="n">
-        <v>901640</v>
-      </c>
-      <c r="AN9" t="n">
+      <c r="AO9" t="n">
         <v>903000</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>117360</v>
       </c>
     </row>
     <row r="10">
@@ -3665,13 +3542,13 @@
         <v>2627250</v>
       </c>
       <c r="C10" t="n">
-        <v>1916460</v>
+        <v>1885780</v>
       </c>
       <c r="D10" t="n">
-        <v>4611820</v>
+        <v>4554130</v>
       </c>
       <c r="E10" t="n">
-        <v>1286880</v>
+        <v>1285760</v>
       </c>
       <c r="F10" t="n">
         <v>1392920</v>
@@ -3680,7 +3557,7 @@
         <v>184820</v>
       </c>
       <c r="H10" t="n">
-        <v>105430</v>
+        <v>63170</v>
       </c>
       <c r="I10" t="n">
         <v>7140</v>
@@ -3689,7 +3566,7 @@
         <v>11870</v>
       </c>
       <c r="K10" t="n">
-        <v>12144590</v>
+        <v>12012840</v>
       </c>
       <c r="L10" t="n">
         <v>41410</v>
@@ -3736,37 +3613,22 @@
       <c r="AB10" t="n">
         <v>57100</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>own: NEPRA KE decision, no fuel split (counted as gas); IPP purchases: no figure</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE10" t="n">
         <v>758000</v>
       </c>
-      <c r="AD10" t="n">
-        <v>1120</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>57690</v>
-      </c>
       <c r="AF10" t="n">
-        <v>30680</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>42260</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>own: NEPRA KE decision (no fuel split); IPP purchases: ESTIMATE copied from 2024-04</t>
-        </is>
-      </c>
-      <c r="AI10" t="n">
         <v>1019000</v>
       </c>
-      <c r="AJ10" t="n">
-        <v>887250</v>
-      </c>
-      <c r="AN10" t="n">
+      <c r="AO10" t="n">
         <v>758000</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>131750</v>
       </c>
     </row>
     <row r="11">
@@ -3777,13 +3639,13 @@
         <v>2816490</v>
       </c>
       <c r="C11" t="n">
-        <v>1409800</v>
+        <v>1379120</v>
       </c>
       <c r="D11" t="n">
-        <v>2824550</v>
+        <v>2766860</v>
       </c>
       <c r="E11" t="n">
-        <v>171510</v>
+        <v>170390</v>
       </c>
       <c r="F11" t="n">
         <v>1485190</v>
@@ -3792,7 +3654,7 @@
         <v>175190</v>
       </c>
       <c r="H11" t="n">
-        <v>92880</v>
+        <v>50620</v>
       </c>
       <c r="I11" t="n">
         <v>54330</v>
@@ -3801,7 +3663,7 @@
         <v>11840</v>
       </c>
       <c r="K11" t="n">
-        <v>9041780</v>
+        <v>8910030</v>
       </c>
       <c r="L11" t="n">
         <v>36690</v>
@@ -3848,37 +3710,22 @@
       <c r="AB11" t="n">
         <v>24990</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>own: NEPRA KE decision, no fuel split (counted as gas); IPP purchases: no figure</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE11" t="n">
         <v>463000</v>
       </c>
-      <c r="AD11" t="n">
-        <v>1120</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>57690</v>
-      </c>
       <c r="AF11" t="n">
-        <v>30680</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>42260</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>own: NEPRA KE decision (no fuel split); IPP purchases: ESTIMATE copied from 2024-04</t>
-        </is>
-      </c>
-      <c r="AI11" t="n">
         <v>943000</v>
       </c>
-      <c r="AJ11" t="n">
-        <v>811250</v>
-      </c>
-      <c r="AN11" t="n">
+      <c r="AO11" t="n">
         <v>463000</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>131750</v>
       </c>
     </row>
     <row r="12">
@@ -3889,13 +3736,13 @@
         <v>1768840</v>
       </c>
       <c r="C12" t="n">
-        <v>2134330</v>
+        <v>2103650</v>
       </c>
       <c r="D12" t="n">
-        <v>2766050</v>
+        <v>2708360</v>
       </c>
       <c r="E12" t="n">
-        <v>604940</v>
+        <v>603820</v>
       </c>
       <c r="F12" t="n">
         <v>1549060</v>
@@ -3904,7 +3751,7 @@
         <v>210080</v>
       </c>
       <c r="H12" t="n">
-        <v>87440</v>
+        <v>45180</v>
       </c>
       <c r="I12" t="n">
         <v>98470</v>
@@ -3913,7 +3760,7 @@
         <v>7880</v>
       </c>
       <c r="K12" t="n">
-        <v>9227090</v>
+        <v>9095340</v>
       </c>
       <c r="L12" t="n">
         <v>36470</v>
@@ -3960,37 +3807,22 @@
       <c r="AB12" t="n">
         <v>250560</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>own: NEPRA KE decision, no fuel split (counted as gas); IPP purchases: no figure</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE12" t="n">
         <v>301000</v>
       </c>
-      <c r="AD12" t="n">
-        <v>1120</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>57690</v>
-      </c>
       <c r="AF12" t="n">
-        <v>30680</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>42260</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>own: NEPRA KE decision (no fuel split); IPP purchases: ESTIMATE copied from 2024-04</t>
-        </is>
-      </c>
-      <c r="AI12" t="n">
         <v>871000</v>
       </c>
-      <c r="AJ12" t="n">
-        <v>739250</v>
-      </c>
-      <c r="AN12" t="n">
+      <c r="AO12" t="n">
         <v>301000</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>131750</v>
       </c>
     </row>
     <row r="13">
@@ -4001,13 +3833,13 @@
         <v>512930</v>
       </c>
       <c r="C13" t="n">
-        <v>2947380</v>
+        <v>2916700</v>
       </c>
       <c r="D13" t="n">
-        <v>2189130</v>
+        <v>2131440</v>
       </c>
       <c r="E13" t="n">
-        <v>1831200</v>
+        <v>1830080</v>
       </c>
       <c r="F13" t="n">
         <v>1264570</v>
@@ -4016,7 +3848,7 @@
         <v>194880</v>
       </c>
       <c r="H13" t="n">
-        <v>88840</v>
+        <v>46580</v>
       </c>
       <c r="I13" t="n">
         <v>107130</v>
@@ -4025,7 +3857,7 @@
         <v>2300</v>
       </c>
       <c r="K13" t="n">
-        <v>9138360</v>
+        <v>9006610</v>
       </c>
       <c r="L13" t="n">
         <v>31650</v>
@@ -4072,37 +3904,22 @@
       <c r="AB13" t="n">
         <v>592080</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>own: NEPRA KE decision, no fuel split (counted as gas); IPP purchases: no figure</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE13" t="n">
         <v>241000</v>
       </c>
-      <c r="AD13" t="n">
-        <v>1120</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>57690</v>
-      </c>
       <c r="AF13" t="n">
-        <v>30680</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>42260</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>own: NEPRA KE decision (no fuel split); IPP purchases: ESTIMATE copied from 2024-04</t>
-        </is>
-      </c>
-      <c r="AI13" t="n">
         <v>853000</v>
       </c>
-      <c r="AJ13" t="n">
-        <v>721250</v>
-      </c>
-      <c r="AN13" t="n">
+      <c r="AO13" t="n">
         <v>241000</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>131750</v>
       </c>
     </row>
     <row r="14">
@@ -4113,13 +3930,13 @@
         <v>1703910</v>
       </c>
       <c r="C14" t="n">
-        <v>2617300</v>
+        <v>2586620</v>
       </c>
       <c r="D14" t="n">
-        <v>3607090</v>
+        <v>3549400</v>
       </c>
       <c r="E14" t="n">
-        <v>1107310</v>
+        <v>1106190</v>
       </c>
       <c r="F14" t="n">
         <v>1563660</v>
@@ -4128,7 +3945,7 @@
         <v>267920</v>
       </c>
       <c r="H14" t="n">
-        <v>110990</v>
+        <v>68730</v>
       </c>
       <c r="I14" t="n">
         <v>107010</v>
@@ -4137,7 +3954,7 @@
         <v>13220</v>
       </c>
       <c r="K14" t="n">
-        <v>11098410</v>
+        <v>10966660</v>
       </c>
       <c r="L14" t="n">
         <v>42750</v>
@@ -4184,37 +4001,22 @@
       <c r="AB14" t="n">
         <v>0</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>own: NEPRA KE decision, no fuel split (counted as gas); IPP purchases: no figure</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE14" t="n">
         <v>591000</v>
       </c>
-      <c r="AD14" t="n">
-        <v>1120</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>57690</v>
-      </c>
       <c r="AF14" t="n">
-        <v>30680</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>42260</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>own: NEPRA KE decision (no fuel split); IPP purchases: ESTIMATE copied from 2024-04</t>
-        </is>
-      </c>
-      <c r="AI14" t="n">
         <v>1038000</v>
       </c>
-      <c r="AJ14" t="n">
-        <v>906250</v>
-      </c>
-      <c r="AN14" t="n">
+      <c r="AO14" t="n">
         <v>591000</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>131750</v>
       </c>
     </row>
     <row r="15">
@@ -4225,13 +4027,13 @@
         <v>2404350</v>
       </c>
       <c r="C15" t="n">
-        <v>2199610</v>
+        <v>2168930</v>
       </c>
       <c r="D15" t="n">
-        <v>4742110</v>
+        <v>4684420</v>
       </c>
       <c r="E15" t="n">
-        <v>1623720</v>
+        <v>1622600</v>
       </c>
       <c r="F15" t="n">
         <v>2251190</v>
@@ -4240,7 +4042,7 @@
         <v>464780</v>
       </c>
       <c r="H15" t="n">
-        <v>129570</v>
+        <v>87310</v>
       </c>
       <c r="I15" t="n">
         <v>106490</v>
@@ -4249,7 +4051,7 @@
         <v>9380</v>
       </c>
       <c r="K15" t="n">
-        <v>13931200</v>
+        <v>13799450</v>
       </c>
       <c r="L15" t="n">
         <v>51950</v>
@@ -4296,37 +4098,22 @@
       <c r="AB15" t="n">
         <v>58490</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>own: NEPRA KE decision, no fuel split (counted as gas); IPP purchases: no figure</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE15" t="n">
         <v>891000</v>
       </c>
-      <c r="AD15" t="n">
-        <v>1120</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>57690</v>
-      </c>
       <c r="AF15" t="n">
-        <v>30680</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>42260</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>own: NEPRA KE decision (no fuel split); IPP purchases: ESTIMATE copied from 2024-04</t>
-        </is>
-      </c>
-      <c r="AI15" t="n">
         <v>1035000</v>
       </c>
-      <c r="AJ15" t="n">
-        <v>903250</v>
-      </c>
-      <c r="AN15" t="n">
+      <c r="AO15" t="n">
         <v>891000</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>131750</v>
       </c>
     </row>
     <row r="16">
@@ -4337,13 +4124,13 @@
         <v>3590820</v>
       </c>
       <c r="C16" t="n">
-        <v>2049170</v>
+        <v>2018490</v>
       </c>
       <c r="D16" t="n">
-        <v>5760510</v>
+        <v>4819820</v>
       </c>
       <c r="E16" t="n">
-        <v>1319930</v>
+        <v>1318810</v>
       </c>
       <c r="F16" t="n">
         <v>1890380</v>
@@ -4352,7 +4139,7 @@
         <v>779130</v>
       </c>
       <c r="H16" t="n">
-        <v>132150</v>
+        <v>89890</v>
       </c>
       <c r="I16" t="n">
         <v>78260</v>
@@ -4361,7 +4148,7 @@
         <v>16770</v>
       </c>
       <c r="K16" t="n">
-        <v>15617120</v>
+        <v>14602370</v>
       </c>
       <c r="L16" t="n">
         <v>54520</v>
@@ -4408,31 +4195,13 @@
       <c r="AB16" t="n">
         <v>28480</v>
       </c>
-      <c r="AC16" t="n">
-        <v>883000</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1120</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>57690</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>30680</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>42260</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>own: ESTIMATE copied from 2023-05; IPP purchases: ESTIMATE copied from 2024-04</t>
-        </is>
-      </c>
-      <c r="AN16" t="n">
-        <v>883000</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>131750</v>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>no KE figure</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -4443,13 +4212,13 @@
         <v>3361210</v>
       </c>
       <c r="C17" t="n">
-        <v>1913810</v>
+        <v>1883130</v>
       </c>
       <c r="D17" t="n">
-        <v>5459865.1</v>
+        <v>5402175.1</v>
       </c>
       <c r="E17" t="n">
-        <v>1843774.9</v>
+        <v>1842654.9</v>
       </c>
       <c r="F17" t="n">
         <v>1265670</v>
@@ -4458,7 +4227,7 @@
         <v>811590</v>
       </c>
       <c r="H17" t="n">
-        <v>128530</v>
+        <v>86270</v>
       </c>
       <c r="I17" t="n">
         <v>83010</v>
@@ -4467,7 +4236,7 @@
         <v>9870</v>
       </c>
       <c r="K17" t="n">
-        <v>14877330</v>
+        <v>14745580</v>
       </c>
       <c r="L17" t="n">
         <v>51490</v>
@@ -4514,43 +4283,28 @@
       <c r="AB17" t="n">
         <v>0</v>
       </c>
-      <c r="AD17" t="n">
-        <v>1120</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>57690</v>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>own: NEPRA KE decision, by fuel from KE's filing; IPP purchases: no figure</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>1</v>
       </c>
       <c r="AF17" t="n">
-        <v>30680</v>
+        <v>1034000</v>
       </c>
       <c r="AG17" t="n">
-        <v>42260</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>own by fuel: KE filing; IPP purchases: ESTIMATE copied from 2024-04</t>
-        </is>
+        <v>388674.9</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>1034000</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>902250</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>388674.9</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM17" t="n">
         <v>532325.1</v>
       </c>
-      <c r="AN17" t="n">
+      <c r="AO17" t="n">
         <v>921000</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>131750</v>
       </c>
     </row>
     <row r="18">
@@ -4561,13 +4315,13 @@
         <v>4976930</v>
       </c>
       <c r="C18" t="n">
-        <v>1840760</v>
+        <v>1802190</v>
       </c>
       <c r="D18" t="n">
-        <v>4434570</v>
+        <v>4377960</v>
       </c>
       <c r="E18" t="n">
-        <v>1122090</v>
+        <v>1082890</v>
       </c>
       <c r="F18" t="n">
         <v>2009540</v>
@@ -4576,7 +4330,7 @@
         <v>521720</v>
       </c>
       <c r="H18" t="n">
-        <v>87970</v>
+        <v>70770</v>
       </c>
       <c r="I18" t="n">
         <v>40630</v>
@@ -4585,7 +4339,7 @@
         <v>16920</v>
       </c>
       <c r="K18" t="n">
-        <v>15051130</v>
+        <v>14899550</v>
       </c>
       <c r="L18" t="n">
         <v>46570</v>
@@ -4632,37 +4386,22 @@
       <c r="AB18" t="n">
         <v>205970</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>own: NEPRA KE decision, no fuel split (counted as gas); IPP purchases: no figure</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE18" t="n">
         <v>792000</v>
       </c>
-      <c r="AD18" t="n">
-        <v>39200</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>56610</v>
-      </c>
       <c r="AF18" t="n">
-        <v>38570</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>17200</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>own: NEPRA KE decision (no fuel split); IPP purchases: ESTIMATE copied from 2024-07</t>
-        </is>
-      </c>
-      <c r="AI18" t="n">
         <v>1006000</v>
       </c>
-      <c r="AJ18" t="n">
-        <v>854420</v>
-      </c>
-      <c r="AN18" t="n">
+      <c r="AO18" t="n">
         <v>792000</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>151580</v>
       </c>
     </row>
     <row r="19">
@@ -4673,13 +4412,13 @@
         <v>5353690</v>
       </c>
       <c r="C19" t="n">
-        <v>2193690</v>
+        <v>2163010</v>
       </c>
       <c r="D19" t="n">
-        <v>3798700</v>
+        <v>3741010</v>
       </c>
       <c r="E19" t="n">
-        <v>1022710</v>
+        <v>1021590</v>
       </c>
       <c r="F19" t="n">
         <v>1873980</v>
@@ -4688,7 +4427,7 @@
         <v>390710</v>
       </c>
       <c r="H19" t="n">
-        <v>115700</v>
+        <v>73440</v>
       </c>
       <c r="I19" t="n">
         <v>33130</v>
@@ -4697,7 +4436,7 @@
         <v>17780</v>
       </c>
       <c r="K19" t="n">
-        <v>14800090</v>
+        <v>14668340</v>
       </c>
       <c r="L19" t="n">
         <v>54470</v>
@@ -4744,37 +4483,22 @@
       <c r="AB19" t="n">
         <v>0</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>own: NEPRA KE decision, no fuel split (counted as gas); IPP purchases: no figure</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE19" t="n">
         <v>670000</v>
       </c>
-      <c r="AD19" t="n">
-        <v>1120</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>57690</v>
-      </c>
       <c r="AF19" t="n">
-        <v>30680</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>42260</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>own: NEPRA KE decision (no fuel split); IPP purchases: ESTIMATE copied from 2024-04</t>
-        </is>
-      </c>
-      <c r="AI19" t="n">
         <v>1044000</v>
       </c>
-      <c r="AJ19" t="n">
-        <v>912250</v>
-      </c>
-      <c r="AN19" t="n">
+      <c r="AO19" t="n">
         <v>670000</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>131750</v>
       </c>
     </row>
     <row r="20">
@@ -4785,13 +4509,13 @@
         <v>3143620</v>
       </c>
       <c r="C20" t="n">
-        <v>1687200</v>
+        <v>1656520</v>
       </c>
       <c r="D20" t="n">
-        <v>3860800</v>
+        <v>3803110</v>
       </c>
       <c r="E20" t="n">
-        <v>157690</v>
+        <v>156570</v>
       </c>
       <c r="F20" t="n">
         <v>2206330</v>
@@ -4800,7 +4524,7 @@
         <v>209700</v>
       </c>
       <c r="H20" t="n">
-        <v>121340</v>
+        <v>79080</v>
       </c>
       <c r="I20" t="n">
         <v>37810</v>
@@ -4809,7 +4533,7 @@
         <v>14770</v>
       </c>
       <c r="K20" t="n">
-        <v>11439260</v>
+        <v>11307510</v>
       </c>
       <c r="L20" t="n">
         <v>47770</v>
@@ -4856,37 +4580,22 @@
       <c r="AB20" t="n">
         <v>0</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>own: NEPRA KE decision, no fuel split (counted as gas); IPP purchases: no figure</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE20" t="n">
         <v>663000</v>
       </c>
-      <c r="AD20" t="n">
-        <v>1120</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>57690</v>
-      </c>
       <c r="AF20" t="n">
-        <v>30680</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>42260</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>own: NEPRA KE decision (no fuel split); IPP purchases: ESTIMATE copied from 2024-04</t>
-        </is>
-      </c>
-      <c r="AI20" t="n">
         <v>1013000</v>
       </c>
-      <c r="AJ20" t="n">
-        <v>881250</v>
-      </c>
-      <c r="AN20" t="n">
+      <c r="AO20" t="n">
         <v>663000</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>131750</v>
       </c>
     </row>
     <row r="21">
@@ -4897,13 +4606,13 @@
         <v>1720430</v>
       </c>
       <c r="C21" t="n">
-        <v>1551610</v>
+        <v>1520930</v>
       </c>
       <c r="D21" t="n">
-        <v>2816220</v>
+        <v>2758530</v>
       </c>
       <c r="E21" t="n">
-        <v>40030</v>
+        <v>38910</v>
       </c>
       <c r="F21" t="n">
         <v>2284860</v>
@@ -4912,7 +4621,7 @@
         <v>211570</v>
       </c>
       <c r="H21" t="n">
-        <v>111720</v>
+        <v>69460</v>
       </c>
       <c r="I21" t="n">
         <v>101090</v>
@@ -4921,7 +4630,7 @@
         <v>2180</v>
       </c>
       <c r="K21" t="n">
-        <v>8839710</v>
+        <v>8707960</v>
       </c>
       <c r="L21" t="n">
         <v>39850</v>
@@ -4968,37 +4677,22 @@
       <c r="AB21" t="n">
         <v>0</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>own: NEPRA KE decision, no fuel split (counted as gas); IPP purchases: no figure</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE21" t="n">
         <v>331000</v>
       </c>
-      <c r="AD21" t="n">
-        <v>1120</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>57690</v>
-      </c>
       <c r="AF21" t="n">
-        <v>30680</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>42260</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>own: NEPRA KE decision (no fuel split); IPP purchases: ESTIMATE copied from 2024-04</t>
-        </is>
-      </c>
-      <c r="AI21" t="n">
         <v>846000</v>
       </c>
-      <c r="AJ21" t="n">
-        <v>714250</v>
-      </c>
-      <c r="AN21" t="n">
+      <c r="AO21" t="n">
         <v>331000</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>131750</v>
       </c>
     </row>
     <row r="22">
@@ -5009,13 +4703,13 @@
         <v>800330</v>
       </c>
       <c r="C22" t="n">
-        <v>2474450</v>
+        <v>2443770</v>
       </c>
       <c r="D22" t="n">
-        <v>2730370</v>
+        <v>2431680</v>
       </c>
       <c r="E22" t="n">
-        <v>464440</v>
+        <v>463320</v>
       </c>
       <c r="F22" t="n">
         <v>1875650</v>
@@ -5024,7 +4718,7 @@
         <v>287210</v>
       </c>
       <c r="H22" t="n">
-        <v>114420</v>
+        <v>72160</v>
       </c>
       <c r="I22" t="n">
         <v>101440</v>
@@ -5033,7 +4727,7 @@
         <v>2150</v>
       </c>
       <c r="K22" t="n">
-        <v>8850460</v>
+        <v>8477710</v>
       </c>
       <c r="L22" t="n">
         <v>37130</v>
@@ -5080,31 +4774,13 @@
       <c r="AB22" t="n">
         <v>0</v>
       </c>
-      <c r="AC22" t="n">
-        <v>241000</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1120</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>57690</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>30680</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>42260</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>own: ESTIMATE copied from 2022-01; IPP purchases: ESTIMATE copied from 2024-04</t>
-        </is>
-      </c>
-      <c r="AN22" t="n">
-        <v>241000</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>131750</v>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>no KE figure</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -5115,13 +4791,13 @@
         <v>2052160</v>
       </c>
       <c r="C23" t="n">
-        <v>1121820</v>
+        <v>1091140</v>
       </c>
       <c r="D23" t="n">
-        <v>2665200</v>
+        <v>2607510</v>
       </c>
       <c r="E23" t="n">
-        <v>108890</v>
+        <v>107770</v>
       </c>
       <c r="F23" t="n">
         <v>1883090</v>
@@ -5130,7 +4806,7 @@
         <v>92200</v>
       </c>
       <c r="H23" t="n">
-        <v>124520</v>
+        <v>82260</v>
       </c>
       <c r="I23" t="n">
         <v>100120</v>
@@ -5139,7 +4815,7 @@
         <v>1870</v>
       </c>
       <c r="K23" t="n">
-        <v>8149870</v>
+        <v>8018120</v>
       </c>
       <c r="L23" t="n">
         <v>32950</v>
@@ -5186,37 +4862,22 @@
       <c r="AB23" t="n">
         <v>0</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>own: NEPRA KE decision, no fuel split (counted as gas); IPP purchases: no figure</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE23" t="n">
         <v>295000</v>
       </c>
-      <c r="AD23" t="n">
-        <v>1120</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>57690</v>
-      </c>
       <c r="AF23" t="n">
-        <v>30680</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>42260</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>own: NEPRA KE decision (no fuel split); IPP purchases: ESTIMATE copied from 2024-04</t>
-        </is>
-      </c>
-      <c r="AI23" t="n">
         <v>822000</v>
       </c>
-      <c r="AJ23" t="n">
-        <v>690250</v>
-      </c>
-      <c r="AN23" t="n">
+      <c r="AO23" t="n">
         <v>295000</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>131750</v>
       </c>
     </row>
     <row r="24">
@@ -5227,13 +4888,13 @@
         <v>2001610</v>
       </c>
       <c r="C24" t="n">
-        <v>1364200</v>
+        <v>1333520</v>
       </c>
       <c r="D24" t="n">
-        <v>3469290</v>
+        <v>3411600</v>
       </c>
       <c r="E24" t="n">
-        <v>41640</v>
+        <v>40520</v>
       </c>
       <c r="F24" t="n">
         <v>2002010</v>
@@ -5242,7 +4903,7 @@
         <v>221330</v>
       </c>
       <c r="H24" t="n">
-        <v>152990</v>
+        <v>110730</v>
       </c>
       <c r="I24" t="n">
         <v>104860</v>
@@ -5251,7 +4912,7 @@
         <v>3560</v>
       </c>
       <c r="K24" t="n">
-        <v>9361490</v>
+        <v>9229740</v>
       </c>
       <c r="L24" t="n">
         <v>31500</v>
@@ -5298,37 +4959,22 @@
       <c r="AB24" t="n">
         <v>0</v>
       </c>
-      <c r="AC24" t="n">
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>own: NEPRA KE decision, no fuel split (counted as gas); IPP purchases: no figure</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE24" t="n">
         <v>520000</v>
       </c>
-      <c r="AD24" t="n">
-        <v>1120</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>57690</v>
-      </c>
       <c r="AF24" t="n">
-        <v>30680</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>42260</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>own: NEPRA KE decision (no fuel split); IPP purchases: ESTIMATE copied from 2024-04</t>
-        </is>
-      </c>
-      <c r="AI24" t="n">
         <v>958000</v>
       </c>
-      <c r="AJ24" t="n">
-        <v>826250</v>
-      </c>
-      <c r="AN24" t="n">
+      <c r="AO24" t="n">
         <v>520000</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>131750</v>
       </c>
     </row>
     <row r="25">
@@ -5339,13 +4985,13 @@
         <v>1873190</v>
       </c>
       <c r="C25" t="n">
-        <v>1849410</v>
+        <v>1818730</v>
       </c>
       <c r="D25" t="n">
-        <v>4332730</v>
+        <v>4275040</v>
       </c>
       <c r="E25" t="n">
-        <v>223690</v>
+        <v>222570</v>
       </c>
       <c r="F25" t="n">
         <v>1916070</v>
@@ -5354,7 +5000,7 @@
         <v>322930</v>
       </c>
       <c r="H25" t="n">
-        <v>168060</v>
+        <v>125800</v>
       </c>
       <c r="I25" t="n">
         <v>81170</v>
@@ -5363,7 +5009,7 @@
         <v>13350</v>
       </c>
       <c r="K25" t="n">
-        <v>10780600</v>
+        <v>10648850</v>
       </c>
       <c r="L25" t="n">
         <v>30460</v>
@@ -5410,37 +5056,22 @@
       <c r="AB25" t="n">
         <v>0</v>
       </c>
-      <c r="AC25" t="n">
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>own: NEPRA KE decision, no fuel split (counted as gas); IPP purchases: no figure</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE25" t="n">
         <v>666000</v>
       </c>
-      <c r="AD25" t="n">
-        <v>1120</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>57690</v>
-      </c>
       <c r="AF25" t="n">
-        <v>30680</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>42260</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>own: NEPRA KE decision (no fuel split); IPP purchases: ESTIMATE copied from 2024-04</t>
-        </is>
-      </c>
-      <c r="AI25" t="n">
         <v>862000</v>
       </c>
-      <c r="AJ25" t="n">
-        <v>730250</v>
-      </c>
-      <c r="AN25" t="n">
+      <c r="AO25" t="n">
         <v>666000</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>131750</v>
       </c>
     </row>
     <row r="26">
@@ -5451,13 +5082,13 @@
         <v>3312200</v>
       </c>
       <c r="C26" t="n">
-        <v>2091980</v>
+        <v>2061300</v>
       </c>
       <c r="D26" t="n">
-        <v>5199640</v>
+        <v>5141950</v>
       </c>
       <c r="E26" t="n">
-        <v>242090</v>
+        <v>240970</v>
       </c>
       <c r="F26" t="n">
         <v>1542590</v>
@@ -5466,7 +5097,7 @@
         <v>606580</v>
       </c>
       <c r="H26" t="n">
-        <v>131760</v>
+        <v>89500</v>
       </c>
       <c r="I26" t="n">
         <v>74870</v>
@@ -5475,7 +5106,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>13201710</v>
+        <v>13069960</v>
       </c>
       <c r="L26" t="n">
         <v>34500</v>
@@ -5522,37 +5153,22 @@
       <c r="AB26" t="n">
         <v>0</v>
       </c>
-      <c r="AC26" t="n">
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>own: NEPRA KE decision, no fuel split (counted as gas); IPP purchases: no figure</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE26" t="n">
         <v>883000</v>
       </c>
-      <c r="AD26" t="n">
-        <v>1120</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>57690</v>
-      </c>
       <c r="AF26" t="n">
-        <v>30680</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>42260</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>own: NEPRA KE decision (no fuel split); IPP purchases: ESTIMATE copied from 2024-04</t>
-        </is>
-      </c>
-      <c r="AI26" t="n">
         <v>978000</v>
       </c>
-      <c r="AJ26" t="n">
-        <v>846250</v>
-      </c>
-      <c r="AN26" t="n">
+      <c r="AO26" t="n">
         <v>883000</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>131750</v>
       </c>
     </row>
     <row r="27">
@@ -5563,13 +5179,13 @@
         <v>4133450</v>
       </c>
       <c r="C27" t="n">
-        <v>2465110</v>
+        <v>2434430</v>
       </c>
       <c r="D27" t="n">
-        <v>4692520</v>
+        <v>3713830</v>
       </c>
       <c r="E27" t="n">
-        <v>755780</v>
+        <v>754660</v>
       </c>
       <c r="F27" t="n">
         <v>1857110</v>
@@ -5578,7 +5194,7 @@
         <v>597440</v>
       </c>
       <c r="H27" t="n">
-        <v>127780</v>
+        <v>85520</v>
       </c>
       <c r="I27" t="n">
         <v>66490</v>
@@ -5587,7 +5203,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>14695680</v>
+        <v>13642930</v>
       </c>
       <c r="L27" t="n">
         <v>24980</v>
@@ -5634,31 +5250,13 @@
       <c r="AB27" t="n">
         <v>10240</v>
       </c>
-      <c r="AC27" t="n">
-        <v>921000</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1120</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>57690</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>30680</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>42260</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>own: ESTIMATE copied from 2022-06; IPP purchases: ESTIMATE copied from 2024-04</t>
-        </is>
-      </c>
-      <c r="AN27" t="n">
-        <v>921000</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>131750</v>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>no KE figure</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -5669,13 +5267,13 @@
         <v>5517770</v>
       </c>
       <c r="C28" t="n">
-        <v>2218460</v>
+        <v>2179890</v>
       </c>
       <c r="D28" t="n">
-        <v>4895420</v>
+        <v>4046810</v>
       </c>
       <c r="E28" t="n">
-        <v>333006.7</v>
+        <v>293806.7</v>
       </c>
       <c r="F28" t="n">
         <v>2106930</v>
@@ -5684,7 +5282,7 @@
         <v>548760</v>
       </c>
       <c r="H28" t="n">
-        <v>92390</v>
+        <v>75190</v>
       </c>
       <c r="I28" t="n">
         <v>39970</v>
@@ -5693,7 +5291,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>15752706.7</v>
+        <v>14809126.7</v>
       </c>
       <c r="L28" t="n">
         <v>28850</v>
@@ -5740,31 +5338,13 @@
       <c r="AB28" t="n">
         <v>0</v>
       </c>
-      <c r="AC28" t="n">
-        <v>792000</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>39200</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>56610</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>38570</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>17200</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>own: ESTIMATE copied from 2022-07; IPP purchases: ESTIMATE copied from 2024-07</t>
-        </is>
-      </c>
-      <c r="AN28" t="n">
-        <v>792000</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>151580</v>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>no KE figure</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -5775,13 +5355,13 @@
         <v>6005500</v>
       </c>
       <c r="C29" t="n">
-        <v>2387910</v>
+        <v>2357230</v>
       </c>
       <c r="D29" t="n">
-        <v>4681890</v>
+        <v>3954200</v>
       </c>
       <c r="E29" t="n">
-        <v>650280</v>
+        <v>649160</v>
       </c>
       <c r="F29" t="n">
         <v>2040450</v>
@@ -5790,7 +5370,7 @@
         <v>804700</v>
       </c>
       <c r="H29" t="n">
-        <v>126330</v>
+        <v>84070</v>
       </c>
       <c r="I29" t="n">
         <v>37760</v>
@@ -5799,7 +5379,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>16734820</v>
+        <v>15933070</v>
       </c>
       <c r="L29" t="n">
         <v>26200</v>
@@ -5852,31 +5432,13 @@
       <c r="AB29" t="n">
         <v>0</v>
       </c>
-      <c r="AC29" t="n">
-        <v>670000</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1120</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>57690</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>30680</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>42260</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>own: ESTIMATE copied from 2022-08; IPP purchases: ESTIMATE copied from 2024-04</t>
-        </is>
-      </c>
-      <c r="AN29" t="n">
-        <v>670000</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>131750</v>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>no KE figure</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -5887,13 +5449,13 @@
         <v>5008520</v>
       </c>
       <c r="C30" t="n">
-        <v>2157880</v>
+        <v>2122860</v>
       </c>
       <c r="D30" t="n">
-        <v>3847410</v>
+        <v>3133080</v>
       </c>
       <c r="E30" t="n">
-        <v>251360</v>
+        <v>240610</v>
       </c>
       <c r="F30" t="n">
         <v>2286350</v>
@@ -5902,7 +5464,7 @@
         <v>410230</v>
       </c>
       <c r="H30" t="n">
-        <v>100050</v>
+        <v>78790</v>
       </c>
       <c r="I30" t="n">
         <v>34520</v>
@@ -5911,7 +5473,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>14096320</v>
+        <v>13314960</v>
       </c>
       <c r="L30" t="n">
         <v>24230</v>
@@ -5964,31 +5526,13 @@
       <c r="AB30" t="n">
         <v>0</v>
       </c>
-      <c r="AC30" t="n">
-        <v>664000</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>10750</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>50330</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>35020</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>21260</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>own: ESTIMATE copied from 2022-09; IPP purchases: ESTIMATE copied from 2024-09</t>
-        </is>
-      </c>
-      <c r="AN30" t="n">
-        <v>664000</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>117360</v>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>no KE figure</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -5999,13 +5543,13 @@
         <v>3114140</v>
       </c>
       <c r="C31" t="n">
-        <v>1700850</v>
+        <v>1670170</v>
       </c>
       <c r="D31" t="n">
-        <v>3363180</v>
+        <v>2642490</v>
       </c>
       <c r="E31" t="n">
-        <v>1190</v>
+        <v>70</v>
       </c>
       <c r="F31" t="n">
         <v>1826260</v>
@@ -6014,7 +5558,7 @@
         <v>191140</v>
       </c>
       <c r="H31" t="n">
-        <v>118260</v>
+        <v>76000</v>
       </c>
       <c r="I31" t="n">
         <v>28760</v>
@@ -6023,7 +5567,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>10343780</v>
+        <v>9549030</v>
       </c>
       <c r="L31" t="n">
         <v>22540</v>
@@ -6076,31 +5620,13 @@
       <c r="AB31" t="n">
         <v>0</v>
       </c>
-      <c r="AC31" t="n">
-        <v>663000</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1120</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>57690</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>30680</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>42260</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>own: ESTIMATE copied from 2022-10; IPP purchases: ESTIMATE copied from 2024-04</t>
-        </is>
-      </c>
-      <c r="AN31" t="n">
-        <v>663000</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>131750</v>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>no KE figure</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -6111,13 +5637,13 @@
         <v>2754860</v>
       </c>
       <c r="C32" t="n">
-        <v>1503800</v>
+        <v>1473120</v>
       </c>
       <c r="D32" t="n">
-        <v>2013450</v>
+        <v>1492760</v>
       </c>
       <c r="E32" t="n">
-        <v>1400</v>
+        <v>280</v>
       </c>
       <c r="F32" t="n">
         <v>1571660</v>
@@ -6126,7 +5652,7 @@
         <v>147840</v>
       </c>
       <c r="H32" t="n">
-        <v>92040</v>
+        <v>49780</v>
       </c>
       <c r="I32" t="n">
         <v>26680</v>
@@ -6135,7 +5661,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>8111730</v>
+        <v>7516980</v>
       </c>
       <c r="L32" t="n">
         <v>29730</v>
@@ -6188,31 +5714,13 @@
       <c r="AB32" t="n">
         <v>0</v>
       </c>
-      <c r="AC32" t="n">
-        <v>463000</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1120</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>57690</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>30680</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>42260</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>own: ESTIMATE copied from 2021-11; IPP purchases: ESTIMATE copied from 2024-04</t>
-        </is>
-      </c>
-      <c r="AN32" t="n">
-        <v>463000</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>131750</v>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>no KE figure</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -6223,13 +5731,13 @@
         <v>1859010</v>
       </c>
       <c r="C33" t="n">
-        <v>1723860</v>
+        <v>1693180</v>
       </c>
       <c r="D33" t="n">
-        <v>2482590</v>
+        <v>2093900</v>
       </c>
       <c r="E33" t="n">
-        <v>175650</v>
+        <v>174530</v>
       </c>
       <c r="F33" t="n">
         <v>1464430</v>
@@ -6238,7 +5746,7 @@
         <v>150370</v>
       </c>
       <c r="H33" t="n">
-        <v>104080</v>
+        <v>61820</v>
       </c>
       <c r="I33" t="n">
         <v>101240</v>
@@ -6247,7 +5755,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>8061230</v>
+        <v>7598480</v>
       </c>
       <c r="L33" t="n">
         <v>28200</v>
@@ -6300,31 +5808,13 @@
       <c r="AB33" t="n">
         <v>6310</v>
       </c>
-      <c r="AC33" t="n">
-        <v>331000</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1120</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>57690</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>30680</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>42260</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>own: ESTIMATE copied from 2022-12; IPP purchases: ESTIMATE copied from 2024-04</t>
-        </is>
-      </c>
-      <c r="AN33" t="n">
-        <v>331000</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>131750</v>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>no KE figure</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -6335,13 +5825,13 @@
         <v>924220</v>
       </c>
       <c r="C34" t="n">
-        <v>1979610</v>
+        <v>1948930</v>
       </c>
       <c r="D34" t="n">
-        <v>2848440</v>
+        <v>2549750</v>
       </c>
       <c r="E34" t="n">
-        <v>853210</v>
+        <v>852090</v>
       </c>
       <c r="F34" t="n">
         <v>1727800</v>
@@ -6350,7 +5840,7 @@
         <v>127550</v>
       </c>
       <c r="H34" t="n">
-        <v>90200</v>
+        <v>47940</v>
       </c>
       <c r="I34" t="n">
         <v>106370</v>
@@ -6359,7 +5849,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>8657400</v>
+        <v>8284650</v>
       </c>
       <c r="L34" t="n">
         <v>29090</v>
@@ -6412,31 +5902,13 @@
       <c r="AB34" t="n">
         <v>101670</v>
       </c>
-      <c r="AC34" t="n">
-        <v>241000</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1120</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>57690</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>30680</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>42260</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>own: ESTIMATE copied from 2022-01; IPP purchases: ESTIMATE copied from 2024-04</t>
-        </is>
-      </c>
-      <c r="AN34" t="n">
-        <v>241000</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>131750</v>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>no KE figure</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -6447,13 +5919,13 @@
         <v>1766290</v>
       </c>
       <c r="C35" t="n">
-        <v>1159390</v>
+        <v>1128710</v>
       </c>
       <c r="D35" t="n">
-        <v>2589510</v>
+        <v>2236820</v>
       </c>
       <c r="E35" t="n">
-        <v>1120</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
         <v>1660250</v>
@@ -6462,7 +5934,7 @@
         <v>107633.5</v>
       </c>
       <c r="H35" t="n">
-        <v>132430</v>
+        <v>90170</v>
       </c>
       <c r="I35" t="n">
         <v>100530</v>
@@ -6471,7 +5943,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>7517153.5</v>
+        <v>7090403.5</v>
       </c>
       <c r="L35" t="n">
         <v>25660</v>
@@ -6521,31 +5993,13 @@
       <c r="AA35" t="n">
         <v>0</v>
       </c>
-      <c r="AC35" t="n">
-        <v>295000</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1120</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>57690</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>30680</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>42260</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>own: ESTIMATE copied from 2023-02; IPP purchases: ESTIMATE copied from 2024-04</t>
-        </is>
-      </c>
-      <c r="AN35" t="n">
-        <v>295000</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>131750</v>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>no KE figure</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -6556,13 +6010,13 @@
         <v>2216810</v>
       </c>
       <c r="C36" t="n">
-        <v>892450</v>
+        <v>861770</v>
       </c>
       <c r="D36" t="n">
-        <v>3031210</v>
+        <v>2453520</v>
       </c>
       <c r="E36" t="n">
-        <v>1120</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
         <v>2069600</v>
@@ -6571,7 +6025,7 @@
         <v>204700</v>
       </c>
       <c r="H36" t="n">
-        <v>152240</v>
+        <v>109980</v>
       </c>
       <c r="I36" t="n">
         <v>78500</v>
@@ -6580,7 +6034,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>8646630</v>
+        <v>7994880</v>
       </c>
       <c r="L36" t="n">
         <v>28380</v>
@@ -6633,31 +6087,13 @@
       <c r="AB36" t="n">
         <v>0</v>
       </c>
-      <c r="AC36" t="n">
-        <v>520000</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1120</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>57690</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>30680</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>42260</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>own: ESTIMATE copied from 2023-03; IPP purchases: ESTIMATE copied from 2024-04</t>
-        </is>
-      </c>
-      <c r="AN36" t="n">
-        <v>520000</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>131750</v>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>no KE figure</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -6668,13 +6104,13 @@
         <v>3906270</v>
       </c>
       <c r="C37" t="n">
-        <v>1784950</v>
+        <v>1754270</v>
       </c>
       <c r="D37" t="n">
-        <v>4803320</v>
+        <v>4745630</v>
       </c>
       <c r="E37" t="n">
-        <v>63060</v>
+        <v>61940</v>
       </c>
       <c r="F37" t="n">
         <v>2360020</v>
@@ -6683,7 +6119,7 @@
         <v>445440</v>
       </c>
       <c r="H37" t="n">
-        <v>167130</v>
+        <v>124870</v>
       </c>
       <c r="I37" t="n">
         <v>56940</v>
@@ -6692,7 +6128,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>13587130</v>
+        <v>13455380</v>
       </c>
       <c r="L37" t="n">
         <v>49960</v>
@@ -6745,37 +6181,22 @@
       <c r="AB37" t="n">
         <v>0</v>
       </c>
-      <c r="AC37" t="n">
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>own: NEPRA KE decision, no fuel split (counted as gas); IPP purchases: no figure</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE37" t="n">
         <v>889000</v>
       </c>
-      <c r="AD37" t="n">
-        <v>1120</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>57690</v>
-      </c>
       <c r="AF37" t="n">
-        <v>30680</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>42260</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>own: NEPRA KE decision (no fuel split); IPP purchases: ESTIMATE copied from 2024-04</t>
-        </is>
-      </c>
-      <c r="AI37" t="n">
         <v>951000</v>
       </c>
-      <c r="AJ37" t="n">
-        <v>819250</v>
-      </c>
-      <c r="AN37" t="n">
+      <c r="AO37" t="n">
         <v>889000</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>131750</v>
       </c>
     </row>
     <row r="38">
@@ -6786,13 +6207,13 @@
         <v>4728500</v>
       </c>
       <c r="C38" t="n">
-        <v>2164640</v>
+        <v>2126070</v>
       </c>
       <c r="D38" t="n">
-        <v>4615840</v>
+        <v>4559230</v>
       </c>
       <c r="E38" t="n">
-        <v>302160</v>
+        <v>262960</v>
       </c>
       <c r="F38" t="n">
         <v>1998390</v>
@@ -6801,7 +6222,7 @@
         <v>515730</v>
       </c>
       <c r="H38" t="n">
-        <v>134740</v>
+        <v>117540</v>
       </c>
       <c r="I38" t="n">
         <v>59740</v>
@@ -6810,7 +6231,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>14519740</v>
+        <v>14368160</v>
       </c>
       <c r="L38" t="n">
         <v>47650</v>
@@ -6863,37 +6284,22 @@
       <c r="AB38" t="n">
         <v>0</v>
       </c>
-      <c r="AC38" t="n">
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>own: NEPRA KE decision, no fuel split (counted as gas); IPP purchases: no figure</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE38" t="n">
         <v>956000</v>
       </c>
-      <c r="AD38" t="n">
-        <v>39200</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>56610</v>
-      </c>
       <c r="AF38" t="n">
-        <v>38570</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>17200</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>own: NEPRA KE decision (no fuel split); IPP purchases: ESTIMATE copied from 2024-07</t>
-        </is>
-      </c>
-      <c r="AI38" t="n">
         <v>887000</v>
       </c>
-      <c r="AJ38" t="n">
-        <v>735420</v>
-      </c>
-      <c r="AN38" t="n">
+      <c r="AO38" t="n">
         <v>956000</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>151580</v>
       </c>
     </row>
     <row r="39">
@@ -6981,42 +6387,45 @@
       <c r="AB39" t="n">
         <v>0</v>
       </c>
-      <c r="AD39" t="n">
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>own: NEPRA KE decision, by fuel from KE's filing; IPP purchases by fuel: KE's filing</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>935000</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>147844.7</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>41536.9</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>886618.3</v>
+      </c>
+      <c r="AJ39" t="n">
         <v>39200</v>
       </c>
-      <c r="AE39" t="n">
+      <c r="AK39" t="n">
         <v>56610</v>
       </c>
-      <c r="AF39" t="n">
+      <c r="AL39" t="n">
         <v>38570</v>
       </c>
-      <c r="AG39" t="n">
+      <c r="AM39" t="n">
         <v>17200</v>
       </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>own by fuel: KE filing; IPP purchases: KE filing</t>
-        </is>
-      </c>
-      <c r="AI39" t="n">
-        <v>935000</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>783420</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>147844.7</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>41536.9</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>886618.3</v>
-      </c>
       <c r="AN39" t="n">
+        <v>783380</v>
+      </c>
+      <c r="AO39" t="n">
         <v>1075999.9</v>
       </c>
-      <c r="AO39" t="n">
+      <c r="AP39" t="n">
         <v>151580</v>
       </c>
     </row>
@@ -7028,13 +6437,13 @@
         <v>5361562.6</v>
       </c>
       <c r="C40" t="n">
-        <v>2021372.9</v>
+        <v>1986352.9</v>
       </c>
       <c r="D40" t="n">
-        <v>3912230.8</v>
+        <v>3861900.8</v>
       </c>
       <c r="E40" t="n">
-        <v>16413.2</v>
+        <v>5663.2</v>
       </c>
       <c r="F40" t="n">
         <v>2190305</v>
@@ -7043,7 +6452,7 @@
         <v>398253.9</v>
       </c>
       <c r="H40" t="n">
-        <v>119633.3</v>
+        <v>98373.3</v>
       </c>
       <c r="I40" t="n">
         <v>46709.4</v>
@@ -7052,7 +6461,7 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>14066481.1</v>
+        <v>13949121.1</v>
       </c>
       <c r="L40" t="n">
         <v>35774.1</v>
@@ -7105,37 +6514,22 @@
       <c r="AB40" t="n">
         <v>0</v>
       </c>
-      <c r="AC40" t="n">
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>own: NEPRA KE decision, no fuel split (counted as gas); IPP purchases: no figure</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE40" t="n">
         <v>806000</v>
       </c>
-      <c r="AD40" t="n">
-        <v>10750</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>50330</v>
-      </c>
       <c r="AF40" t="n">
-        <v>35020</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>21260</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>own: NEPRA KE decision (no fuel split); IPP purchases: ESTIMATE copied from 2024-09</t>
-        </is>
-      </c>
-      <c r="AI40" t="n">
         <v>874000</v>
       </c>
-      <c r="AJ40" t="n">
-        <v>756640</v>
-      </c>
-      <c r="AN40" t="n">
+      <c r="AO40" t="n">
         <v>806000</v>
-      </c>
-      <c r="AO40" t="n">
-        <v>117360</v>
       </c>
     </row>
     <row r="41">
@@ -7223,42 +6617,45 @@
       <c r="AB41" t="n">
         <v>0</v>
       </c>
-      <c r="AD41" t="n">
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>own: NEPRA KE decision, by fuel from KE's filing; IPP purchases by fuel: KE's filing</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>851000</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>27606.9</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>27857</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>664536.1</v>
+      </c>
+      <c r="AJ41" t="n">
         <v>10750</v>
       </c>
-      <c r="AE41" t="n">
+      <c r="AK41" t="n">
         <v>50330</v>
       </c>
-      <c r="AF41" t="n">
+      <c r="AL41" t="n">
         <v>35020</v>
       </c>
-      <c r="AG41" t="n">
+      <c r="AM41" t="n">
         <v>21260</v>
       </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>own by fuel: KE filing; IPP purchases: KE filing</t>
-        </is>
-      </c>
-      <c r="AI41" t="n">
-        <v>851000</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>733640</v>
-      </c>
-      <c r="AK41" t="n">
-        <v>27606.9</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>27857</v>
-      </c>
-      <c r="AM41" t="n">
-        <v>664536.1</v>
-      </c>
       <c r="AN41" t="n">
+        <v>733650</v>
+      </c>
+      <c r="AO41" t="n">
         <v>720000</v>
       </c>
-      <c r="AO41" t="n">
+      <c r="AP41" t="n">
         <v>117360</v>
       </c>
     </row>
@@ -7270,13 +6667,13 @@
         <v>3187387</v>
       </c>
       <c r="C42" t="n">
-        <v>2455814.4</v>
+        <v>2420794.4</v>
       </c>
       <c r="D42" t="n">
-        <v>3668293.1</v>
+        <v>3617963.1</v>
       </c>
       <c r="E42" t="n">
-        <v>25341.6</v>
+        <v>14591.6</v>
       </c>
       <c r="F42" t="n">
         <v>1441938</v>
@@ -7285,7 +6682,7 @@
         <v>189980.9</v>
       </c>
       <c r="H42" t="n">
-        <v>120326.7</v>
+        <v>99066.7</v>
       </c>
       <c r="I42" t="n">
         <v>50265.4</v>
@@ -7294,7 +6691,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>11139347.1</v>
+        <v>11021987.1</v>
       </c>
       <c r="L42" t="n">
         <v>42382.8</v>
@@ -7347,43 +6744,28 @@
       <c r="AB42" t="n">
         <v>0</v>
       </c>
-      <c r="AD42" t="n">
-        <v>10750</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>50330</v>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>own: NEPRA KE decision, by fuel from KE's filing; IPP purchases: no figure</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>1</v>
       </c>
       <c r="AF42" t="n">
-        <v>35020</v>
+        <v>912000</v>
       </c>
       <c r="AG42" t="n">
-        <v>21260</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>own by fuel: KE filing; IPP purchases: ESTIMATE copied from 2024-09</t>
-        </is>
+        <v>12591.7</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>24842.7</v>
       </c>
       <c r="AI42" t="n">
-        <v>912000</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>794640</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>12591.7</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>24842.7</v>
-      </c>
-      <c r="AM42" t="n">
         <v>764565.6</v>
       </c>
-      <c r="AN42" t="n">
+      <c r="AO42" t="n">
         <v>802000</v>
-      </c>
-      <c r="AO42" t="n">
-        <v>117360</v>
       </c>
     </row>
     <row r="43">
@@ -7394,13 +6776,13 @@
         <v>2859994</v>
       </c>
       <c r="C43" t="n">
-        <v>1530669.2</v>
+        <v>1495649.2</v>
       </c>
       <c r="D43" t="n">
-        <v>2277865</v>
+        <v>1764535</v>
       </c>
       <c r="E43" t="n">
-        <v>10750.1</v>
+        <v>0.1</v>
       </c>
       <c r="F43" t="n">
         <v>1655204</v>
@@ -7409,7 +6791,7 @@
         <v>98003.60000000001</v>
       </c>
       <c r="H43" t="n">
-        <v>90344.10000000001</v>
+        <v>69084.10000000001</v>
       </c>
       <c r="I43" t="n">
         <v>52226.4</v>
@@ -7418,7 +6800,7 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>8575056.4</v>
+        <v>7994696.4</v>
       </c>
       <c r="L43" t="n">
         <v>36803.8</v>
@@ -7471,31 +6853,13 @@
       <c r="AB43" t="n">
         <v>0</v>
       </c>
-      <c r="AC43" t="n">
-        <v>463000</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>10750</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>50330</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>35020</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>21260</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>own: ESTIMATE copied from 2021-11; IPP purchases: ESTIMATE copied from 2024-09</t>
-        </is>
-      </c>
-      <c r="AN43" t="n">
-        <v>463000</v>
-      </c>
-      <c r="AO43" t="n">
-        <v>117360</v>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>no KE figure</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -7506,13 +6870,13 @@
         <v>1778280.7</v>
       </c>
       <c r="C44" t="n">
-        <v>942935.2</v>
+        <v>907915.2</v>
       </c>
       <c r="D44" t="n">
-        <v>2955824.9</v>
+        <v>2574494.9</v>
       </c>
       <c r="E44" t="n">
-        <v>13386.7</v>
+        <v>2636.7</v>
       </c>
       <c r="F44" t="n">
         <v>2065100</v>
@@ -7521,7 +6885,7 @@
         <v>261623.8</v>
       </c>
       <c r="H44" t="n">
-        <v>97076.10000000001</v>
+        <v>75816.10000000001</v>
       </c>
       <c r="I44" t="n">
         <v>101065.6</v>
@@ -7530,7 +6894,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>8215293</v>
+        <v>7766933</v>
       </c>
       <c r="L44" t="n">
         <v>32757.1</v>
@@ -7583,31 +6947,13 @@
       <c r="AB44" t="n">
         <v>0</v>
       </c>
-      <c r="AC44" t="n">
-        <v>331000</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>10750</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>50330</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>35020</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>21260</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>own: ESTIMATE copied from 2022-12; IPP purchases: ESTIMATE copied from 2024-09</t>
-        </is>
-      </c>
-      <c r="AN44" t="n">
-        <v>331000</v>
-      </c>
-      <c r="AO44" t="n">
-        <v>117360</v>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>no KE figure</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -7618,13 +6964,13 @@
         <v>866385.6</v>
       </c>
       <c r="C45" t="n">
-        <v>1999138.6</v>
+        <v>1964118.6</v>
       </c>
       <c r="D45" t="n">
-        <v>2902667.2</v>
+        <v>2611337.2</v>
       </c>
       <c r="E45" t="n">
-        <v>119869</v>
+        <v>109119</v>
       </c>
       <c r="F45" t="n">
         <v>2169373</v>
@@ -7633,7 +6979,7 @@
         <v>218039.4</v>
       </c>
       <c r="H45" t="n">
-        <v>107284.6</v>
+        <v>86024.60000000001</v>
       </c>
       <c r="I45" t="n">
         <v>95296</v>
@@ -7642,7 +6988,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>8478053.4</v>
+        <v>8119693.4</v>
       </c>
       <c r="L45" t="n">
         <v>33585.9</v>
@@ -7695,31 +7041,13 @@
       <c r="AB45" t="n">
         <v>0</v>
       </c>
-      <c r="AC45" t="n">
-        <v>241000</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>10750</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>50330</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>35020</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>21260</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>own: ESTIMATE copied from 2022-01; IPP purchases: ESTIMATE copied from 2024-09</t>
-        </is>
-      </c>
-      <c r="AN45" t="n">
-        <v>241000</v>
-      </c>
-      <c r="AO45" t="n">
-        <v>117360</v>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>no KE figure</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -7730,13 +7058,13 @@
         <v>1883386.6</v>
       </c>
       <c r="C46" t="n">
-        <v>1186582.2</v>
+        <v>1151562.2</v>
       </c>
       <c r="D46" t="n">
-        <v>2042064.8</v>
+        <v>1696734.8</v>
       </c>
       <c r="E46" t="n">
-        <v>10750</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
         <v>1846937</v>
@@ -7745,7 +7073,7 @@
         <v>173537.5</v>
       </c>
       <c r="H46" t="n">
-        <v>105975.4</v>
+        <v>84715.39999999999</v>
       </c>
       <c r="I46" t="n">
         <v>78883.8</v>
@@ -7754,7 +7082,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>7328117.3</v>
+        <v>6915757.3</v>
       </c>
       <c r="L46" t="n">
         <v>29631.8</v>
@@ -7807,31 +7135,13 @@
       <c r="AB46" t="n">
         <v>0</v>
       </c>
-      <c r="AC46" t="n">
-        <v>295000</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>10750</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>50330</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>35020</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>21260</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>own: ESTIMATE copied from 2023-02; IPP purchases: ESTIMATE copied from 2024-09</t>
-        </is>
-      </c>
-      <c r="AN46" t="n">
-        <v>295000</v>
-      </c>
-      <c r="AO46" t="n">
-        <v>117360</v>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>no KE figure</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -7842,13 +7152,13 @@
         <v>1296770.4</v>
       </c>
       <c r="C47" t="n">
-        <v>1972962.2</v>
+        <v>1937942.2</v>
       </c>
       <c r="D47" t="n">
-        <v>3077084.6</v>
+        <v>2506754.6</v>
       </c>
       <c r="E47" t="n">
-        <v>14371.3</v>
+        <v>3621.3</v>
       </c>
       <c r="F47" t="n">
         <v>2222792</v>
@@ -7857,7 +7167,7 @@
         <v>230496</v>
       </c>
       <c r="H47" t="n">
-        <v>141201.6</v>
+        <v>119941.6</v>
       </c>
       <c r="I47" t="n">
         <v>51326.3</v>
@@ -7866,7 +7176,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>9007004.4</v>
+        <v>8369644.4</v>
       </c>
       <c r="L47" t="n">
         <v>39283.9</v>
@@ -7919,31 +7229,13 @@
       <c r="AB47" t="n">
         <v>0</v>
       </c>
-      <c r="AC47" t="n">
-        <v>520000</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>10750</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>50330</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>35020</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>21260</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>own: ESTIMATE copied from 2023-03; IPP purchases: ESTIMATE copied from 2024-09</t>
-        </is>
-      </c>
-      <c r="AN47" t="n">
-        <v>520000</v>
-      </c>
-      <c r="AO47" t="n">
-        <v>117360</v>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>no KE figure</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -7954,13 +7246,13 @@
         <v>2306427.4</v>
       </c>
       <c r="C48" t="n">
-        <v>2609588.8</v>
+        <v>2578908.8</v>
       </c>
       <c r="D48" t="n">
-        <v>3637548</v>
+        <v>2998858</v>
       </c>
       <c r="E48" t="n">
-        <v>84583.5</v>
+        <v>83463.5</v>
       </c>
       <c r="F48" t="n">
         <v>1882431</v>
@@ -7969,7 +7261,7 @@
         <v>478378.1</v>
       </c>
       <c r="H48" t="n">
-        <v>157638.3</v>
+        <v>115378.3</v>
       </c>
       <c r="I48" t="n">
         <v>36912.8</v>
@@ -7978,7 +7270,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>11193507.9</v>
+        <v>10480757.9</v>
       </c>
       <c r="L48" t="n">
         <v>32458.7</v>
@@ -8031,31 +7323,13 @@
       <c r="AB48" t="n">
         <v>0</v>
       </c>
-      <c r="AC48" t="n">
-        <v>581000</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>1120</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>57690</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>30680</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>42260</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>own: ESTIMATE copied from 2024-04; IPP purchases: ESTIMATE copied from 2024-04</t>
-        </is>
-      </c>
-      <c r="AN48" t="n">
-        <v>581000</v>
-      </c>
-      <c r="AO48" t="n">
-        <v>131750</v>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>no KE figure</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -8066,13 +7340,13 @@
         <v>4843855</v>
       </c>
       <c r="C49" t="n">
-        <v>2244692.4</v>
+        <v>2209672.4</v>
       </c>
       <c r="D49" t="n">
-        <v>3990014.5</v>
+        <v>3050684.5</v>
       </c>
       <c r="E49" t="n">
-        <v>30831.3</v>
+        <v>20081.3</v>
       </c>
       <c r="F49" t="n">
         <v>2011778</v>
@@ -8081,7 +7355,7 @@
         <v>432581.8</v>
       </c>
       <c r="H49" t="n">
-        <v>137278.4</v>
+        <v>116018.4</v>
       </c>
       <c r="I49" t="n">
         <v>33750.7</v>
@@ -8090,7 +7364,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>13724782.1</v>
+        <v>12718422.1</v>
       </c>
       <c r="L49" t="n">
         <v>36189.3</v>
@@ -8143,31 +7417,13 @@
       <c r="AB49" t="n">
         <v>0</v>
       </c>
-      <c r="AC49" t="n">
-        <v>889000</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>10750</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>50330</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>35020</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>21260</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>own: ESTIMATE copied from 2024-05; IPP purchases: ESTIMATE copied from 2024-09</t>
-        </is>
-      </c>
-      <c r="AN49" t="n">
-        <v>889000</v>
-      </c>
-      <c r="AO49" t="n">
-        <v>117360</v>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>no KE figure</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -8178,13 +7434,13 @@
         <v>5409725.5</v>
       </c>
       <c r="C50" t="n">
-        <v>2941835.6</v>
+        <v>2906815.6</v>
       </c>
       <c r="D50" t="n">
-        <v>4190086.2</v>
+        <v>3183756.2</v>
       </c>
       <c r="E50" t="n">
-        <v>161833.3</v>
+        <v>151083.3</v>
       </c>
       <c r="F50" t="n">
         <v>1382836</v>
@@ -8193,7 +7449,7 @@
         <v>522015.7</v>
       </c>
       <c r="H50" t="n">
-        <v>127503.8</v>
+        <v>106243.8</v>
       </c>
       <c r="I50" t="n">
         <v>34963.2</v>
@@ -8202,7 +7458,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>14770799.3</v>
+        <v>13697439.3</v>
       </c>
       <c r="L50" t="n">
         <v>46992.7</v>
@@ -8255,31 +7511,13 @@
       <c r="AB50" t="n">
         <v>0</v>
       </c>
-      <c r="AC50" t="n">
-        <v>956000</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>10750</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>50330</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>35020</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>21260</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>own: ESTIMATE copied from 2024-06; IPP purchases: ESTIMATE copied from 2024-09</t>
-        </is>
-      </c>
-      <c r="AN50" t="n">
-        <v>956000</v>
-      </c>
-      <c r="AO50" t="n">
-        <v>117360</v>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>no KE figure</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -8290,13 +7528,13 @@
         <v>5668138.4</v>
       </c>
       <c r="C51" t="n">
-        <v>2680679.7</v>
+        <v>2642109.7</v>
       </c>
       <c r="D51" t="n">
-        <v>4663474</v>
+        <v>3530864</v>
       </c>
       <c r="E51" t="n">
-        <v>147605.8</v>
+        <v>108405.8</v>
       </c>
       <c r="F51" t="n">
         <v>1405452</v>
@@ -8305,7 +7543,7 @@
         <v>591921.8</v>
       </c>
       <c r="H51" t="n">
-        <v>122181.3</v>
+        <v>104981.3</v>
       </c>
       <c r="I51" t="n">
         <v>35253.9</v>
@@ -8314,7 +7552,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>15314706.9</v>
+        <v>14087126.9</v>
       </c>
       <c r="L51" t="n">
         <v>35999.5</v>
@@ -8367,31 +7605,13 @@
       <c r="AB51" t="n">
         <v>0</v>
       </c>
-      <c r="AC51" t="n">
-        <v>1076000</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>39200</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>56610</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>38570</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>17200</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>own: ESTIMATE copied from 2024-07; IPP purchases: ESTIMATE copied from 2024-07</t>
-        </is>
-      </c>
-      <c r="AN51" t="n">
-        <v>1076000</v>
-      </c>
-      <c r="AO51" t="n">
-        <v>151580</v>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>no KE figure</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -8402,13 +7622,13 @@
         <v>5517345.5</v>
       </c>
       <c r="C52" t="n">
-        <v>2615037.7</v>
+        <v>2580017.7</v>
       </c>
       <c r="D52" t="n">
-        <v>4071054.2</v>
+        <v>3214724.2</v>
       </c>
       <c r="E52" t="n">
-        <v>102642.2</v>
+        <v>91892.2</v>
       </c>
       <c r="F52" t="n">
         <v>2145255</v>
@@ -8417,7 +7637,7 @@
         <v>512182.8</v>
       </c>
       <c r="H52" t="n">
-        <v>125255.6</v>
+        <v>103995.6</v>
       </c>
       <c r="I52" t="n">
         <v>35561.4</v>
@@ -8426,7 +7646,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>15124334.4</v>
+        <v>14200974.4</v>
       </c>
       <c r="L52" t="n">
         <v>17366.2</v>
@@ -8479,31 +7699,13 @@
       <c r="AB52" t="n">
         <v>0</v>
       </c>
-      <c r="AC52" t="n">
-        <v>806000</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>10750</v>
-      </c>
-      <c r="AE52" t="n">
-        <v>50330</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>35020</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>21260</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>own: ESTIMATE copied from 2024-08; IPP purchases: ESTIMATE copied from 2024-09</t>
-        </is>
-      </c>
-      <c r="AN52" t="n">
-        <v>806000</v>
-      </c>
-      <c r="AO52" t="n">
-        <v>117360</v>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>no KE figure</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -8514,13 +7716,13 @@
         <v>4783282.1</v>
       </c>
       <c r="C53" t="n">
-        <v>2256179.5</v>
+        <v>2221159.5</v>
       </c>
       <c r="D53" t="n">
-        <v>3525843.7</v>
+        <v>2755513.7</v>
       </c>
       <c r="E53" t="n">
-        <v>108151.8</v>
+        <v>97401.8</v>
       </c>
       <c r="F53" t="n">
         <v>2227359</v>
@@ -8529,7 +7731,7 @@
         <v>341649.9</v>
       </c>
       <c r="H53" t="n">
-        <v>129069.1</v>
+        <v>107809.1</v>
       </c>
       <c r="I53" t="n">
         <v>34060.3</v>
@@ -8538,7 +7740,7 @@
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>13405595.4</v>
+        <v>12568235.4</v>
       </c>
       <c r="L53" t="n">
         <v>23795.7</v>
@@ -8591,31 +7793,13 @@
       <c r="AB53" t="n">
         <v>0</v>
       </c>
-      <c r="AC53" t="n">
-        <v>720000</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>10750</v>
-      </c>
-      <c r="AE53" t="n">
-        <v>50330</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>35020</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>21260</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>own: ESTIMATE copied from 2024-09; IPP purchases: ESTIMATE copied from 2024-09</t>
-        </is>
-      </c>
-      <c r="AN53" t="n">
-        <v>720000</v>
-      </c>
-      <c r="AO53" t="n">
-        <v>117360</v>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>no KE figure</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -8626,13 +7810,13 @@
         <v>2704723.5</v>
       </c>
       <c r="C54" t="n">
-        <v>1761657.9</v>
+        <v>1726637.9</v>
       </c>
       <c r="D54" t="n">
-        <v>3706759.6</v>
+        <v>2854429.6</v>
       </c>
       <c r="E54" t="n">
-        <v>58290.6</v>
+        <v>47540.6</v>
       </c>
       <c r="F54" t="n">
         <v>2187854</v>
@@ -8641,7 +7825,7 @@
         <v>185198.5</v>
       </c>
       <c r="H54" t="n">
-        <v>117523.6</v>
+        <v>96263.60000000001</v>
       </c>
       <c r="I54" t="n">
         <v>39872</v>
@@ -8650,7 +7834,7 @@
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>10761879.7</v>
+        <v>9842519.699999999</v>
       </c>
       <c r="L54" t="n">
         <v>43256.7</v>
@@ -8703,31 +7887,13 @@
       <c r="AB54" t="n">
         <v>0</v>
       </c>
-      <c r="AC54" t="n">
-        <v>802000</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>10750</v>
-      </c>
-      <c r="AE54" t="n">
-        <v>50330</v>
-      </c>
-      <c r="AF54" t="n">
-        <v>35020</v>
-      </c>
-      <c r="AG54" t="n">
-        <v>21260</v>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>own: ESTIMATE copied from 2024-10; IPP purchases: ESTIMATE copied from 2024-09</t>
-        </is>
-      </c>
-      <c r="AN54" t="n">
-        <v>802000</v>
-      </c>
-      <c r="AO54" t="n">
-        <v>117360</v>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>no KE figure</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -8738,13 +7904,13 @@
         <v>3152632.8</v>
       </c>
       <c r="C55" t="n">
-        <v>1194239.6</v>
+        <v>1159219.6</v>
       </c>
       <c r="D55" t="n">
-        <v>1889028.4</v>
+        <v>1375698.4</v>
       </c>
       <c r="E55" t="n">
-        <v>10750</v>
+        <v>0</v>
       </c>
       <c r="F55" t="n">
         <v>2030922</v>
@@ -8753,7 +7919,7 @@
         <v>135628.8</v>
       </c>
       <c r="H55" t="n">
-        <v>107339.4</v>
+        <v>86079.39999999999</v>
       </c>
       <c r="I55" t="n">
         <v>75379.8</v>
@@ -8762,7 +7928,7 @@
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>8595920.800000001</v>
+        <v>8015560.8</v>
       </c>
       <c r="L55" t="n">
         <v>34647.8</v>
@@ -8815,31 +7981,13 @@
       <c r="AB55" t="n">
         <v>0</v>
       </c>
-      <c r="AC55" t="n">
-        <v>463000</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>10750</v>
-      </c>
-      <c r="AE55" t="n">
-        <v>50330</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>35020</v>
-      </c>
-      <c r="AG55" t="n">
-        <v>21260</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>own: ESTIMATE copied from 2021-11; IPP purchases: ESTIMATE copied from 2024-09</t>
-        </is>
-      </c>
-      <c r="AN55" t="n">
-        <v>463000</v>
-      </c>
-      <c r="AO55" t="n">
-        <v>117360</v>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>no KE figure</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -8850,13 +7998,13 @@
         <v>1534031.3</v>
       </c>
       <c r="C56" t="n">
-        <v>2082108.2</v>
+        <v>2047088.2</v>
       </c>
       <c r="D56" t="n">
-        <v>2795627.2</v>
+        <v>2414297.2</v>
       </c>
       <c r="E56" t="n">
-        <v>10750</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
         <v>2125797</v>
@@ -8865,7 +8013,7 @@
         <v>162248.5</v>
       </c>
       <c r="H56" t="n">
-        <v>94864.7</v>
+        <v>73604.7</v>
       </c>
       <c r="I56" t="n">
         <v>97028.8</v>
@@ -8874,7 +8022,7 @@
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>8902455.699999999</v>
+        <v>8454095.699999999</v>
       </c>
       <c r="L56" t="n">
         <v>32947.6</v>
@@ -8927,31 +8075,13 @@
       <c r="AB56" t="n">
         <v>0</v>
       </c>
-      <c r="AC56" t="n">
-        <v>331000</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>10750</v>
-      </c>
-      <c r="AE56" t="n">
-        <v>50330</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>35020</v>
-      </c>
-      <c r="AG56" t="n">
-        <v>21260</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>own: ESTIMATE copied from 2022-12; IPP purchases: ESTIMATE copied from 2024-09</t>
-        </is>
-      </c>
-      <c r="AN56" t="n">
-        <v>331000</v>
-      </c>
-      <c r="AO56" t="n">
-        <v>117360</v>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>no KE figure</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -8962,13 +8092,13 @@
         <v>713271.2</v>
       </c>
       <c r="C57" t="n">
-        <v>3018479.9</v>
+        <v>2983459.9</v>
       </c>
       <c r="D57" t="n">
-        <v>3410732.4</v>
+        <v>3119402.4</v>
       </c>
       <c r="E57" t="n">
-        <v>284951.3</v>
+        <v>274201.3</v>
       </c>
       <c r="F57" t="n">
         <v>1598833</v>
@@ -8977,7 +8107,7 @@
         <v>241318.1</v>
       </c>
       <c r="H57" t="n">
-        <v>94793.8</v>
+        <v>73533.8</v>
       </c>
       <c r="I57" t="n">
         <v>101540.8</v>
@@ -8986,7 +8116,7 @@
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>9463920.5</v>
+        <v>9105560.5</v>
       </c>
       <c r="L57" t="n">
         <v>34799.8</v>
@@ -9039,31 +8169,13 @@
       <c r="AB57" t="n">
         <v>0</v>
       </c>
-      <c r="AC57" t="n">
-        <v>241000</v>
-      </c>
-      <c r="AD57" t="n">
-        <v>10750</v>
-      </c>
-      <c r="AE57" t="n">
-        <v>50330</v>
-      </c>
-      <c r="AF57" t="n">
-        <v>35020</v>
-      </c>
-      <c r="AG57" t="n">
-        <v>21260</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>own: ESTIMATE copied from 2022-01; IPP purchases: ESTIMATE copied from 2024-09</t>
-        </is>
-      </c>
-      <c r="AN57" t="n">
-        <v>241000</v>
-      </c>
-      <c r="AO57" t="n">
-        <v>117360</v>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>no KE figure</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -9074,13 +8186,13 @@
         <v>1782514.6</v>
       </c>
       <c r="C58" t="n">
-        <v>2416028.7</v>
+        <v>2381008.7</v>
       </c>
       <c r="D58" t="n">
-        <v>1960613.1</v>
+        <v>1615283.1</v>
       </c>
       <c r="E58" t="n">
-        <v>10750</v>
+        <v>0</v>
       </c>
       <c r="F58" t="n">
         <v>1448964.4</v>
@@ -9089,7 +8201,7 @@
         <v>250502.1</v>
       </c>
       <c r="H58" t="n">
-        <v>112976.9</v>
+        <v>91716.89999999999</v>
       </c>
       <c r="I58" t="n">
         <v>90954</v>
@@ -9098,7 +8210,7 @@
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>8073303.8</v>
+        <v>7660943.8</v>
       </c>
       <c r="L58" t="n">
         <v>34799.8</v>
@@ -9151,31 +8263,13 @@
       <c r="AB58" t="n">
         <v>0</v>
       </c>
-      <c r="AC58" t="n">
-        <v>295000</v>
-      </c>
-      <c r="AD58" t="n">
-        <v>10750</v>
-      </c>
-      <c r="AE58" t="n">
-        <v>50330</v>
-      </c>
-      <c r="AF58" t="n">
-        <v>35020</v>
-      </c>
-      <c r="AG58" t="n">
-        <v>21260</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>own: ESTIMATE copied from 2023-02; IPP purchases: ESTIMATE copied from 2024-09</t>
-        </is>
-      </c>
-      <c r="AN58" t="n">
-        <v>295000</v>
-      </c>
-      <c r="AO58" t="n">
-        <v>117360</v>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>no KE figure</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -9186,13 +8280,13 @@
         <v>2105177.3</v>
       </c>
       <c r="C59" t="n">
-        <v>2766999.7</v>
+        <v>2731979.7</v>
       </c>
       <c r="D59" t="n">
-        <v>2087868.9</v>
+        <v>1517538.9</v>
       </c>
       <c r="E59" t="n">
-        <v>101722.2</v>
+        <v>90972.2</v>
       </c>
       <c r="F59" t="n">
         <v>1962290</v>
@@ -9201,7 +8295,7 @@
         <v>308972.5</v>
       </c>
       <c r="H59" t="n">
-        <v>126887.3</v>
+        <v>105627.3</v>
       </c>
       <c r="I59" t="n">
         <v>77437</v>
@@ -9210,7 +8304,7 @@
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>9537354.9</v>
+        <v>8899994.9</v>
       </c>
       <c r="L59" t="n">
         <v>39283.9</v>
@@ -9263,31 +8357,13 @@
       <c r="AB59" t="n">
         <v>0</v>
       </c>
-      <c r="AC59" t="n">
-        <v>520000</v>
-      </c>
-      <c r="AD59" t="n">
-        <v>10750</v>
-      </c>
-      <c r="AE59" t="n">
-        <v>50330</v>
-      </c>
-      <c r="AF59" t="n">
-        <v>35020</v>
-      </c>
-      <c r="AG59" t="n">
-        <v>21260</v>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>own: ESTIMATE copied from 2023-03; IPP purchases: ESTIMATE copied from 2024-09</t>
-        </is>
-      </c>
-      <c r="AN59" t="n">
-        <v>520000</v>
-      </c>
-      <c r="AO59" t="n">
-        <v>117360</v>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>no KE figure</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -9298,13 +8374,13 @@
         <v>2078975.4</v>
       </c>
       <c r="C60" t="n">
-        <v>2855956.8</v>
+        <v>2825276.8</v>
       </c>
       <c r="D60" t="n">
-        <v>1987013.7</v>
+        <v>1348323.7</v>
       </c>
       <c r="E60" t="n">
-        <v>533807.6</v>
+        <v>532687.6</v>
       </c>
       <c r="F60" t="n">
         <v>2096831</v>
@@ -9313,7 +8389,7 @@
         <v>409101.7</v>
       </c>
       <c r="H60" t="n">
-        <v>153689.8</v>
+        <v>111429.8</v>
       </c>
       <c r="I60" t="n">
         <v>63809.6</v>
@@ -9322,7 +8398,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>10179185.6</v>
+        <v>9466435.6</v>
       </c>
       <c r="L60" t="n">
         <v>32458.7</v>
@@ -9375,31 +8451,13 @@
       <c r="AB60" t="n">
         <v>46850.4</v>
       </c>
-      <c r="AC60" t="n">
-        <v>581000</v>
-      </c>
-      <c r="AD60" t="n">
-        <v>1120</v>
-      </c>
-      <c r="AE60" t="n">
-        <v>57690</v>
-      </c>
-      <c r="AF60" t="n">
-        <v>30680</v>
-      </c>
-      <c r="AG60" t="n">
-        <v>42260</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>own: ESTIMATE copied from 2024-04; IPP purchases: ESTIMATE copied from 2024-04</t>
-        </is>
-      </c>
-      <c r="AN60" t="n">
-        <v>581000</v>
-      </c>
-      <c r="AO60" t="n">
-        <v>131750</v>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>no KE figure</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -9410,13 +8468,13 @@
         <v>4204987.9</v>
       </c>
       <c r="C61" t="n">
-        <v>3220520.7</v>
+        <v>3185500.7</v>
       </c>
       <c r="D61" t="n">
-        <v>3481920.3</v>
+        <v>2542590.3</v>
       </c>
       <c r="E61" t="n">
-        <v>30858.9</v>
+        <v>20108.9</v>
       </c>
       <c r="F61" t="n">
         <v>1801332</v>
@@ -9425,7 +8483,7 @@
         <v>665157</v>
       </c>
       <c r="H61" t="n">
-        <v>140394.3</v>
+        <v>119134.3</v>
       </c>
       <c r="I61" t="n">
         <v>63134.1</v>
@@ -9434,7 +8492,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>13608305.2</v>
+        <v>12601945.2</v>
       </c>
       <c r="L61" t="n">
         <v>36189.3</v>
@@ -9487,31 +8545,13 @@
       <c r="AB61" t="n">
         <v>0</v>
       </c>
-      <c r="AC61" t="n">
-        <v>889000</v>
-      </c>
-      <c r="AD61" t="n">
-        <v>10750</v>
-      </c>
-      <c r="AE61" t="n">
-        <v>50330</v>
-      </c>
-      <c r="AF61" t="n">
-        <v>35020</v>
-      </c>
-      <c r="AG61" t="n">
-        <v>21260</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>own: ESTIMATE copied from 2024-05; IPP purchases: ESTIMATE copied from 2024-09</t>
-        </is>
-      </c>
-      <c r="AN61" t="n">
-        <v>889000</v>
-      </c>
-      <c r="AO61" t="n">
-        <v>117360</v>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>no KE figure</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -9522,13 +8562,13 @@
         <v>5241797.3</v>
       </c>
       <c r="C62" t="n">
-        <v>3092556.4</v>
+        <v>3057536.4</v>
       </c>
       <c r="D62" t="n">
-        <v>3352835.5</v>
+        <v>2346505.5</v>
       </c>
       <c r="E62" t="n">
-        <v>116170.4</v>
+        <v>105420.4</v>
       </c>
       <c r="F62" t="n">
         <v>1800261</v>
@@ -9537,7 +8577,7 @@
         <v>675947.6</v>
       </c>
       <c r="H62" t="n">
-        <v>131668.2</v>
+        <v>110408.2</v>
       </c>
       <c r="I62" t="n">
         <v>46346.1</v>
@@ -9546,7 +8586,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>14457582.5</v>
+        <v>13384222.5</v>
       </c>
       <c r="L62" t="n">
         <v>46992.7</v>
@@ -9599,31 +8639,13 @@
       <c r="AB62" t="n">
         <v>5472.1</v>
       </c>
-      <c r="AC62" t="n">
-        <v>956000</v>
-      </c>
-      <c r="AD62" t="n">
-        <v>10750</v>
-      </c>
-      <c r="AE62" t="n">
-        <v>50330</v>
-      </c>
-      <c r="AF62" t="n">
-        <v>35020</v>
-      </c>
-      <c r="AG62" t="n">
-        <v>21260</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>own: ESTIMATE copied from 2024-06; IPP purchases: ESTIMATE copied from 2024-09</t>
-        </is>
-      </c>
-      <c r="AN62" t="n">
-        <v>956000</v>
-      </c>
-      <c r="AO62" t="n">
-        <v>117360</v>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>no KE figure</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -9634,13 +8656,13 @@
         <v>6019491.6</v>
       </c>
       <c r="C63" t="n">
-        <v>3856923.2</v>
+        <v>3818353.2</v>
       </c>
       <c r="D63" t="n">
-        <v>3751576.9</v>
+        <v>2618966.9</v>
       </c>
       <c r="E63" t="n">
-        <v>285423.6</v>
+        <v>246223.6</v>
       </c>
       <c r="F63" t="n">
         <v>1526708</v>
@@ -9649,7 +8671,7 @@
         <v>681807.3</v>
       </c>
       <c r="H63" t="n">
-        <v>123336.4</v>
+        <v>106136.4</v>
       </c>
       <c r="I63" t="n">
         <v>45875.3</v>
@@ -9658,7 +8680,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>16291142.3</v>
+        <v>15063562.3</v>
       </c>
       <c r="L63" t="n">
         <v>57938.1</v>
@@ -9711,31 +8733,13 @@
       <c r="AB63" t="n">
         <v>31095.3</v>
       </c>
-      <c r="AC63" t="n">
-        <v>1076000</v>
-      </c>
-      <c r="AD63" t="n">
-        <v>39200</v>
-      </c>
-      <c r="AE63" t="n">
-        <v>56610</v>
-      </c>
-      <c r="AF63" t="n">
-        <v>38570</v>
-      </c>
-      <c r="AG63" t="n">
-        <v>17200</v>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>own: ESTIMATE copied from 2024-07; IPP purchases: ESTIMATE copied from 2024-07</t>
-        </is>
-      </c>
-      <c r="AN63" t="n">
-        <v>1076000</v>
-      </c>
-      <c r="AO63" t="n">
-        <v>151580</v>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>no KE figure</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -9746,13 +8750,13 @@
         <v>5654882</v>
       </c>
       <c r="C64" t="n">
-        <v>3990071.8</v>
+        <v>3955051.8</v>
       </c>
       <c r="D64" t="n">
-        <v>3219824.1</v>
+        <v>2363494.1</v>
       </c>
       <c r="E64" t="n">
-        <v>412521.8</v>
+        <v>401771.8</v>
       </c>
       <c r="F64" t="n">
         <v>1531552</v>
@@ -9761,7 +8765,7 @@
         <v>833247.2</v>
       </c>
       <c r="H64" t="n">
-        <v>133281.7</v>
+        <v>112021.7</v>
       </c>
       <c r="I64" t="n">
         <v>35989.6</v>
@@ -9770,7 +8774,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>15811370.2</v>
+        <v>14888010.2</v>
       </c>
       <c r="L64" t="n">
         <v>58894.1</v>
@@ -9823,31 +8827,13 @@
       <c r="AB64" t="n">
         <v>80396.5</v>
       </c>
-      <c r="AC64" t="n">
-        <v>806000</v>
-      </c>
-      <c r="AD64" t="n">
-        <v>10750</v>
-      </c>
-      <c r="AE64" t="n">
-        <v>50330</v>
-      </c>
-      <c r="AF64" t="n">
-        <v>35020</v>
-      </c>
-      <c r="AG64" t="n">
-        <v>21260</v>
-      </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>own: ESTIMATE copied from 2024-08; IPP purchases: ESTIMATE copied from 2024-09</t>
-        </is>
-      </c>
-      <c r="AN64" t="n">
-        <v>806000</v>
-      </c>
-      <c r="AO64" t="n">
-        <v>117360</v>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>no KE figure</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/pakistan_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/pakistan_power_generation_daily.xlsx
@@ -832,7 +832,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Monthly from Feb 2021 to Aug 2026 (63 months; national-grid sources: {'NEPRA FCA decision': 37, 'CPPA-G workbook': 24, 'CPPA-G PDF': 2}; KE basis: {'no': 39, 'own': 24}). Calendar-year totals, TWh (Pakistan incl. KE, national grid alone): {2023: (np.float64(131.8), np.float64(129.4)), 2025: (np.float64(127.5), np.float64(127.5))}.</t>
+          <t>Monthly from Feb 2021 to Aug 2026 (63 months; national-grid sources: {'NEPRA FCA decision': 37, 'CPPA-G workbook': 24, 'CPPA-G PDF': 2}; KE basis: {'no': 26, 'NEPRA': 19, 'own': 18}). Calendar-year totals, TWh (Pakistan incl. KE, national grid alone): {2023: (np.float64(137.4), np.float64(129.4)), 2025: (np.float64(127.8), np.float64(127.5))}.</t>
         </is>
       </c>
     </row>
@@ -1076,22 +1076,22 @@
         <v>4695.76</v>
       </c>
       <c r="C7" t="n">
-        <v>5353.89</v>
+        <v>5426.259</v>
       </c>
       <c r="D7" t="n">
         <v>550.37</v>
       </c>
       <c r="E7" t="n">
-        <v>61.82</v>
+        <v>74.88</v>
       </c>
       <c r="F7" t="n">
-        <v>2383.33</v>
+        <v>2422.934</v>
       </c>
       <c r="G7" t="n">
-        <v>1659.86</v>
+        <v>1702.438</v>
       </c>
       <c r="H7" t="n">
-        <v>1790.65</v>
+        <v>1903.223</v>
       </c>
     </row>
     <row r="8">
@@ -1128,22 +1128,22 @@
         <v>5085.48</v>
       </c>
       <c r="C9" t="n">
-        <v>4803.23</v>
+        <v>4874.847</v>
       </c>
       <c r="D9" t="n">
         <v>230.4</v>
       </c>
       <c r="E9" t="n">
-        <v>60.75</v>
+        <v>74.98699999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>2392.52</v>
+        <v>2419.161</v>
       </c>
       <c r="G9" t="n">
         <v>1281.8</v>
       </c>
       <c r="H9" t="n">
-        <v>1032.44</v>
+        <v>1185.95</v>
       </c>
     </row>
     <row r="10">
@@ -1154,22 +1154,22 @@
         <v>2627.25</v>
       </c>
       <c r="C10" t="n">
-        <v>4554.13</v>
+        <v>4624.733</v>
       </c>
       <c r="D10" t="n">
         <v>184.82</v>
       </c>
       <c r="E10" t="n">
-        <v>63.17</v>
+        <v>79.36499999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>1885.78</v>
+        <v>1923.456</v>
       </c>
       <c r="G10" t="n">
         <v>1392.92</v>
       </c>
       <c r="H10" t="n">
-        <v>1304.77</v>
+        <v>1425.96</v>
       </c>
     </row>
     <row r="11">
@@ -1180,22 +1180,22 @@
         <v>2816.49</v>
       </c>
       <c r="C11" t="n">
-        <v>2766.86</v>
+        <v>2827.973</v>
       </c>
       <c r="D11" t="n">
         <v>175.19</v>
       </c>
       <c r="E11" t="n">
-        <v>50.62</v>
+        <v>65.02200000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>1379.12</v>
+        <v>1418.165</v>
       </c>
       <c r="G11" t="n">
         <v>1485.19</v>
       </c>
       <c r="H11" t="n">
-        <v>236.56</v>
+        <v>329.42</v>
       </c>
     </row>
     <row r="12">
@@ -1206,22 +1206,22 @@
         <v>1768.84</v>
       </c>
       <c r="C12" t="n">
-        <v>2708.36</v>
+        <v>2764.713</v>
       </c>
       <c r="D12" t="n">
         <v>210.08</v>
       </c>
       <c r="E12" t="n">
-        <v>45.18</v>
+        <v>58.227</v>
       </c>
       <c r="F12" t="n">
-        <v>2103.65</v>
+        <v>2137.818</v>
       </c>
       <c r="G12" t="n">
         <v>1549.06</v>
       </c>
       <c r="H12" t="n">
-        <v>710.1700000000001</v>
+        <v>767.3910000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1232,22 +1232,22 @@
         <v>512.9299999999999</v>
       </c>
       <c r="C13" t="n">
-        <v>2131.44</v>
+        <v>2176.616</v>
       </c>
       <c r="D13" t="n">
         <v>194.88</v>
       </c>
       <c r="E13" t="n">
-        <v>46.58</v>
+        <v>60.8</v>
       </c>
       <c r="F13" t="n">
-        <v>2916.7</v>
+        <v>2919.919</v>
       </c>
       <c r="G13" t="n">
         <v>1264.57</v>
       </c>
       <c r="H13" t="n">
-        <v>1939.51</v>
+        <v>2035.973</v>
       </c>
     </row>
     <row r="14">
@@ -1258,22 +1258,22 @@
         <v>1703.91</v>
       </c>
       <c r="C14" t="n">
-        <v>3549.4</v>
+        <v>3619.889</v>
       </c>
       <c r="D14" t="n">
         <v>267.92</v>
       </c>
       <c r="E14" t="n">
-        <v>68.73</v>
+        <v>88.294</v>
       </c>
       <c r="F14" t="n">
-        <v>2586.62</v>
+        <v>2620.343</v>
       </c>
       <c r="G14" t="n">
         <v>1563.66</v>
       </c>
       <c r="H14" t="n">
-        <v>1226.42</v>
+        <v>1364.291</v>
       </c>
     </row>
     <row r="15">
@@ -1284,22 +1284,22 @@
         <v>2404.35</v>
       </c>
       <c r="C15" t="n">
-        <v>4684.42</v>
+        <v>4758.582</v>
       </c>
       <c r="D15" t="n">
         <v>464.78</v>
       </c>
       <c r="E15" t="n">
-        <v>87.31</v>
+        <v>103.163</v>
       </c>
       <c r="F15" t="n">
-        <v>2168.93</v>
+        <v>2207.913</v>
       </c>
       <c r="G15" t="n">
         <v>2251.19</v>
       </c>
       <c r="H15" t="n">
-        <v>1738.47</v>
+        <v>1899.225</v>
       </c>
     </row>
     <row r="16">
@@ -1336,22 +1336,22 @@
         <v>3361.21</v>
       </c>
       <c r="C17" t="n">
-        <v>5402.175099999999</v>
+        <v>5465.5651</v>
       </c>
       <c r="D17" t="n">
         <v>811.59</v>
       </c>
       <c r="E17" t="n">
-        <v>86.27</v>
+        <v>103.672</v>
       </c>
       <c r="F17" t="n">
-        <v>1883.13</v>
+        <v>1922.229</v>
       </c>
       <c r="G17" t="n">
         <v>1265.67</v>
       </c>
       <c r="H17" t="n">
-        <v>1935.5349</v>
+        <v>2086.2769</v>
       </c>
     </row>
     <row r="18">
@@ -1362,22 +1362,22 @@
         <v>4976.93</v>
       </c>
       <c r="C18" t="n">
-        <v>4377.96</v>
+        <v>4448.46</v>
       </c>
       <c r="D18" t="n">
         <v>521.72</v>
       </c>
       <c r="E18" t="n">
-        <v>70.77</v>
+        <v>83.81999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>1802.19</v>
+        <v>1837.46</v>
       </c>
       <c r="G18" t="n">
         <v>2009.54</v>
       </c>
       <c r="H18" t="n">
-        <v>1140.44</v>
+        <v>1253.89</v>
       </c>
     </row>
     <row r="19">
@@ -1388,22 +1388,22 @@
         <v>5353.69</v>
       </c>
       <c r="C19" t="n">
-        <v>3741.01</v>
+        <v>3803.52</v>
       </c>
       <c r="D19" t="n">
         <v>390.71</v>
       </c>
       <c r="E19" t="n">
-        <v>73.44</v>
+        <v>85.2</v>
       </c>
       <c r="F19" t="n">
-        <v>2163.01</v>
+        <v>2203.28</v>
       </c>
       <c r="G19" t="n">
         <v>1873.98</v>
       </c>
       <c r="H19" t="n">
-        <v>1072.5</v>
+        <v>1207.39</v>
       </c>
     </row>
     <row r="20">
@@ -1414,22 +1414,22 @@
         <v>3143.62</v>
       </c>
       <c r="C20" t="n">
-        <v>3803.11</v>
+        <v>3866.35</v>
       </c>
       <c r="D20" t="n">
         <v>209.7</v>
       </c>
       <c r="E20" t="n">
-        <v>79.08</v>
+        <v>98.08</v>
       </c>
       <c r="F20" t="n">
-        <v>1656.52</v>
+        <v>1695.35</v>
       </c>
       <c r="G20" t="n">
         <v>2206.33</v>
       </c>
       <c r="H20" t="n">
-        <v>209.15</v>
+        <v>328.86</v>
       </c>
     </row>
     <row r="21">
@@ -1440,22 +1440,22 @@
         <v>1720.43</v>
       </c>
       <c r="C21" t="n">
-        <v>2758.53</v>
+        <v>2801.37</v>
       </c>
       <c r="D21" t="n">
         <v>211.57</v>
       </c>
       <c r="E21" t="n">
-        <v>69.45999999999999</v>
+        <v>86.31999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>1520.93</v>
+        <v>1545.43</v>
       </c>
       <c r="G21" t="n">
         <v>2284.86</v>
       </c>
       <c r="H21" t="n">
-        <v>142.18</v>
+        <v>181.52</v>
       </c>
     </row>
     <row r="22">
@@ -1492,22 +1492,22 @@
         <v>2052.16</v>
       </c>
       <c r="C23" t="n">
-        <v>2607.51</v>
+        <v>2653.34</v>
       </c>
       <c r="D23" t="n">
         <v>92.2</v>
       </c>
       <c r="E23" t="n">
-        <v>82.26000000000001</v>
+        <v>104.41</v>
       </c>
       <c r="F23" t="n">
-        <v>1091.14</v>
+        <v>1111.11</v>
       </c>
       <c r="G23" t="n">
         <v>1883.09</v>
       </c>
       <c r="H23" t="n">
-        <v>209.76</v>
+        <v>265.88</v>
       </c>
     </row>
     <row r="24">
@@ -1518,22 +1518,22 @@
         <v>2001.61</v>
       </c>
       <c r="C24" t="n">
-        <v>3411.6</v>
+        <v>3468.37</v>
       </c>
       <c r="D24" t="n">
         <v>221.33</v>
       </c>
       <c r="E24" t="n">
-        <v>110.73</v>
+        <v>135.3</v>
       </c>
       <c r="F24" t="n">
-        <v>1333.52</v>
+        <v>1369.48</v>
       </c>
       <c r="G24" t="n">
         <v>2002.01</v>
       </c>
       <c r="H24" t="n">
-        <v>148.94</v>
+        <v>222.63</v>
       </c>
     </row>
     <row r="25">
@@ -1544,22 +1544,22 @@
         <v>1873.19</v>
       </c>
       <c r="C25" t="n">
-        <v>4275.04</v>
+        <v>4321.02</v>
       </c>
       <c r="D25" t="n">
         <v>322.93</v>
       </c>
       <c r="E25" t="n">
-        <v>125.8</v>
+        <v>151.66</v>
       </c>
       <c r="F25" t="n">
-        <v>1818.73</v>
+        <v>1855.48</v>
       </c>
       <c r="G25" t="n">
         <v>1916.07</v>
       </c>
       <c r="H25" t="n">
-        <v>317.09</v>
+        <v>343.37</v>
       </c>
     </row>
     <row r="26">
@@ -1570,22 +1570,22 @@
         <v>3312.2</v>
       </c>
       <c r="C26" t="n">
-        <v>5141.95</v>
+        <v>5192.61</v>
       </c>
       <c r="D26" t="n">
         <v>606.58</v>
       </c>
       <c r="E26" t="n">
-        <v>89.5</v>
+        <v>114.78</v>
       </c>
       <c r="F26" t="n">
-        <v>2061.3</v>
+        <v>2074.97</v>
       </c>
       <c r="G26" t="n">
         <v>1542.59</v>
       </c>
       <c r="H26" t="n">
-        <v>315.84</v>
+        <v>413.21</v>
       </c>
     </row>
     <row r="27">
@@ -1622,22 +1622,22 @@
         <v>5517.77</v>
       </c>
       <c r="C28" t="n">
-        <v>4046.81</v>
+        <v>4967.98</v>
       </c>
       <c r="D28" t="n">
         <v>548.76</v>
       </c>
       <c r="E28" t="n">
-        <v>75.19</v>
+        <v>92.64</v>
       </c>
       <c r="F28" t="n">
-        <v>2179.89</v>
+        <v>2195.06</v>
       </c>
       <c r="G28" t="n">
         <v>2106.93</v>
       </c>
       <c r="H28" t="n">
-        <v>333.7767</v>
+        <v>504.4067</v>
       </c>
     </row>
     <row r="29">
@@ -1648,22 +1648,22 @@
         <v>6005.5</v>
       </c>
       <c r="C29" t="n">
-        <v>3954.2</v>
+        <v>4791</v>
       </c>
       <c r="D29" t="n">
         <v>804.7</v>
       </c>
       <c r="E29" t="n">
-        <v>84.06999999999999</v>
+        <v>96.81</v>
       </c>
       <c r="F29" t="n">
-        <v>2357.23</v>
+        <v>2382.46</v>
       </c>
       <c r="G29" t="n">
         <v>2040.45</v>
       </c>
       <c r="H29" t="n">
-        <v>686.92</v>
+        <v>745.67</v>
       </c>
     </row>
     <row r="30">
@@ -1674,22 +1674,22 @@
         <v>5008.52</v>
       </c>
       <c r="C30" t="n">
-        <v>3133.08</v>
+        <v>3906.76</v>
       </c>
       <c r="D30" t="n">
         <v>410.23</v>
       </c>
       <c r="E30" t="n">
-        <v>78.79000000000001</v>
+        <v>97.08</v>
       </c>
       <c r="F30" t="n">
-        <v>2122.86</v>
+        <v>2160.11</v>
       </c>
       <c r="G30" t="n">
         <v>2286.35</v>
       </c>
       <c r="H30" t="n">
-        <v>275.13</v>
+        <v>401.89</v>
       </c>
     </row>
     <row r="31">
@@ -1700,22 +1700,22 @@
         <v>3114.14</v>
       </c>
       <c r="C31" t="n">
-        <v>2642.49</v>
+        <v>3418.17</v>
       </c>
       <c r="D31" t="n">
         <v>191.14</v>
       </c>
       <c r="E31" t="n">
-        <v>76</v>
+        <v>95.73999999999999</v>
       </c>
       <c r="F31" t="n">
-        <v>1670.17</v>
+        <v>1710.71</v>
       </c>
       <c r="G31" t="n">
         <v>1826.26</v>
       </c>
       <c r="H31" t="n">
-        <v>28.83</v>
+        <v>167.58</v>
       </c>
     </row>
     <row r="32">
@@ -1726,22 +1726,22 @@
         <v>2754.86</v>
       </c>
       <c r="C32" t="n">
-        <v>1492.76</v>
+        <v>1961.65</v>
       </c>
       <c r="D32" t="n">
         <v>147.84</v>
       </c>
       <c r="E32" t="n">
-        <v>49.78</v>
+        <v>66.22</v>
       </c>
       <c r="F32" t="n">
-        <v>1473.12</v>
+        <v>1509.18</v>
       </c>
       <c r="G32" t="n">
         <v>1571.66</v>
       </c>
       <c r="H32" t="n">
-        <v>26.96</v>
+        <v>118.75</v>
       </c>
     </row>
     <row r="33">
@@ -1752,22 +1752,22 @@
         <v>1859.01</v>
       </c>
       <c r="C33" t="n">
-        <v>2093.9</v>
+        <v>2398.52</v>
       </c>
       <c r="D33" t="n">
         <v>150.37</v>
       </c>
       <c r="E33" t="n">
-        <v>61.82</v>
+        <v>82.02</v>
       </c>
       <c r="F33" t="n">
-        <v>1693.18</v>
+        <v>1721.96</v>
       </c>
       <c r="G33" t="n">
         <v>1464.43</v>
       </c>
       <c r="H33" t="n">
-        <v>275.77</v>
+        <v>282.91</v>
       </c>
     </row>
     <row r="34">
@@ -1778,22 +1778,22 @@
         <v>924.22</v>
       </c>
       <c r="C34" t="n">
-        <v>2549.75</v>
+        <v>2850.4</v>
       </c>
       <c r="D34" t="n">
         <v>127.55</v>
       </c>
       <c r="E34" t="n">
-        <v>47.94</v>
+        <v>69.62</v>
       </c>
       <c r="F34" t="n">
-        <v>1948.93</v>
+        <v>1949.99</v>
       </c>
       <c r="G34" t="n">
         <v>1727.8</v>
       </c>
       <c r="H34" t="n">
-        <v>958.46</v>
+        <v>1004.53</v>
       </c>
     </row>
     <row r="35">
@@ -1804,22 +1804,22 @@
         <v>1766.29</v>
       </c>
       <c r="C35" t="n">
-        <v>2236.82</v>
+        <v>2602.99</v>
       </c>
       <c r="D35" t="n">
         <v>107.6335</v>
       </c>
       <c r="E35" t="n">
-        <v>90.17</v>
+        <v>113.86</v>
       </c>
       <c r="F35" t="n">
-        <v>1128.71</v>
+        <v>1132.98</v>
       </c>
       <c r="G35" t="n">
         <v>1660.25</v>
       </c>
       <c r="H35" t="n">
-        <v>100.53</v>
+        <v>120.95</v>
       </c>
     </row>
     <row r="36">
@@ -1830,22 +1830,22 @@
         <v>2216.81</v>
       </c>
       <c r="C36" t="n">
-        <v>2453.52</v>
+        <v>2953.52</v>
       </c>
       <c r="D36" t="n">
         <v>204.7</v>
       </c>
       <c r="E36" t="n">
-        <v>109.98</v>
+        <v>141.47</v>
       </c>
       <c r="F36" t="n">
-        <v>861.77</v>
+        <v>890.3</v>
       </c>
       <c r="G36" t="n">
         <v>2069.6</v>
       </c>
       <c r="H36" t="n">
-        <v>78.5</v>
+        <v>100.96</v>
       </c>
     </row>
     <row r="37">
@@ -1856,22 +1856,22 @@
         <v>3906.27</v>
       </c>
       <c r="C37" t="n">
-        <v>4745.63</v>
+        <v>4764.04</v>
       </c>
       <c r="D37" t="n">
         <v>445.44</v>
       </c>
       <c r="E37" t="n">
-        <v>124.87</v>
+        <v>157.17</v>
       </c>
       <c r="F37" t="n">
-        <v>1754.27</v>
+        <v>1793.56</v>
       </c>
       <c r="G37" t="n">
         <v>2360.02</v>
       </c>
       <c r="H37" t="n">
-        <v>118.88</v>
+        <v>221.72</v>
       </c>
     </row>
     <row r="38">
@@ -1882,22 +1882,22 @@
         <v>4728.5</v>
       </c>
       <c r="C38" t="n">
-        <v>4559.23</v>
+        <v>4552.52</v>
       </c>
       <c r="D38" t="n">
         <v>515.73</v>
       </c>
       <c r="E38" t="n">
-        <v>117.54</v>
+        <v>139.49</v>
       </c>
       <c r="F38" t="n">
-        <v>2126.07</v>
+        <v>2163.75</v>
       </c>
       <c r="G38" t="n">
         <v>1998.39</v>
       </c>
       <c r="H38" t="n">
-        <v>322.7</v>
+        <v>434.01</v>
       </c>
     </row>
     <row r="39">
@@ -1908,7 +1908,7 @@
         <v>5341.2248</v>
       </c>
       <c r="C39" t="n">
-        <v>5134.6061</v>
+        <v>5134.450900000001</v>
       </c>
       <c r="D39" t="n">
         <v>445.0073</v>
@@ -1923,7 +1923,7 @@
         <v>1987.716</v>
       </c>
       <c r="H39" t="n">
-        <v>342.508</v>
+        <v>342.4833</v>
       </c>
     </row>
     <row r="40">
@@ -1934,22 +1934,22 @@
         <v>5361.562599999999</v>
       </c>
       <c r="C40" t="n">
-        <v>3861.9008</v>
+        <v>3907.5408</v>
       </c>
       <c r="D40" t="n">
         <v>398.2539</v>
       </c>
       <c r="E40" t="n">
-        <v>98.3733</v>
+        <v>110.7733</v>
       </c>
       <c r="F40" t="n">
-        <v>1986.3529</v>
+        <v>2022.6729</v>
       </c>
       <c r="G40" t="n">
         <v>2190.305</v>
       </c>
       <c r="H40" t="n">
-        <v>52.37260000000001</v>
+        <v>76.49260000000001</v>
       </c>
     </row>
     <row r="41">
@@ -1960,7 +1960,7 @@
         <v>4837.980799999999</v>
       </c>
       <c r="C41" t="n">
-        <v>3770.0755</v>
+        <v>3769.6524</v>
       </c>
       <c r="D41" t="n">
         <v>395.4457</v>
@@ -1975,7 +1975,7 @@
         <v>1595.672</v>
       </c>
       <c r="H41" t="n">
-        <v>113.1442</v>
+        <v>113.1273</v>
       </c>
     </row>
     <row r="42">
@@ -1986,22 +1986,22 @@
         <v>3187.387</v>
       </c>
       <c r="C42" t="n">
-        <v>3617.9631</v>
+        <v>3661.6748</v>
       </c>
       <c r="D42" t="n">
         <v>189.9809</v>
       </c>
       <c r="E42" t="n">
-        <v>99.0667</v>
+        <v>122.5767</v>
       </c>
       <c r="F42" t="n">
-        <v>2420.7944</v>
+        <v>2460.2944</v>
       </c>
       <c r="G42" t="n">
         <v>1441.938</v>
       </c>
       <c r="H42" t="n">
-        <v>64.857</v>
+        <v>78.4453</v>
       </c>
     </row>
     <row r="43">
@@ -2012,22 +2012,22 @@
         <v>2859.994</v>
       </c>
       <c r="C43" t="n">
-        <v>1764.535</v>
+        <v>2185.495</v>
       </c>
       <c r="D43" t="n">
         <v>98.00360000000001</v>
       </c>
       <c r="E43" t="n">
-        <v>69.08410000000001</v>
+        <v>88.9641</v>
       </c>
       <c r="F43" t="n">
-        <v>1495.6492</v>
+        <v>1527.7492</v>
       </c>
       <c r="G43" t="n">
         <v>1655.204</v>
       </c>
       <c r="H43" t="n">
-        <v>52.2265</v>
+        <v>53.9965</v>
       </c>
     </row>
     <row r="44">
@@ -2038,16 +2038,16 @@
         <v>1778.2807</v>
       </c>
       <c r="C44" t="n">
-        <v>2574.4949</v>
+        <v>2802.6249</v>
       </c>
       <c r="D44" t="n">
         <v>261.6238</v>
       </c>
       <c r="E44" t="n">
-        <v>75.81610000000001</v>
+        <v>102.2361</v>
       </c>
       <c r="F44" t="n">
-        <v>907.9151999999999</v>
+        <v>911.0952</v>
       </c>
       <c r="G44" t="n">
         <v>2065.1</v>
@@ -2064,13 +2064,13 @@
         <v>866.3856</v>
       </c>
       <c r="C45" t="n">
-        <v>2611.3372</v>
+        <v>2677.9972</v>
       </c>
       <c r="D45" t="n">
         <v>218.0394</v>
       </c>
       <c r="E45" t="n">
-        <v>86.02460000000001</v>
+        <v>117.4346</v>
       </c>
       <c r="F45" t="n">
         <v>1964.1186</v>
@@ -2090,22 +2090,22 @@
         <v>1883.3866</v>
       </c>
       <c r="C46" t="n">
-        <v>1696.7348</v>
+        <v>1845.7048</v>
       </c>
       <c r="D46" t="n">
         <v>173.5375</v>
       </c>
       <c r="E46" t="n">
-        <v>84.71539999999999</v>
+        <v>118.7854</v>
       </c>
       <c r="F46" t="n">
-        <v>1151.5622</v>
+        <v>1153.0622</v>
       </c>
       <c r="G46" t="n">
         <v>1846.937</v>
       </c>
       <c r="H46" t="n">
-        <v>78.88380000000001</v>
+        <v>78.9038</v>
       </c>
     </row>
     <row r="47">
@@ -2588,7 +2588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP64"/>
+  <dimension ref="A1:AR64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2754,50 +2754,60 @@
       </c>
       <c r="AG1" t="inlineStr">
         <is>
+          <t>KE_IPP_Oil_MWh</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>KE_IPP_Gas_MWh</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>KE_IPP_Coal_MWh</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>KE_IPP_Nuclear_MWh</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>KE_IPP_Solar_MWh</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>KE_from_CPPA_MWh</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
           <t>KE_own_Oil_MWh</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>KE_own_Gas_MWh</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>KE_own_RLNG_MWh</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
-        <is>
-          <t>KE_IPP_Oil_MWh</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>KE_IPP_Gas_MWh</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
-        <is>
-          <t>KE_IPP_Coal_MWh</t>
-        </is>
-      </c>
-      <c r="AM1" t="inlineStr">
-        <is>
-          <t>KE_IPP_Solar_MWh</t>
-        </is>
-      </c>
-      <c r="AN1" t="inlineStr">
-        <is>
-          <t>KE_from_CPPA_MWh</t>
-        </is>
-      </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>KE_own_decision_MWh</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>KE_own_MWh</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>KE_purchases_nonCPPA_MWh</t>
         </is>
@@ -3248,7 +3258,7 @@
       <c r="AF6" t="n">
         <v>1131000</v>
       </c>
-      <c r="AO6" t="n">
+      <c r="AQ6" t="n">
         <v>960000</v>
       </c>
     </row>
@@ -3260,22 +3270,22 @@
         <v>4695760</v>
       </c>
       <c r="C7" t="n">
-        <v>2383330</v>
+        <v>2422934</v>
       </c>
       <c r="D7" t="n">
-        <v>5353890</v>
+        <v>5426259</v>
       </c>
       <c r="E7" t="n">
-        <v>1735750</v>
+        <v>1848323</v>
       </c>
       <c r="F7" t="n">
-        <v>1659860</v>
+        <v>1702438</v>
       </c>
       <c r="G7" t="n">
         <v>550370</v>
       </c>
       <c r="H7" t="n">
-        <v>61820</v>
+        <v>74880</v>
       </c>
       <c r="I7" t="n">
         <v>45020</v>
@@ -3284,7 +3294,7 @@
         <v>9880</v>
       </c>
       <c r="K7" t="n">
-        <v>16495680</v>
+        <v>16775864</v>
       </c>
       <c r="L7" t="n">
         <v>40090</v>
@@ -3333,7 +3343,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>own: NEPRA KE decision, no fuel split (counted as gas); IPP purchases: no figure</t>
+          <t>own: NEPRA KE decision, no fuel split (counted as gas); IPP purchases by fuel: NEPRA State of Industry Report</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -3343,10 +3353,31 @@
         <v>854000</v>
       </c>
       <c r="AF7" t="n">
-        <v>1113000</v>
-      </c>
-      <c r="AO7" t="n">
+        <v>1112860</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>112573</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>72369</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>39604</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>42578</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>13060</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>832677</v>
+      </c>
+      <c r="AQ7" t="n">
         <v>854000</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>280184</v>
       </c>
     </row>
     <row r="8">
@@ -3445,13 +3476,13 @@
         <v>5085480</v>
       </c>
       <c r="C9" t="n">
-        <v>2392520</v>
+        <v>2419161</v>
       </c>
       <c r="D9" t="n">
-        <v>4803230</v>
+        <v>4874847</v>
       </c>
       <c r="E9" t="n">
-        <v>999780</v>
+        <v>1153290</v>
       </c>
       <c r="F9" t="n">
         <v>1281800</v>
@@ -3460,7 +3491,7 @@
         <v>230400</v>
       </c>
       <c r="H9" t="n">
-        <v>60750</v>
+        <v>74987</v>
       </c>
       <c r="I9" t="n">
         <v>16480</v>
@@ -3469,7 +3500,7 @@
         <v>16180</v>
       </c>
       <c r="K9" t="n">
-        <v>14886620</v>
+        <v>15152625</v>
       </c>
       <c r="L9" t="n">
         <v>48270</v>
@@ -3518,7 +3549,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>own: NEPRA KE decision, no fuel split (counted as gas); IPP purchases: no figure</t>
+          <t>own: NEPRA KE decision, no fuel split (counted as gas); IPP purchases by fuel: NEPRA State of Industry Report</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -3528,10 +3559,31 @@
         <v>903000</v>
       </c>
       <c r="AF9" t="n">
-        <v>1019000</v>
-      </c>
-      <c r="AO9" t="n">
+        <v>1018610</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>153510</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>71617</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>26641</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>14237</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>752604</v>
+      </c>
+      <c r="AQ9" t="n">
         <v>903000</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>266005</v>
       </c>
     </row>
     <row r="10">
@@ -3542,13 +3594,13 @@
         <v>2627250</v>
       </c>
       <c r="C10" t="n">
-        <v>1885780</v>
+        <v>1923456</v>
       </c>
       <c r="D10" t="n">
-        <v>4554130</v>
+        <v>4624733</v>
       </c>
       <c r="E10" t="n">
-        <v>1285760</v>
+        <v>1406950</v>
       </c>
       <c r="F10" t="n">
         <v>1392920</v>
@@ -3557,7 +3609,7 @@
         <v>184820</v>
       </c>
       <c r="H10" t="n">
-        <v>63170</v>
+        <v>79365</v>
       </c>
       <c r="I10" t="n">
         <v>7140</v>
@@ -3566,7 +3618,7 @@
         <v>11870</v>
       </c>
       <c r="K10" t="n">
-        <v>12012840</v>
+        <v>12258504</v>
       </c>
       <c r="L10" t="n">
         <v>41410</v>
@@ -3615,7 +3667,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>own: NEPRA KE decision, no fuel split (counted as gas); IPP purchases: no figure</t>
+          <t>own: NEPRA KE decision, no fuel split (counted as gas); IPP purchases by fuel: NEPRA State of Industry Report</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -3625,10 +3677,31 @@
         <v>758000</v>
       </c>
       <c r="AF10" t="n">
-        <v>1019000</v>
-      </c>
-      <c r="AO10" t="n">
+        <v>1018840</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>121190</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>70603</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>37676</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>16195</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>773176</v>
+      </c>
+      <c r="AQ10" t="n">
         <v>758000</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>245664</v>
       </c>
     </row>
     <row r="11">
@@ -3639,13 +3712,13 @@
         <v>2816490</v>
       </c>
       <c r="C11" t="n">
-        <v>1379120</v>
+        <v>1418165</v>
       </c>
       <c r="D11" t="n">
-        <v>2766860</v>
+        <v>2827973</v>
       </c>
       <c r="E11" t="n">
-        <v>170390</v>
+        <v>263250</v>
       </c>
       <c r="F11" t="n">
         <v>1485190</v>
@@ -3654,7 +3727,7 @@
         <v>175190</v>
       </c>
       <c r="H11" t="n">
-        <v>50620</v>
+        <v>65022</v>
       </c>
       <c r="I11" t="n">
         <v>54330</v>
@@ -3663,7 +3736,7 @@
         <v>11840</v>
       </c>
       <c r="K11" t="n">
-        <v>8910030</v>
+        <v>9117450</v>
       </c>
       <c r="L11" t="n">
         <v>36690</v>
@@ -3712,7 +3785,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>own: NEPRA KE decision, no fuel split (counted as gas); IPP purchases: no figure</t>
+          <t>own: NEPRA KE decision, no fuel split (counted as gas); IPP purchases by fuel: NEPRA State of Industry Report</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -3722,10 +3795,31 @@
         <v>463000</v>
       </c>
       <c r="AF11" t="n">
-        <v>943000</v>
-      </c>
-      <c r="AO11" t="n">
+        <v>942590</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>92860</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>61113</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>39045</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>14402</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>735165</v>
+      </c>
+      <c r="AQ11" t="n">
         <v>463000</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>207420</v>
       </c>
     </row>
     <row r="12">
@@ -3736,13 +3830,13 @@
         <v>1768840</v>
       </c>
       <c r="C12" t="n">
-        <v>2103650</v>
+        <v>2137818</v>
       </c>
       <c r="D12" t="n">
-        <v>2708360</v>
+        <v>2764713</v>
       </c>
       <c r="E12" t="n">
-        <v>603820</v>
+        <v>661041</v>
       </c>
       <c r="F12" t="n">
         <v>1549060</v>
@@ -3751,7 +3845,7 @@
         <v>210080</v>
       </c>
       <c r="H12" t="n">
-        <v>45180</v>
+        <v>58227</v>
       </c>
       <c r="I12" t="n">
         <v>98470</v>
@@ -3760,7 +3854,7 @@
         <v>7880</v>
       </c>
       <c r="K12" t="n">
-        <v>9095340</v>
+        <v>9256129</v>
       </c>
       <c r="L12" t="n">
         <v>36470</v>
@@ -3809,7 +3903,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>own: NEPRA KE decision, no fuel split (counted as gas); IPP purchases: no figure</t>
+          <t>own: NEPRA KE decision, no fuel split (counted as gas); IPP purchases by fuel: NEPRA State of Industry Report</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -3819,10 +3913,31 @@
         <v>301000</v>
       </c>
       <c r="AF12" t="n">
-        <v>871000</v>
-      </c>
-      <c r="AO12" t="n">
+        <v>870540</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>57221</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>56353</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>34168</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>13047</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>709747</v>
+      </c>
+      <c r="AQ12" t="n">
         <v>301000</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>160789</v>
       </c>
     </row>
     <row r="13">
@@ -3833,13 +3948,13 @@
         <v>512930</v>
       </c>
       <c r="C13" t="n">
-        <v>2916700</v>
+        <v>2919919</v>
       </c>
       <c r="D13" t="n">
-        <v>2131440</v>
+        <v>2176616</v>
       </c>
       <c r="E13" t="n">
-        <v>1830080</v>
+        <v>1926543</v>
       </c>
       <c r="F13" t="n">
         <v>1264570</v>
@@ -3848,7 +3963,7 @@
         <v>194880</v>
       </c>
       <c r="H13" t="n">
-        <v>46580</v>
+        <v>60800</v>
       </c>
       <c r="I13" t="n">
         <v>107130</v>
@@ -3857,7 +3972,7 @@
         <v>2300</v>
       </c>
       <c r="K13" t="n">
-        <v>9006610</v>
+        <v>9165688</v>
       </c>
       <c r="L13" t="n">
         <v>31650</v>
@@ -3906,7 +4021,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>own: NEPRA KE decision, no fuel split (counted as gas); IPP purchases: no figure</t>
+          <t>own: NEPRA KE decision, no fuel split (counted as gas); IPP purchases by fuel: NEPRA State of Industry Report</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -3916,10 +4031,31 @@
         <v>241000</v>
       </c>
       <c r="AF13" t="n">
-        <v>853000</v>
-      </c>
-      <c r="AO13" t="n">
+        <v>852980</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>96463</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>45176</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>3219</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>14220</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>693899</v>
+      </c>
+      <c r="AQ13" t="n">
         <v>241000</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>159078</v>
       </c>
     </row>
     <row r="14">
@@ -3930,13 +4066,13 @@
         <v>1703910</v>
       </c>
       <c r="C14" t="n">
-        <v>2586620</v>
+        <v>2620343</v>
       </c>
       <c r="D14" t="n">
-        <v>3549400</v>
+        <v>3619889</v>
       </c>
       <c r="E14" t="n">
-        <v>1106190</v>
+        <v>1244061</v>
       </c>
       <c r="F14" t="n">
         <v>1563660</v>
@@ -3945,7 +4081,7 @@
         <v>267920</v>
       </c>
       <c r="H14" t="n">
-        <v>68730</v>
+        <v>88294</v>
       </c>
       <c r="I14" t="n">
         <v>107010</v>
@@ -3954,7 +4090,7 @@
         <v>13220</v>
       </c>
       <c r="K14" t="n">
-        <v>10966660</v>
+        <v>11228307</v>
       </c>
       <c r="L14" t="n">
         <v>42750</v>
@@ -4003,7 +4139,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>own: NEPRA KE decision, no fuel split (counted as gas); IPP purchases: no figure</t>
+          <t>own: NEPRA KE decision, no fuel split (counted as gas); IPP purchases by fuel: NEPRA State of Industry Report</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -4013,10 +4149,31 @@
         <v>591000</v>
       </c>
       <c r="AF14" t="n">
-        <v>1038000</v>
-      </c>
-      <c r="AO14" t="n">
+        <v>1038210</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>137871</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>70489</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>33723</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>19564</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>776560</v>
+      </c>
+      <c r="AQ14" t="n">
         <v>591000</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>261647</v>
       </c>
     </row>
     <row r="15">
@@ -4027,13 +4184,13 @@
         <v>2404350</v>
       </c>
       <c r="C15" t="n">
-        <v>2168930</v>
+        <v>2207913</v>
       </c>
       <c r="D15" t="n">
-        <v>4684420</v>
+        <v>4758582</v>
       </c>
       <c r="E15" t="n">
-        <v>1622600</v>
+        <v>1783355</v>
       </c>
       <c r="F15" t="n">
         <v>2251190</v>
@@ -4042,7 +4199,7 @@
         <v>464780</v>
       </c>
       <c r="H15" t="n">
-        <v>87310</v>
+        <v>103163</v>
       </c>
       <c r="I15" t="n">
         <v>106490</v>
@@ -4051,7 +4208,7 @@
         <v>9380</v>
       </c>
       <c r="K15" t="n">
-        <v>13799450</v>
+        <v>14089203</v>
       </c>
       <c r="L15" t="n">
         <v>51950</v>
@@ -4100,7 +4257,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>own: NEPRA KE decision, no fuel split (counted as gas); IPP purchases: no figure</t>
+          <t>own: NEPRA KE decision, no fuel split (counted as gas); IPP purchases by fuel: NEPRA State of Industry Report</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -4110,10 +4267,31 @@
         <v>891000</v>
       </c>
       <c r="AF15" t="n">
-        <v>1035000</v>
-      </c>
-      <c r="AO15" t="n">
+        <v>1035420</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>160755</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>74162</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>38983</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>15853</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>745668</v>
+      </c>
+      <c r="AQ15" t="n">
         <v>891000</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>289753</v>
       </c>
     </row>
     <row r="16">
@@ -4212,13 +4390,13 @@
         <v>3361210</v>
       </c>
       <c r="C17" t="n">
-        <v>1883130</v>
+        <v>1922229</v>
       </c>
       <c r="D17" t="n">
-        <v>5402175.1</v>
+        <v>5465565.1</v>
       </c>
       <c r="E17" t="n">
-        <v>1842654.9</v>
+        <v>1993396.9</v>
       </c>
       <c r="F17" t="n">
         <v>1265670</v>
@@ -4227,7 +4405,7 @@
         <v>811590</v>
       </c>
       <c r="H17" t="n">
-        <v>86270</v>
+        <v>103672</v>
       </c>
       <c r="I17" t="n">
         <v>83010</v>
@@ -4236,7 +4414,7 @@
         <v>9870</v>
       </c>
       <c r="K17" t="n">
-        <v>14745580</v>
+        <v>15016213</v>
       </c>
       <c r="L17" t="n">
         <v>51490</v>
@@ -4285,26 +4463,47 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>own: NEPRA KE decision, by fuel from KE's filing; IPP purchases: no figure</t>
+          <t>own: NEPRA KE decision, by fuel from KE's filing; IPP purchases by fuel: NEPRA State of Industry Report</t>
         </is>
       </c>
       <c r="AD17" t="b">
         <v>1</v>
       </c>
       <c r="AF17" t="n">
-        <v>1034000</v>
+        <v>1033350</v>
       </c>
       <c r="AG17" t="n">
+        <v>150742</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>63390</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>39099</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>17402</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>762717</v>
+      </c>
+      <c r="AM17" t="n">
         <v>388674.9</v>
       </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="n">
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
         <v>532325.1</v>
       </c>
-      <c r="AO17" t="n">
+      <c r="AQ17" t="n">
         <v>921000</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>270633</v>
       </c>
     </row>
     <row r="18">
@@ -4315,13 +4514,13 @@
         <v>4976930</v>
       </c>
       <c r="C18" t="n">
-        <v>1802190</v>
+        <v>1837460</v>
       </c>
       <c r="D18" t="n">
-        <v>4377960</v>
+        <v>4448460</v>
       </c>
       <c r="E18" t="n">
-        <v>1082890</v>
+        <v>1196340</v>
       </c>
       <c r="F18" t="n">
         <v>2009540</v>
@@ -4330,7 +4529,7 @@
         <v>521720</v>
       </c>
       <c r="H18" t="n">
-        <v>70770</v>
+        <v>83820</v>
       </c>
       <c r="I18" t="n">
         <v>40630</v>
@@ -4339,7 +4538,7 @@
         <v>16920</v>
       </c>
       <c r="K18" t="n">
-        <v>14899550</v>
+        <v>15131820</v>
       </c>
       <c r="L18" t="n">
         <v>46570</v>
@@ -4388,7 +4587,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>own: NEPRA KE decision, no fuel split (counted as gas); IPP purchases: no figure</t>
+          <t>own: NEPRA KE decision, no fuel split (counted as gas); IPP purchases by fuel: NEPRA State of Industry Report</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -4398,10 +4597,28 @@
         <v>792000</v>
       </c>
       <c r="AF18" t="n">
-        <v>1006000</v>
-      </c>
-      <c r="AO18" t="n">
+        <v>1005520</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>113450</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>70500</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>35270</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>13050</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>773250</v>
+      </c>
+      <c r="AQ18" t="n">
         <v>792000</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>232270</v>
       </c>
     </row>
     <row r="19">
@@ -4412,13 +4629,13 @@
         <v>5353690</v>
       </c>
       <c r="C19" t="n">
-        <v>2163010</v>
+        <v>2203280</v>
       </c>
       <c r="D19" t="n">
-        <v>3741010</v>
+        <v>3803520</v>
       </c>
       <c r="E19" t="n">
-        <v>1021590</v>
+        <v>1156480</v>
       </c>
       <c r="F19" t="n">
         <v>1873980</v>
@@ -4427,7 +4644,7 @@
         <v>390710</v>
       </c>
       <c r="H19" t="n">
-        <v>73440</v>
+        <v>85200</v>
       </c>
       <c r="I19" t="n">
         <v>33130</v>
@@ -4436,7 +4653,7 @@
         <v>17780</v>
       </c>
       <c r="K19" t="n">
-        <v>14668340</v>
+        <v>14917770</v>
       </c>
       <c r="L19" t="n">
         <v>54470</v>
@@ -4485,7 +4702,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>own: NEPRA KE decision, no fuel split (counted as gas); IPP purchases: no figure</t>
+          <t>own: NEPRA KE decision, no fuel split (counted as gas); IPP purchases by fuel: NEPRA State of Industry Report</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -4495,10 +4712,28 @@
         <v>670000</v>
       </c>
       <c r="AF19" t="n">
-        <v>1044000</v>
-      </c>
-      <c r="AO19" t="n">
+        <v>1044350</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>134890</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>62510</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>40270</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>11760</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>794940</v>
+      </c>
+      <c r="AQ19" t="n">
         <v>670000</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>249430</v>
       </c>
     </row>
     <row r="20">
@@ -4509,13 +4744,13 @@
         <v>3143620</v>
       </c>
       <c r="C20" t="n">
-        <v>1656520</v>
+        <v>1695350</v>
       </c>
       <c r="D20" t="n">
-        <v>3803110</v>
+        <v>3866350</v>
       </c>
       <c r="E20" t="n">
-        <v>156570</v>
+        <v>276280</v>
       </c>
       <c r="F20" t="n">
         <v>2206330</v>
@@ -4524,7 +4759,7 @@
         <v>209700</v>
       </c>
       <c r="H20" t="n">
-        <v>79080</v>
+        <v>98080</v>
       </c>
       <c r="I20" t="n">
         <v>37810</v>
@@ -4533,7 +4768,7 @@
         <v>14770</v>
       </c>
       <c r="K20" t="n">
-        <v>11307510</v>
+        <v>11548290</v>
       </c>
       <c r="L20" t="n">
         <v>47770</v>
@@ -4582,7 +4817,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>own: NEPRA KE decision, no fuel split (counted as gas); IPP purchases: no figure</t>
+          <t>own: NEPRA KE decision, no fuel split (counted as gas); IPP purchases by fuel: NEPRA State of Industry Report</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -4592,10 +4827,28 @@
         <v>663000</v>
       </c>
       <c r="AF20" t="n">
-        <v>1013000</v>
-      </c>
-      <c r="AO20" t="n">
+        <v>1013240</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>119710</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>63240</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>38830</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>19000</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>772460</v>
+      </c>
+      <c r="AQ20" t="n">
         <v>663000</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>240780</v>
       </c>
     </row>
     <row r="21">
@@ -4606,13 +4859,13 @@
         <v>1720430</v>
       </c>
       <c r="C21" t="n">
-        <v>1520930</v>
+        <v>1545430</v>
       </c>
       <c r="D21" t="n">
-        <v>2758530</v>
+        <v>2801370</v>
       </c>
       <c r="E21" t="n">
-        <v>38910</v>
+        <v>78250</v>
       </c>
       <c r="F21" t="n">
         <v>2284860</v>
@@ -4621,7 +4874,7 @@
         <v>211570</v>
       </c>
       <c r="H21" t="n">
-        <v>69460</v>
+        <v>86320</v>
       </c>
       <c r="I21" t="n">
         <v>101090</v>
@@ -4630,7 +4883,7 @@
         <v>2180</v>
       </c>
       <c r="K21" t="n">
-        <v>8707960</v>
+        <v>8831500</v>
       </c>
       <c r="L21" t="n">
         <v>39850</v>
@@ -4679,7 +4932,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>own: NEPRA KE decision, no fuel split (counted as gas); IPP purchases: no figure</t>
+          <t>own: NEPRA KE decision, no fuel split (counted as gas); IPP purchases by fuel: NEPRA State of Industry Report</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -4689,10 +4942,28 @@
         <v>331000</v>
       </c>
       <c r="AF21" t="n">
-        <v>846000</v>
-      </c>
-      <c r="AO21" t="n">
+        <v>846180</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>39340</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>42840</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>24500</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>16860</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>722640</v>
+      </c>
+      <c r="AQ21" t="n">
         <v>331000</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>123540</v>
       </c>
     </row>
     <row r="22">
@@ -4791,13 +5062,13 @@
         <v>2052160</v>
       </c>
       <c r="C23" t="n">
-        <v>1091140</v>
+        <v>1111110</v>
       </c>
       <c r="D23" t="n">
-        <v>2607510</v>
+        <v>2653340</v>
       </c>
       <c r="E23" t="n">
-        <v>107770</v>
+        <v>163890</v>
       </c>
       <c r="F23" t="n">
         <v>1883090</v>
@@ -4806,7 +5077,7 @@
         <v>92200</v>
       </c>
       <c r="H23" t="n">
-        <v>82260</v>
+        <v>104410</v>
       </c>
       <c r="I23" t="n">
         <v>100120</v>
@@ -4815,7 +5086,7 @@
         <v>1870</v>
       </c>
       <c r="K23" t="n">
-        <v>8018120</v>
+        <v>8162190</v>
       </c>
       <c r="L23" t="n">
         <v>32950</v>
@@ -4864,7 +5135,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>own: NEPRA KE decision, no fuel split (counted as gas); IPP purchases: no figure</t>
+          <t>own: NEPRA KE decision, no fuel split (counted as gas); IPP purchases by fuel: NEPRA State of Industry Report</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -4874,10 +5145,28 @@
         <v>295000</v>
       </c>
       <c r="AF23" t="n">
-        <v>822000</v>
-      </c>
-      <c r="AO23" t="n">
+        <v>821800</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>56120</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>45830</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>19970</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>22150</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>677720</v>
+      </c>
+      <c r="AQ23" t="n">
         <v>295000</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>144070</v>
       </c>
     </row>
     <row r="24">
@@ -4888,13 +5177,13 @@
         <v>2001610</v>
       </c>
       <c r="C24" t="n">
-        <v>1333520</v>
+        <v>1369480</v>
       </c>
       <c r="D24" t="n">
-        <v>3411600</v>
+        <v>3468370</v>
       </c>
       <c r="E24" t="n">
-        <v>40520</v>
+        <v>114210</v>
       </c>
       <c r="F24" t="n">
         <v>2002010</v>
@@ -4903,7 +5192,7 @@
         <v>221330</v>
       </c>
       <c r="H24" t="n">
-        <v>110730</v>
+        <v>135300</v>
       </c>
       <c r="I24" t="n">
         <v>104860</v>
@@ -4912,7 +5201,7 @@
         <v>3560</v>
       </c>
       <c r="K24" t="n">
-        <v>9229740</v>
+        <v>9420730</v>
       </c>
       <c r="L24" t="n">
         <v>31500</v>
@@ -4961,7 +5250,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>own: NEPRA KE decision, no fuel split (counted as gas); IPP purchases: no figure</t>
+          <t>own: NEPRA KE decision, no fuel split (counted as gas); IPP purchases by fuel: NEPRA State of Industry Report</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -4973,8 +5262,26 @@
       <c r="AF24" t="n">
         <v>958000</v>
       </c>
-      <c r="AO24" t="n">
+      <c r="AG24" t="n">
+        <v>73690</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>56770</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>35960</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>24570</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>767020</v>
+      </c>
+      <c r="AQ24" t="n">
         <v>520000</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>190990</v>
       </c>
     </row>
     <row r="25">
@@ -4985,13 +5292,13 @@
         <v>1873190</v>
       </c>
       <c r="C25" t="n">
-        <v>1818730</v>
+        <v>1855480</v>
       </c>
       <c r="D25" t="n">
-        <v>4275040</v>
+        <v>4321020</v>
       </c>
       <c r="E25" t="n">
-        <v>222570</v>
+        <v>248850</v>
       </c>
       <c r="F25" t="n">
         <v>1916070</v>
@@ -5000,7 +5307,7 @@
         <v>322930</v>
       </c>
       <c r="H25" t="n">
-        <v>125800</v>
+        <v>151660</v>
       </c>
       <c r="I25" t="n">
         <v>81170</v>
@@ -5009,7 +5316,7 @@
         <v>13350</v>
       </c>
       <c r="K25" t="n">
-        <v>10648850</v>
+        <v>10783720</v>
       </c>
       <c r="L25" t="n">
         <v>30460</v>
@@ -5058,7 +5365,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>own: NEPRA KE decision, no fuel split (counted as gas); IPP purchases: no figure</t>
+          <t>own: NEPRA KE decision, no fuel split (counted as gas); IPP purchases by fuel: NEPRA State of Industry Report</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -5068,10 +5375,28 @@
         <v>666000</v>
       </c>
       <c r="AF25" t="n">
-        <v>862000</v>
-      </c>
-      <c r="AO25" t="n">
+        <v>861860</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>26280</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>45980</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>36750</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>25860</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>726990</v>
+      </c>
+      <c r="AQ25" t="n">
         <v>666000</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>134870</v>
       </c>
     </row>
     <row r="26">
@@ -5082,13 +5407,13 @@
         <v>3312200</v>
       </c>
       <c r="C26" t="n">
-        <v>2061300</v>
+        <v>2074970</v>
       </c>
       <c r="D26" t="n">
-        <v>5141950</v>
+        <v>5192610</v>
       </c>
       <c r="E26" t="n">
-        <v>240970</v>
+        <v>338340</v>
       </c>
       <c r="F26" t="n">
         <v>1542590</v>
@@ -5097,7 +5422,7 @@
         <v>606580</v>
       </c>
       <c r="H26" t="n">
-        <v>89500</v>
+        <v>114780</v>
       </c>
       <c r="I26" t="n">
         <v>74870</v>
@@ -5106,7 +5431,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>13069960</v>
+        <v>13256940</v>
       </c>
       <c r="L26" t="n">
         <v>34500</v>
@@ -5155,7 +5480,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>own: NEPRA KE decision, no fuel split (counted as gas); IPP purchases: no figure</t>
+          <t>own: NEPRA KE decision, no fuel split (counted as gas); IPP purchases by fuel: NEPRA State of Industry Report</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -5165,10 +5490,28 @@
         <v>883000</v>
       </c>
       <c r="AF26" t="n">
-        <v>978000</v>
-      </c>
-      <c r="AO26" t="n">
+        <v>977520</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>97370</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>50660</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>13670</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>25280</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>790540</v>
+      </c>
+      <c r="AQ26" t="n">
         <v>883000</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>186980</v>
       </c>
     </row>
     <row r="27">
@@ -5267,13 +5610,13 @@
         <v>5517770</v>
       </c>
       <c r="C28" t="n">
-        <v>2179890</v>
+        <v>2195060</v>
       </c>
       <c r="D28" t="n">
-        <v>4046810</v>
+        <v>4967980</v>
       </c>
       <c r="E28" t="n">
-        <v>293806.7</v>
+        <v>464436.7</v>
       </c>
       <c r="F28" t="n">
         <v>2106930</v>
@@ -5282,7 +5625,7 @@
         <v>548760</v>
       </c>
       <c r="H28" t="n">
-        <v>75190</v>
+        <v>92640</v>
       </c>
       <c r="I28" t="n">
         <v>39970</v>
@@ -5291,7 +5634,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>14809126.7</v>
+        <v>15933546.7</v>
       </c>
       <c r="L28" t="n">
         <v>28850</v>
@@ -5340,11 +5683,44 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>no KE figure</t>
+          <t>NEPRA State of Industry Report (KE fuel-wise monthly tables)</t>
         </is>
       </c>
       <c r="AD28" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>938840</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>89550</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>44450</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>15170</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>17450</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>772230</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>81080</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>876720</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>957800</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>166620</v>
       </c>
     </row>
     <row r="29">
@@ -5355,13 +5731,13 @@
         <v>6005500</v>
       </c>
       <c r="C29" t="n">
-        <v>2357230</v>
+        <v>2382460</v>
       </c>
       <c r="D29" t="n">
-        <v>3954200</v>
+        <v>4791000</v>
       </c>
       <c r="E29" t="n">
-        <v>649160</v>
+        <v>707910</v>
       </c>
       <c r="F29" t="n">
         <v>2040450</v>
@@ -5370,7 +5746,7 @@
         <v>804700</v>
       </c>
       <c r="H29" t="n">
-        <v>84070</v>
+        <v>96810</v>
       </c>
       <c r="I29" t="n">
         <v>37760</v>
@@ -5379,7 +5755,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>15933070</v>
+        <v>16866590</v>
       </c>
       <c r="L29" t="n">
         <v>26200</v>
@@ -5434,11 +5810,44 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>no KE figure</t>
+          <t>NEPRA State of Industry Report (KE fuel-wise monthly tables)</t>
         </is>
       </c>
       <c r="AD29" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>887300</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>49250</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>46620</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>25230</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>12740</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>753460</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>9500</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>790180</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>799680</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>133840</v>
       </c>
     </row>
     <row r="30">
@@ -5449,13 +5858,13 @@
         <v>5008520</v>
       </c>
       <c r="C30" t="n">
-        <v>2122860</v>
+        <v>2160110</v>
       </c>
       <c r="D30" t="n">
-        <v>3133080</v>
+        <v>3906760</v>
       </c>
       <c r="E30" t="n">
-        <v>240610</v>
+        <v>367370</v>
       </c>
       <c r="F30" t="n">
         <v>2286350</v>
@@ -5464,7 +5873,7 @@
         <v>410230</v>
       </c>
       <c r="H30" t="n">
-        <v>78790</v>
+        <v>97080</v>
       </c>
       <c r="I30" t="n">
         <v>34520</v>
@@ -5473,7 +5882,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>13314960</v>
+        <v>14270940</v>
       </c>
       <c r="L30" t="n">
         <v>24230</v>
@@ -5528,11 +5937,44 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>no KE figure</t>
+          <t>NEPRA State of Industry Report (KE fuel-wise monthly tables)</t>
         </is>
       </c>
       <c r="AD30" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>904800</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>96010</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>42390</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>37250</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>18290</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>710860</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>30750</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>731290</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>762040</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>193940</v>
       </c>
     </row>
     <row r="31">
@@ -5543,13 +5985,13 @@
         <v>3114140</v>
       </c>
       <c r="C31" t="n">
-        <v>1670170</v>
+        <v>1710710</v>
       </c>
       <c r="D31" t="n">
-        <v>2642490</v>
+        <v>3418170</v>
       </c>
       <c r="E31" t="n">
-        <v>70</v>
+        <v>138820</v>
       </c>
       <c r="F31" t="n">
         <v>1826260</v>
@@ -5558,7 +6000,7 @@
         <v>191140</v>
       </c>
       <c r="H31" t="n">
-        <v>76000</v>
+        <v>95740</v>
       </c>
       <c r="I31" t="n">
         <v>28760</v>
@@ -5567,7 +6009,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>9549030</v>
+        <v>10523740</v>
       </c>
       <c r="L31" t="n">
         <v>22540</v>
@@ -5622,11 +6064,44 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>no KE figure</t>
+          <t>NEPRA State of Industry Report (KE fuel-wise monthly tables)</t>
         </is>
       </c>
       <c r="AD31" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>941970</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>108370</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>61930</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>40540</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>19740</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>711400</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>30380</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>713750</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>744130</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>230580</v>
       </c>
     </row>
     <row r="32">
@@ -5637,13 +6112,13 @@
         <v>2754860</v>
       </c>
       <c r="C32" t="n">
-        <v>1473120</v>
+        <v>1509180</v>
       </c>
       <c r="D32" t="n">
-        <v>1492760</v>
+        <v>1961650</v>
       </c>
       <c r="E32" t="n">
-        <v>280</v>
+        <v>92070</v>
       </c>
       <c r="F32" t="n">
         <v>1571660</v>
@@ -5652,7 +6127,7 @@
         <v>147840</v>
       </c>
       <c r="H32" t="n">
-        <v>49780</v>
+        <v>66220</v>
       </c>
       <c r="I32" t="n">
         <v>26680</v>
@@ -5661,7 +6136,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>7516980</v>
+        <v>8130160</v>
       </c>
       <c r="L32" t="n">
         <v>29730</v>
@@ -5716,11 +6191,44 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>no KE figure</t>
+          <t>NEPRA State of Industry Report (KE fuel-wise monthly tables)</t>
         </is>
       </c>
       <c r="AD32" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>843500</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>54230</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>46980</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>36060</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>16440</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>689790</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>37560</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>43470</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>378440</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>459470</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>153710</v>
       </c>
     </row>
     <row r="33">
@@ -5731,13 +6239,13 @@
         <v>1859010</v>
       </c>
       <c r="C33" t="n">
-        <v>1693180</v>
+        <v>1721960</v>
       </c>
       <c r="D33" t="n">
-        <v>2093900</v>
+        <v>2398520</v>
       </c>
       <c r="E33" t="n">
-        <v>174530</v>
+        <v>181670</v>
       </c>
       <c r="F33" t="n">
         <v>1464430</v>
@@ -5746,7 +6254,7 @@
         <v>150370</v>
       </c>
       <c r="H33" t="n">
-        <v>61820</v>
+        <v>82020</v>
       </c>
       <c r="I33" t="n">
         <v>101240</v>
@@ -5755,7 +6263,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>7598480</v>
+        <v>7959220</v>
       </c>
       <c r="L33" t="n">
         <v>28200</v>
@@ -5810,11 +6318,44 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>no KE figure</t>
+          <t>NEPRA State of Industry Report (KE fuel-wise monthly tables)</t>
         </is>
       </c>
       <c r="AD33" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>806300</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>5940</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>41990</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>28780</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>20200</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>709390</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1200</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>262630</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>263830</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>96910</v>
       </c>
     </row>
     <row r="34">
@@ -5825,13 +6366,13 @@
         <v>924220</v>
       </c>
       <c r="C34" t="n">
-        <v>1948930</v>
+        <v>1949990</v>
       </c>
       <c r="D34" t="n">
-        <v>2549750</v>
+        <v>2850400</v>
       </c>
       <c r="E34" t="n">
-        <v>852090</v>
+        <v>898160</v>
       </c>
       <c r="F34" t="n">
         <v>1727800</v>
@@ -5840,7 +6381,7 @@
         <v>127550</v>
       </c>
       <c r="H34" t="n">
-        <v>47940</v>
+        <v>69620</v>
       </c>
       <c r="I34" t="n">
         <v>106370</v>
@@ -5849,7 +6390,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>8284650</v>
+        <v>8654110</v>
       </c>
       <c r="L34" t="n">
         <v>29090</v>
@@ -5904,11 +6445,44 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>no KE figure</t>
+          <t>NEPRA State of Industry Report (KE fuel-wise monthly tables)</t>
         </is>
       </c>
       <c r="AD34" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>782530</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>32880</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>43230</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>1060</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>21680</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>683670</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>13190</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>257420</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>270610</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>98850</v>
       </c>
     </row>
     <row r="35">
@@ -5919,13 +6493,13 @@
         <v>1766290</v>
       </c>
       <c r="C35" t="n">
-        <v>1128710</v>
+        <v>1132980</v>
       </c>
       <c r="D35" t="n">
-        <v>2236820</v>
+        <v>2602990</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>20420</v>
       </c>
       <c r="F35" t="n">
         <v>1660250</v>
@@ -5934,7 +6508,7 @@
         <v>107633.5</v>
       </c>
       <c r="H35" t="n">
-        <v>90170</v>
+        <v>113860</v>
       </c>
       <c r="I35" t="n">
         <v>100530</v>
@@ -5943,7 +6517,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>7090403.5</v>
+        <v>7504953.5</v>
       </c>
       <c r="L35" t="n">
         <v>25660</v>
@@ -5995,11 +6569,44 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>no KE figure</t>
+          <t>NEPRA State of Industry Report (KE fuel-wise monthly tables)</t>
         </is>
       </c>
       <c r="AD35" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>699690</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>11190</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>46660</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>4270</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>23690</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>613890</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>9230</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>4500</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>315010</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>328740</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>85810</v>
       </c>
     </row>
     <row r="36">
@@ -6010,13 +6617,13 @@
         <v>2216810</v>
       </c>
       <c r="C36" t="n">
-        <v>861770</v>
+        <v>890300</v>
       </c>
       <c r="D36" t="n">
-        <v>2453520</v>
+        <v>2953520</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>22460</v>
       </c>
       <c r="F36" t="n">
         <v>2069600</v>
@@ -6025,7 +6632,7 @@
         <v>204700</v>
       </c>
       <c r="H36" t="n">
-        <v>109980</v>
+        <v>141470</v>
       </c>
       <c r="I36" t="n">
         <v>78500</v>
@@ -6034,7 +6641,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>7994880</v>
+        <v>8577360</v>
       </c>
       <c r="L36" t="n">
         <v>28380</v>
@@ -6089,11 +6696,44 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>no KE figure</t>
+          <t>NEPRA State of Industry Report (KE fuel-wise monthly tables)</t>
         </is>
       </c>
       <c r="AD36" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>824770</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>8770</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>53480</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>28530</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>31490</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>702500</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>13690</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>13410</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>433110</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>460210</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>122270</v>
       </c>
     </row>
     <row r="37">
@@ -6104,13 +6744,13 @@
         <v>3906270</v>
       </c>
       <c r="C37" t="n">
-        <v>1754270</v>
+        <v>1793560</v>
       </c>
       <c r="D37" t="n">
-        <v>4745630</v>
+        <v>4764040</v>
       </c>
       <c r="E37" t="n">
-        <v>61940</v>
+        <v>164780</v>
       </c>
       <c r="F37" t="n">
         <v>2360020</v>
@@ -6119,7 +6759,7 @@
         <v>445440</v>
       </c>
       <c r="H37" t="n">
-        <v>124870</v>
+        <v>157170</v>
       </c>
       <c r="I37" t="n">
         <v>56940</v>
@@ -6128,7 +6768,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>13455380</v>
+        <v>13648220</v>
       </c>
       <c r="L37" t="n">
         <v>49960</v>
@@ -6183,20 +6823,47 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>own: NEPRA KE decision, no fuel split (counted as gas); IPP purchases: no figure</t>
+          <t>NEPRA State of Industry Report (KE fuel-wise monthly tables)</t>
         </is>
       </c>
       <c r="AD37" t="b">
         <v>1</v>
       </c>
-      <c r="AE37" t="n">
+      <c r="AF37" t="n">
+        <v>951200</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>58850</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>62890</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>39290</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>32300</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>757880</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>43990</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>36290</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>808230</v>
+      </c>
+      <c r="AP37" t="n">
         <v>889000</v>
       </c>
-      <c r="AF37" t="n">
-        <v>951000</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>889000</v>
+      <c r="AQ37" t="n">
+        <v>888510</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>193330</v>
       </c>
     </row>
     <row r="38">
@@ -6207,13 +6874,13 @@
         <v>4728500</v>
       </c>
       <c r="C38" t="n">
-        <v>2126070</v>
+        <v>2163750</v>
       </c>
       <c r="D38" t="n">
-        <v>4559230</v>
+        <v>4552520</v>
       </c>
       <c r="E38" t="n">
-        <v>262960</v>
+        <v>374270</v>
       </c>
       <c r="F38" t="n">
         <v>1998390</v>
@@ -6222,7 +6889,7 @@
         <v>515730</v>
       </c>
       <c r="H38" t="n">
-        <v>117540</v>
+        <v>139490</v>
       </c>
       <c r="I38" t="n">
         <v>59740</v>
@@ -6231,7 +6898,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>14368160</v>
+        <v>14532390</v>
       </c>
       <c r="L38" t="n">
         <v>47650</v>
@@ -6286,20 +6953,47 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>own: NEPRA KE decision, no fuel split (counted as gas); IPP purchases: no figure</t>
+          <t>NEPRA State of Industry Report (KE fuel-wise monthly tables)</t>
         </is>
       </c>
       <c r="AD38" t="b">
         <v>1</v>
       </c>
-      <c r="AE38" t="n">
+      <c r="AF38" t="n">
+        <v>887410</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>40780</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>64240</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>37680</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>21950</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>722760</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>70530</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>40030</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>845020</v>
+      </c>
+      <c r="AP38" t="n">
         <v>956000</v>
       </c>
-      <c r="AF38" t="n">
-        <v>887000</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>956000</v>
+      <c r="AQ38" t="n">
+        <v>955580</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>164650</v>
       </c>
     </row>
     <row r="39">
@@ -6313,10 +7007,10 @@
         <v>2681395.4</v>
       </c>
       <c r="D39" t="n">
-        <v>5134606.1</v>
+        <v>5134450.9</v>
       </c>
       <c r="E39" t="n">
-        <v>289142</v>
+        <v>289117.3</v>
       </c>
       <c r="F39" t="n">
         <v>1987716</v>
@@ -6334,7 +7028,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>16060151.2</v>
+        <v>16059971.3</v>
       </c>
       <c r="L39" t="n">
         <v>47761.8</v>
@@ -6389,43 +7083,46 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>own: NEPRA KE decision, by fuel from KE's filing; IPP purchases by fuel: KE's filing</t>
+          <t>NEPRA State of Industry Report (KE fuel-wise monthly tables)</t>
         </is>
       </c>
       <c r="AD39" t="b">
         <v>1</v>
       </c>
       <c r="AF39" t="n">
-        <v>935000</v>
+        <v>934960</v>
       </c>
       <c r="AG39" t="n">
-        <v>147844.7</v>
+        <v>39200</v>
       </c>
       <c r="AH39" t="n">
-        <v>41536.9</v>
+        <v>56610</v>
       </c>
       <c r="AI39" t="n">
-        <v>886618.3</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>39200</v>
+        <v>38570</v>
       </c>
       <c r="AK39" t="n">
-        <v>56610</v>
+        <v>17200</v>
       </c>
       <c r="AL39" t="n">
-        <v>38570</v>
+        <v>783380</v>
       </c>
       <c r="AM39" t="n">
-        <v>17200</v>
+        <v>147820</v>
       </c>
       <c r="AN39" t="n">
-        <v>783380</v>
+        <v>41530</v>
       </c>
       <c r="AO39" t="n">
-        <v>1075999.9</v>
+        <v>886470</v>
       </c>
       <c r="AP39" t="n">
+        <v>1076000</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>1075820</v>
+      </c>
+      <c r="AR39" t="n">
         <v>151580</v>
       </c>
     </row>
@@ -6437,13 +7134,13 @@
         <v>5361562.6</v>
       </c>
       <c r="C40" t="n">
-        <v>1986352.9</v>
+        <v>2022672.9</v>
       </c>
       <c r="D40" t="n">
-        <v>3861900.8</v>
+        <v>3907540.8</v>
       </c>
       <c r="E40" t="n">
-        <v>5663.2</v>
+        <v>29783.2</v>
       </c>
       <c r="F40" t="n">
         <v>2190305</v>
@@ -6452,7 +7149,7 @@
         <v>398253.9</v>
       </c>
       <c r="H40" t="n">
-        <v>98373.3</v>
+        <v>110773.3</v>
       </c>
       <c r="I40" t="n">
         <v>46709.4</v>
@@ -6461,7 +7158,7 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>13949121.1</v>
+        <v>14067601.1</v>
       </c>
       <c r="L40" t="n">
         <v>35774.1</v>
@@ -6516,20 +7213,47 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>own: NEPRA KE decision, no fuel split (counted as gas); IPP purchases: no figure</t>
+          <t>NEPRA State of Industry Report (KE fuel-wise monthly tables)</t>
         </is>
       </c>
       <c r="AD40" t="b">
         <v>1</v>
       </c>
-      <c r="AE40" t="n">
+      <c r="AF40" t="n">
+        <v>873990</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>10700</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>59080</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>36320</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>12400</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>755490</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>13420</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>39830</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>752730</v>
+      </c>
+      <c r="AP40" t="n">
         <v>806000</v>
       </c>
-      <c r="AF40" t="n">
-        <v>874000</v>
-      </c>
-      <c r="AO40" t="n">
-        <v>806000</v>
+      <c r="AQ40" t="n">
+        <v>805980</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>118500</v>
       </c>
     </row>
     <row r="41">
@@ -6543,10 +7267,10 @@
         <v>2445144.2</v>
       </c>
       <c r="D41" t="n">
-        <v>3770075.5</v>
+        <v>3769652.4</v>
       </c>
       <c r="E41" t="n">
-        <v>77541.89999999999</v>
+        <v>77525</v>
       </c>
       <c r="F41" t="n">
         <v>1595672</v>
@@ -6564,7 +7288,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>13283651.6</v>
+        <v>13283211.6</v>
       </c>
       <c r="L41" t="n">
         <v>40294.6</v>
@@ -6619,7 +7343,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>own: NEPRA KE decision, by fuel from KE's filing; IPP purchases by fuel: KE's filing</t>
+          <t>NEPRA State of Industry Report (KE fuel-wise monthly tables)</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6629,33 +7353,36 @@
         <v>851000</v>
       </c>
       <c r="AG41" t="n">
-        <v>27606.9</v>
+        <v>10750</v>
       </c>
       <c r="AH41" t="n">
-        <v>27857</v>
+        <v>50330</v>
       </c>
       <c r="AI41" t="n">
-        <v>664536.1</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>10750</v>
+        <v>35020</v>
       </c>
       <c r="AK41" t="n">
-        <v>50330</v>
+        <v>21260</v>
       </c>
       <c r="AL41" t="n">
-        <v>35020</v>
+        <v>733650</v>
       </c>
       <c r="AM41" t="n">
-        <v>21260</v>
+        <v>27590</v>
       </c>
       <c r="AN41" t="n">
-        <v>733650</v>
+        <v>27840</v>
       </c>
       <c r="AO41" t="n">
+        <v>664130</v>
+      </c>
+      <c r="AP41" t="n">
         <v>720000</v>
       </c>
-      <c r="AP41" t="n">
+      <c r="AQ41" t="n">
+        <v>719560</v>
+      </c>
+      <c r="AR41" t="n">
         <v>117360</v>
       </c>
     </row>
@@ -6667,13 +7394,13 @@
         <v>3187387</v>
       </c>
       <c r="C42" t="n">
-        <v>2420794.4</v>
+        <v>2460294.4</v>
       </c>
       <c r="D42" t="n">
-        <v>3617963.1</v>
+        <v>3661674.8</v>
       </c>
       <c r="E42" t="n">
-        <v>14591.6</v>
+        <v>28179.9</v>
       </c>
       <c r="F42" t="n">
         <v>1441938</v>
@@ -6682,7 +7409,7 @@
         <v>189980.9</v>
       </c>
       <c r="H42" t="n">
-        <v>99066.7</v>
+        <v>122576.7</v>
       </c>
       <c r="I42" t="n">
         <v>50265.4</v>
@@ -6691,7 +7418,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>11021987.1</v>
+        <v>11142297.1</v>
       </c>
       <c r="L42" t="n">
         <v>42382.8</v>
@@ -6746,26 +7473,47 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>own: NEPRA KE decision, by fuel from KE's filing; IPP purchases: no figure</t>
+          <t>NEPRA State of Industry Report (KE fuel-wise monthly tables)</t>
         </is>
       </c>
       <c r="AD42" t="b">
         <v>1</v>
       </c>
       <c r="AF42" t="n">
-        <v>912000</v>
+        <v>911660</v>
       </c>
       <c r="AG42" t="n">
-        <v>12591.7</v>
+        <v>12300</v>
       </c>
       <c r="AH42" t="n">
-        <v>24842.7</v>
+        <v>45070</v>
       </c>
       <c r="AI42" t="n">
-        <v>764565.6</v>
+        <v>39500</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>23510</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>791280</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>13880</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>24800</v>
       </c>
       <c r="AO42" t="n">
+        <v>763250</v>
+      </c>
+      <c r="AP42" t="n">
         <v>802000</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>801930</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>120380</v>
       </c>
     </row>
     <row r="43">
@@ -6776,13 +7524,13 @@
         <v>2859994</v>
       </c>
       <c r="C43" t="n">
-        <v>1495649.2</v>
+        <v>1527749.2</v>
       </c>
       <c r="D43" t="n">
-        <v>1764535</v>
+        <v>2185495</v>
       </c>
       <c r="E43" t="n">
-        <v>0.1</v>
+        <v>1770.1</v>
       </c>
       <c r="F43" t="n">
         <v>1655204</v>
@@ -6791,7 +7539,7 @@
         <v>98003.60000000001</v>
       </c>
       <c r="H43" t="n">
-        <v>69084.10000000001</v>
+        <v>88964.10000000001</v>
       </c>
       <c r="I43" t="n">
         <v>52226.4</v>
@@ -6800,7 +7548,7 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>7994696.4</v>
+        <v>8469406.4</v>
       </c>
       <c r="L43" t="n">
         <v>36803.8</v>
@@ -6855,11 +7603,44 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>no KE figure</t>
+          <t>NEPRA State of Industry Report (KE fuel-wise monthly tables)</t>
         </is>
       </c>
       <c r="AD43" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>1072320</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>310</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>52600</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>32100</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>19880</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>967430</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>1460</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>368360</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>369820</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>104890</v>
       </c>
     </row>
     <row r="44">
@@ -6870,10 +7651,10 @@
         <v>1778280.7</v>
       </c>
       <c r="C44" t="n">
-        <v>907915.2</v>
+        <v>911095.2</v>
       </c>
       <c r="D44" t="n">
-        <v>2574494.9</v>
+        <v>2802624.9</v>
       </c>
       <c r="E44" t="n">
         <v>2636.7</v>
@@ -6885,7 +7666,7 @@
         <v>261623.8</v>
       </c>
       <c r="H44" t="n">
-        <v>75816.10000000001</v>
+        <v>102236.1</v>
       </c>
       <c r="I44" t="n">
         <v>101065.6</v>
@@ -6894,7 +7675,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>7766933</v>
+        <v>8024663</v>
       </c>
       <c r="L44" t="n">
         <v>32757.1</v>
@@ -6949,11 +7730,44 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>no KE figure</t>
+          <t>NEPRA State of Industry Report (KE fuel-wise monthly tables)</t>
         </is>
       </c>
       <c r="AD44" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>811080</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>40630</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>3180</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>26420</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>740840</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>187500</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>187500</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>70230</v>
       </c>
     </row>
     <row r="45">
@@ -6967,7 +7781,7 @@
         <v>1964118.6</v>
       </c>
       <c r="D45" t="n">
-        <v>2611337.2</v>
+        <v>2677997.2</v>
       </c>
       <c r="E45" t="n">
         <v>109119</v>
@@ -6979,7 +7793,7 @@
         <v>218039.4</v>
       </c>
       <c r="H45" t="n">
-        <v>86024.60000000001</v>
+        <v>117434.6</v>
       </c>
       <c r="I45" t="n">
         <v>95296</v>
@@ -6988,7 +7802,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>8119693.4</v>
+        <v>8217763.4</v>
       </c>
       <c r="L45" t="n">
         <v>33585.9</v>
@@ -7043,11 +7857,44 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>no KE figure</t>
+          <t>NEPRA State of Industry Report (KE fuel-wise monthly tables)</t>
         </is>
       </c>
       <c r="AD45" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>927420</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>24580</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>31410</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>871440</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>42080</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>42080</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>55990</v>
       </c>
     </row>
     <row r="46">
@@ -7058,13 +7905,13 @@
         <v>1883386.6</v>
       </c>
       <c r="C46" t="n">
-        <v>1151562.2</v>
+        <v>1153062.2</v>
       </c>
       <c r="D46" t="n">
-        <v>1696734.8</v>
+        <v>1845704.8</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F46" t="n">
         <v>1846937</v>
@@ -7073,7 +7920,7 @@
         <v>173537.5</v>
       </c>
       <c r="H46" t="n">
-        <v>84715.39999999999</v>
+        <v>118785.4</v>
       </c>
       <c r="I46" t="n">
         <v>78883.8</v>
@@ -7082,7 +7929,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>6915757.3</v>
+        <v>7100317.3</v>
       </c>
       <c r="L46" t="n">
         <v>29631.8</v>
@@ -7137,11 +7984,44 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>no KE figure</t>
+          <t>NEPRA State of Industry Report (KE fuel-wise monthly tables)</t>
         </is>
       </c>
       <c r="AD46" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>887360</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>29600</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>1500</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>34070</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>822200</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>20</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>119370</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>119390</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>65170</v>
       </c>
     </row>
     <row r="47">
@@ -12316,7 +13196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N29"/>
+  <dimension ref="A1:Y48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12327,67 +13207,122 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>KE_files</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>KE_own_dec_GWh</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>KE_external_dec_GWh</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>KE_soir_IPP_Nuclear_GWh</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>KE_soir_IPP_Coal_GWh</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>KE_soir_IPP_Solar_GWh</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>KE_soir_IPP_Oil_GWh</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>KE_soir_IPP_Gas_GWh</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>KE_soir_CPPA_GWh</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>KE_soir_purch_GWh</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>KE_own_Oil_GWh</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>KE_own_Gas_GWh</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>KE_own_RLNG_GWh</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>KE_own_filed_GWh</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>KE_files</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>KE_own_dec_GWh</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>KE_external_dec_GWh</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>KE_IPP_Oil_GWh</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>KE_IPP_Gas_GWh</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>KE_IPP_Coal_GWh</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>KE_IPP_Solar_GWh</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>KE_from_CPPA_filed_GWh</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>KE_purchases_filed_GWh</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>KE_soir_own_Gas_GWh</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>KE_soir_own_Oil_GWh</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>KE_soir_own_RLNG_GWh</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>KE_soir_own_GWh</t>
         </is>
       </c>
     </row>
@@ -12395,15 +13330,15 @@
       <c r="A2" s="4" t="n">
         <v>44348</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>TRF-362 K-electric FCA Jan-Jun 2021 06-08-2021 33605-09.pdf</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="C2" t="n">
         <v>960</v>
       </c>
-      <c r="H2" t="n">
+      <c r="D2" t="n">
         <v>1131</v>
       </c>
     </row>
@@ -12411,564 +13346,1858 @@
       <c r="A3" s="4" t="n">
         <v>44378</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>TRF-362 KE FCA Jul 2021 25-10-2021 39736-40.PDF</t>
-        </is>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>State of Industry Report 2022</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>854</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1113</v>
+      </c>
+      <c r="E3" t="n">
+        <v>42.578</v>
+      </c>
+      <c r="F3" t="n">
+        <v>39.604</v>
       </c>
       <c r="G3" t="n">
-        <v>854</v>
+        <v>13.06</v>
       </c>
       <c r="H3" t="n">
-        <v>1113</v>
+        <v>112.573</v>
+      </c>
+      <c r="I3" t="n">
+        <v>72.369</v>
+      </c>
+      <c r="J3" t="n">
+        <v>832.677</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1112.86</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>44440</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>TRF-362 FCA Sept-2021 K-Electric 06-12-2021 42395-99.pdf</t>
-        </is>
+        <v>44409</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>State of Industry Report 2022</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>3.143</v>
+      </c>
+      <c r="F4" t="n">
+        <v>40.308</v>
       </c>
       <c r="G4" t="n">
-        <v>903</v>
+        <v>14.157</v>
       </c>
       <c r="H4" t="n">
-        <v>1019</v>
+        <v>81.351</v>
+      </c>
+      <c r="I4" t="n">
+        <v>71.999</v>
+      </c>
+      <c r="J4" t="n">
+        <v>806.4109999999999</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1017.37</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>44470</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>TRF-362 K-electric FCA Oct 2021 04-01-2021 36-40 .PDF</t>
-        </is>
+        <v>44440</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>State of Industry Report 2022</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>903</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1019</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>26.641</v>
       </c>
       <c r="G5" t="n">
-        <v>758</v>
+        <v>14.237</v>
       </c>
       <c r="H5" t="n">
-        <v>1019</v>
+        <v>153.51</v>
+      </c>
+      <c r="I5" t="n">
+        <v>71.617</v>
+      </c>
+      <c r="J5" t="n">
+        <v>752.6039999999999</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1018.61</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>44501</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>TRF-362 KE FCA 19-01-2022 10810.pdf</t>
-        </is>
+        <v>44470</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>State of Industry Report 2022</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>758</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1019</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>37.676</v>
       </c>
       <c r="G6" t="n">
-        <v>463</v>
+        <v>16.195</v>
       </c>
       <c r="H6" t="n">
-        <v>943</v>
+        <v>121.19</v>
+      </c>
+      <c r="I6" t="n">
+        <v>70.60299999999999</v>
+      </c>
+      <c r="J6" t="n">
+        <v>773.176</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1018.84</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>44531</v>
-      </c>
-      <c r="B7" t="n">
-        <v>0</v>
+        <v>44501</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>State of Industry Report 2022</t>
+        </is>
       </c>
       <c r="C7" t="n">
-        <v>130.157</v>
+        <v>463</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>943</v>
       </c>
       <c r="E7" t="n">
-        <v>130.157</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>FCA of KE Dec 2021.pdf | TRF-362 K-Electric FCA Dec 2021 16-02-2022 2357-61.PDF</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>39.045</v>
       </c>
       <c r="G7" t="n">
-        <v>301</v>
+        <v>14.402</v>
       </c>
       <c r="H7" t="n">
-        <v>871</v>
+        <v>92.86</v>
+      </c>
+      <c r="I7" t="n">
+        <v>61.113</v>
+      </c>
+      <c r="J7" t="n">
+        <v>735.165</v>
+      </c>
+      <c r="K7" t="n">
+        <v>942.59</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>44562</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>TRF-362 K-electric FCA Jan 22 30-03-2022 4542-46.PDF</t>
-        </is>
+        <v>44531</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>State of Industry Report 2022</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>301</v>
+      </c>
+      <c r="D8" t="n">
+        <v>871</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>34.168</v>
       </c>
       <c r="G8" t="n">
-        <v>241</v>
+        <v>13.047</v>
       </c>
       <c r="H8" t="n">
-        <v>853</v>
+        <v>57.221</v>
+      </c>
+      <c r="I8" t="n">
+        <v>56.353</v>
+      </c>
+      <c r="J8" t="n">
+        <v>709.747</v>
+      </c>
+      <c r="K8" t="n">
+        <v>870.54</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>130.157</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>130.157</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>44593</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>TRF-362 FCA K-Electric Feb 2022 06-05-2022.PDF</t>
-        </is>
+        <v>44562</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>State of Industry Report 2022</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>241</v>
+      </c>
+      <c r="D9" t="n">
+        <v>853</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3.219</v>
       </c>
       <c r="G9" t="n">
-        <v>251</v>
+        <v>14.22</v>
       </c>
       <c r="H9" t="n">
-        <v>893</v>
+        <v>96.46299999999999</v>
+      </c>
+      <c r="I9" t="n">
+        <v>45.176</v>
+      </c>
+      <c r="J9" t="n">
+        <v>693.899</v>
+      </c>
+      <c r="K9" t="n">
+        <v>852.98</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>44621</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>TRF-362 K-electric FCA Jun 2022 11-08-2022 14947-51.pdf | TRF-362 K-electric FCA Mar 2022 27-05-2022 8192-96.PDF</t>
-        </is>
+        <v>44593</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>State of Industry Report 2022</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>251</v>
+      </c>
+      <c r="D10" t="n">
+        <v>893</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>34.198</v>
       </c>
       <c r="G10" t="n">
-        <v>591</v>
+        <v>15.963</v>
       </c>
       <c r="H10" t="n">
-        <v>1038</v>
+        <v>106.957</v>
+      </c>
+      <c r="I10" t="n">
+        <v>46.155</v>
+      </c>
+      <c r="J10" t="n">
+        <v>689.5650000000001</v>
+      </c>
+      <c r="K10" t="n">
+        <v>892.84</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>44652</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>TRF-362 K-electric FCA Apr 2022 24-06-2022 11099-03.PDF</t>
-        </is>
+        <v>44621</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>State of Industry Report 2022</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>591</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1038</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>33.723</v>
       </c>
       <c r="G11" t="n">
-        <v>891</v>
+        <v>19.564</v>
       </c>
       <c r="H11" t="n">
-        <v>1035</v>
+        <v>137.871</v>
+      </c>
+      <c r="I11" t="n">
+        <v>70.489</v>
+      </c>
+      <c r="J11" t="n">
+        <v>776.5599999999999</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1038.21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>44713</v>
-      </c>
-      <c r="B12" t="n">
-        <v>388.531</v>
+        <v>44652</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>State of Industry Report 2022</t>
+        </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>891</v>
       </c>
       <c r="D12" t="n">
-        <v>532.128</v>
+        <v>1035</v>
       </c>
       <c r="E12" t="n">
-        <v>920.658</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>KE FCA Data for the month of june 2022 MY 2017 - 2023.pdf | TRF-362 K-electric FCA Jun 2022 11-08-2022 14947-51.pdf</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>38.983</v>
       </c>
       <c r="G12" t="n">
-        <v>921</v>
+        <v>15.853</v>
       </c>
       <c r="H12" t="n">
-        <v>1034</v>
+        <v>160.755</v>
+      </c>
+      <c r="I12" t="n">
+        <v>74.16200000000001</v>
+      </c>
+      <c r="J12" t="n">
+        <v>745.668</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1035.42</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>44743</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>TRF-362 K-electric FCA Jul 2022 09-09-2022 17098-02.PDF</t>
-        </is>
+        <v>44682</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>State of Industry Report 2022</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>40.026</v>
       </c>
       <c r="G13" t="n">
-        <v>792</v>
+        <v>13.655</v>
       </c>
       <c r="H13" t="n">
-        <v>1006</v>
+        <v>149.791</v>
+      </c>
+      <c r="I13" t="n">
+        <v>73.50700000000001</v>
+      </c>
+      <c r="J13" t="n">
+        <v>758.153</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1035.13</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>44774</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>TRF-362 K-electric FCA Aug 2022 14-10-2022 19806-10.pdf</t>
-        </is>
+        <v>44713</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>State of Industry Report 2022</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>921</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1034</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>39.099</v>
       </c>
       <c r="G14" t="n">
-        <v>670</v>
+        <v>17.402</v>
       </c>
       <c r="H14" t="n">
-        <v>1044</v>
+        <v>150.742</v>
+      </c>
+      <c r="I14" t="n">
+        <v>63.39</v>
+      </c>
+      <c r="J14" t="n">
+        <v>762.717</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1033.35</v>
+      </c>
+      <c r="L14" t="n">
+        <v>388.531</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>532.128</v>
+      </c>
+      <c r="O14" t="n">
+        <v>920.658</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>44805</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>TRF-362 K-electric FCA Oct 2022 14-12-2022 23528-32.PDF | TRF-362 K-electric FCA Sep 22 11-11-2022 21818-22.pdf</t>
-        </is>
+        <v>44743</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>State of Industry Report 2023</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>792</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1006</v>
+      </c>
+      <c r="F15" t="n">
+        <v>35.27</v>
       </c>
       <c r="G15" t="n">
-        <v>664</v>
+        <v>13.05</v>
       </c>
       <c r="H15" t="n">
-        <v>1010</v>
+        <v>113.45</v>
+      </c>
+      <c r="I15" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>773.25</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1005.52</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>44835</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>TRF-362 K-electric FCA Oct 2022 14-12-2022 23528-32.PDF</t>
-        </is>
+        <v>44774</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>State of Industry Report 2023</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>670</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1044</v>
+      </c>
+      <c r="F16" t="n">
+        <v>40.27</v>
       </c>
       <c r="G16" t="n">
-        <v>663</v>
+        <v>11.76</v>
       </c>
       <c r="H16" t="n">
-        <v>1013</v>
+        <v>134.89</v>
+      </c>
+      <c r="I16" t="n">
+        <v>62.51</v>
+      </c>
+      <c r="J16" t="n">
+        <v>794.9400000000001</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1044.35</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>44896</v>
-      </c>
-      <c r="B17" t="n">
-        <v>1.351</v>
+        <v>44805</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>State of Industry Report 2023</t>
+        </is>
       </c>
       <c r="C17" t="n">
-        <v>0.288</v>
+        <v>664</v>
       </c>
       <c r="D17" t="n">
-        <v>0.978</v>
-      </c>
-      <c r="E17" t="n">
-        <v>2.617</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>KE FCA Data for the month of December 2022.PDF | TRF-362 K-ELECTRIC FCA 09-02-2023 2201-05.PDF</t>
-        </is>
+        <v>1010</v>
+      </c>
+      <c r="F17" t="n">
+        <v>29.59</v>
       </c>
       <c r="G17" t="n">
-        <v>331</v>
+        <v>17.07</v>
       </c>
       <c r="H17" t="n">
-        <v>846</v>
+        <v>120.76</v>
+      </c>
+      <c r="I17" t="n">
+        <v>66.37</v>
+      </c>
+      <c r="J17" t="n">
+        <v>776.6900000000001</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1010.48</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>44958</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>TRF-362 K-ELECTRIC FCA 14-04-2023 9019-23.PDF</t>
-        </is>
+        <v>44835</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>State of Industry Report 2023</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>663</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1013</v>
+      </c>
+      <c r="F18" t="n">
+        <v>38.83</v>
       </c>
       <c r="G18" t="n">
-        <v>295</v>
+        <v>19</v>
       </c>
       <c r="H18" t="n">
-        <v>822</v>
+        <v>119.71</v>
+      </c>
+      <c r="I18" t="n">
+        <v>63.24</v>
+      </c>
+      <c r="J18" t="n">
+        <v>772.46</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1013.24</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>44986</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>TRF-362 KE FCA MAR-2023 11-05-2023 10682-86.PDF</t>
-        </is>
+        <v>44866</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>State of Industry Report 2023</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>38.04</v>
       </c>
       <c r="G19" t="n">
-        <v>520</v>
+        <v>16.47</v>
       </c>
       <c r="H19" t="n">
-        <v>958</v>
+        <v>105.43</v>
+      </c>
+      <c r="I19" t="n">
+        <v>47.67</v>
+      </c>
+      <c r="J19" t="n">
+        <v>738.7</v>
+      </c>
+      <c r="K19" t="n">
+        <v>946.3099999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>45017</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>TRF-362 K-Electric FCA April 2023 16-06-23 14979-83.PDF</t>
-        </is>
+        <v>44896</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>State of Industry Report 2023</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>331</v>
+      </c>
+      <c r="D20" t="n">
+        <v>846</v>
+      </c>
+      <c r="F20" t="n">
+        <v>24.5</v>
       </c>
       <c r="G20" t="n">
-        <v>666</v>
+        <v>16.86</v>
       </c>
       <c r="H20" t="n">
-        <v>862</v>
+        <v>39.34</v>
+      </c>
+      <c r="I20" t="n">
+        <v>42.84</v>
+      </c>
+      <c r="J20" t="n">
+        <v>722.64</v>
+      </c>
+      <c r="K20" t="n">
+        <v>846.1799999999999</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.351</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.978</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.617</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>45047</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>TRF-362 K-ELECTRIC FCA May 2023 14-07-2023 18080-84.PDF</t>
-        </is>
+        <v>44927</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>State of Industry Report 2023</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>14.22</v>
       </c>
       <c r="G21" t="n">
-        <v>883</v>
+        <v>19.16</v>
       </c>
       <c r="H21" t="n">
-        <v>978</v>
+        <v>31.56</v>
+      </c>
+      <c r="I21" t="n">
+        <v>36.13</v>
+      </c>
+      <c r="J21" t="n">
+        <v>673.5599999999999</v>
+      </c>
+      <c r="K21" t="n">
+        <v>774.63</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>45383</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>PROVISIONAL REQUEST FOR MONTHLY FUEL COST VARIATION FOR APRIL 2024 K-ELECTRIC.PD | DECISION OF THE AUTHORITY - FCA April 2024 for K-Electric.PDF</t>
-        </is>
+        <v>44958</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>State of Industry Report 2023</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>295</v>
+      </c>
+      <c r="D22" t="n">
+        <v>822</v>
+      </c>
+      <c r="F22" t="n">
+        <v>19.97</v>
       </c>
       <c r="G22" t="n">
-        <v>581</v>
+        <v>22.15</v>
       </c>
       <c r="H22" t="n">
-        <v>830</v>
+        <v>56.12</v>
       </c>
       <c r="I22" t="n">
-        <v>1.12</v>
+        <v>45.83</v>
       </c>
       <c r="J22" t="n">
-        <v>57.69</v>
+        <v>677.72</v>
       </c>
       <c r="K22" t="n">
-        <v>30.68</v>
-      </c>
-      <c r="L22" t="n">
-        <v>42.26</v>
-      </c>
-      <c r="M22" t="n">
-        <v>710.24</v>
-      </c>
-      <c r="N22" t="n">
-        <v>841.99</v>
+        <v>821.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>45413</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>TRF-362 KE FCA MAY-JUN 2024 21-08-24 13413-17.pdf</t>
-        </is>
+        <v>44986</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>State of Industry Report 2023</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>520</v>
+      </c>
+      <c r="D23" t="n">
+        <v>958</v>
+      </c>
+      <c r="F23" t="n">
+        <v>35.96</v>
       </c>
       <c r="G23" t="n">
-        <v>889</v>
+        <v>24.57</v>
       </c>
       <c r="H23" t="n">
-        <v>951</v>
+        <v>73.69</v>
+      </c>
+      <c r="I23" t="n">
+        <v>56.77</v>
+      </c>
+      <c r="J23" t="n">
+        <v>767.02</v>
+      </c>
+      <c r="K23" t="n">
+        <v>958</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>45444</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>TRF-362 KE FCA MAY-JUN 2024 21-08-24 13413-17.pdf</t>
-        </is>
+        <v>45017</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>State of Industry Report 2023</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>666</v>
+      </c>
+      <c r="D24" t="n">
+        <v>862</v>
+      </c>
+      <c r="F24" t="n">
+        <v>36.75</v>
       </c>
       <c r="G24" t="n">
-        <v>956</v>
+        <v>25.86</v>
       </c>
       <c r="H24" t="n">
-        <v>887</v>
+        <v>26.28</v>
+      </c>
+      <c r="I24" t="n">
+        <v>45.98</v>
+      </c>
+      <c r="J24" t="n">
+        <v>726.99</v>
+      </c>
+      <c r="K24" t="n">
+        <v>861.86</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
-        <v>45474</v>
-      </c>
-      <c r="B25" t="n">
-        <v>147.82</v>
+        <v>45047</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>State of Industry Report 2023</t>
+        </is>
       </c>
       <c r="C25" t="n">
-        <v>41.53</v>
+        <v>883</v>
       </c>
       <c r="D25" t="n">
-        <v>886.47</v>
-      </c>
-      <c r="E25" t="n">
-        <v>1075.83</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>KE PROVISIONAL REQUEST FOR MONTHLY FUEL COST VARIATION FOR JULY 2024.PDF | TRF-362 K-Electric MFPA July-2024 25-10-2024 16199-203.pdf</t>
-        </is>
+        <v>978</v>
+      </c>
+      <c r="F25" t="n">
+        <v>13.67</v>
       </c>
       <c r="G25" t="n">
-        <v>1076</v>
+        <v>25.28</v>
       </c>
       <c r="H25" t="n">
-        <v>935</v>
+        <v>97.37</v>
       </c>
       <c r="I25" t="n">
-        <v>39.2</v>
+        <v>50.66</v>
       </c>
       <c r="J25" t="n">
-        <v>56.61</v>
+        <v>790.54</v>
       </c>
       <c r="K25" t="n">
-        <v>38.57</v>
-      </c>
-      <c r="L25" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="M25" t="n">
-        <v>783.38</v>
-      </c>
-      <c r="N25" t="n">
-        <v>934.96</v>
+        <v>977.52</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
-        <v>45505</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>TRF-362 KE FCA AUG-2024 04-11-2024 16513-17.pdf</t>
-        </is>
+        <v>45078</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>State of Industry Report 2023</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>19.11</v>
       </c>
       <c r="G26" t="n">
-        <v>806</v>
+        <v>18.36</v>
       </c>
       <c r="H26" t="n">
-        <v>874</v>
+        <v>108.54</v>
+      </c>
+      <c r="I26" t="n">
+        <v>42.56</v>
+      </c>
+      <c r="J26" t="n">
+        <v>746.3</v>
+      </c>
+      <c r="K26" t="n">
+        <v>934.87</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
-        <v>45536</v>
-      </c>
-      <c r="B27" t="n">
-        <v>27.59</v>
-      </c>
-      <c r="C27" t="n">
-        <v>27.84</v>
-      </c>
-      <c r="D27" t="n">
-        <v>664.13</v>
-      </c>
-      <c r="E27" t="n">
-        <v>719.5599999999999</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>PROVISIONAL REQUEST OF K-ELECTRIC FOR MONTHLY FUEL COST VARIATION FOR SEPTEMBER | TRF-362 K-Electric FCA Sept-2024 02-12-2024 18550-54.PDF</t>
-        </is>
+        <v>45108</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>State of Industry Report 2024</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>15.17</v>
       </c>
       <c r="G27" t="n">
-        <v>720</v>
+        <v>17.45</v>
       </c>
       <c r="H27" t="n">
-        <v>851</v>
+        <v>89.55</v>
       </c>
       <c r="I27" t="n">
-        <v>10.75</v>
+        <v>44.45</v>
       </c>
       <c r="J27" t="n">
-        <v>50.33</v>
+        <v>772.23</v>
       </c>
       <c r="K27" t="n">
-        <v>35.02</v>
-      </c>
-      <c r="L27" t="n">
-        <v>21.26</v>
-      </c>
-      <c r="M27" t="n">
-        <v>733.65</v>
-      </c>
-      <c r="N27" t="n">
-        <v>851</v>
+        <v>938.84</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>81.08</v>
+      </c>
+      <c r="X27" t="n">
+        <v>876.72</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>957.8099999999999</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
-        <v>45566</v>
-      </c>
-      <c r="B28" t="n">
-        <v>12.57</v>
-      </c>
-      <c r="C28" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="D28" t="n">
-        <v>763.25</v>
-      </c>
-      <c r="E28" t="n">
-        <v>801.9299999999999</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>KE PROVISIONAL REQUEST FOR MONThLY FUEL COST VARIATION FOR OCTOBER 2024.PDF | TRF-362 KE FCA OCT-2024 07-01-2025 176-180.pdf</t>
-        </is>
+        <v>45139</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>State of Industry Report 2024</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>25.23</v>
       </c>
       <c r="G28" t="n">
-        <v>802</v>
+        <v>12.74</v>
       </c>
       <c r="H28" t="n">
-        <v>912</v>
+        <v>49.25</v>
+      </c>
+      <c r="I28" t="n">
+        <v>46.62</v>
+      </c>
+      <c r="J28" t="n">
+        <v>753.46</v>
+      </c>
+      <c r="K28" t="n">
+        <v>887.3</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="X28" t="n">
+        <v>790.1799999999999</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>799.6900000000001</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
+        <v>45170</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>State of Industry Report 2024</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>37.25</v>
+      </c>
+      <c r="G29" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="H29" t="n">
+        <v>96.01000000000001</v>
+      </c>
+      <c r="I29" t="n">
+        <v>42.39</v>
+      </c>
+      <c r="J29" t="n">
+        <v>710.86</v>
+      </c>
+      <c r="K29" t="n">
+        <v>904.8</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>30.75</v>
+      </c>
+      <c r="X29" t="n">
+        <v>731.29</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>762.05</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>45200</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>State of Industry Report 2024</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>40.54</v>
+      </c>
+      <c r="G30" t="n">
+        <v>19.74</v>
+      </c>
+      <c r="H30" t="n">
+        <v>108.37</v>
+      </c>
+      <c r="I30" t="n">
+        <v>61.93</v>
+      </c>
+      <c r="J30" t="n">
+        <v>711.4</v>
+      </c>
+      <c r="K30" t="n">
+        <v>941.97</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>30.38</v>
+      </c>
+      <c r="X30" t="n">
+        <v>713.75</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>744.13</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>45231</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>State of Industry Report 2024</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>36.06</v>
+      </c>
+      <c r="G31" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="H31" t="n">
+        <v>54.23</v>
+      </c>
+      <c r="I31" t="n">
+        <v>46.98</v>
+      </c>
+      <c r="J31" t="n">
+        <v>689.79</v>
+      </c>
+      <c r="K31" t="n">
+        <v>843.5</v>
+      </c>
+      <c r="V31" t="n">
+        <v>43.47</v>
+      </c>
+      <c r="W31" t="n">
+        <v>37.56</v>
+      </c>
+      <c r="X31" t="n">
+        <v>378.44</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>459.46</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>45261</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>State of Industry Report 2024</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>28.78</v>
+      </c>
+      <c r="G32" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="H32" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="I32" t="n">
+        <v>41.99</v>
+      </c>
+      <c r="J32" t="n">
+        <v>709.39</v>
+      </c>
+      <c r="K32" t="n">
+        <v>806.3</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X32" t="n">
+        <v>262.63</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>263.83</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>45292</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>State of Industry Report 2024</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="G33" t="n">
+        <v>21.68</v>
+      </c>
+      <c r="H33" t="n">
+        <v>32.88</v>
+      </c>
+      <c r="I33" t="n">
+        <v>43.23</v>
+      </c>
+      <c r="J33" t="n">
+        <v>683.67</v>
+      </c>
+      <c r="K33" t="n">
+        <v>782.53</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>13.19</v>
+      </c>
+      <c r="X33" t="n">
+        <v>257.42</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>270.61</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>45323</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>State of Industry Report 2024</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="G34" t="n">
+        <v>23.69</v>
+      </c>
+      <c r="H34" t="n">
+        <v>11.19</v>
+      </c>
+      <c r="I34" t="n">
+        <v>46.66</v>
+      </c>
+      <c r="J34" t="n">
+        <v>613.89</v>
+      </c>
+      <c r="K34" t="n">
+        <v>699.6900000000001</v>
+      </c>
+      <c r="V34" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W34" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="X34" t="n">
+        <v>315.01</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>328.75</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>45352</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>State of Industry Report 2024</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>28.53</v>
+      </c>
+      <c r="G35" t="n">
+        <v>31.49</v>
+      </c>
+      <c r="H35" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="I35" t="n">
+        <v>53.48</v>
+      </c>
+      <c r="J35" t="n">
+        <v>702.5</v>
+      </c>
+      <c r="K35" t="n">
+        <v>824.77</v>
+      </c>
+      <c r="V35" t="n">
+        <v>13.41</v>
+      </c>
+      <c r="W35" t="n">
+        <v>13.69</v>
+      </c>
+      <c r="X35" t="n">
+        <v>433.11</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>460.21</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>45383</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>State of Industry Report 2024</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>581</v>
+      </c>
+      <c r="D36" t="n">
+        <v>830</v>
+      </c>
+      <c r="F36" t="n">
+        <v>30.68</v>
+      </c>
+      <c r="G36" t="n">
+        <v>30.07</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="I36" t="n">
+        <v>57.69</v>
+      </c>
+      <c r="J36" t="n">
+        <v>710.24</v>
+      </c>
+      <c r="K36" t="n">
+        <v>829.8</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>57.69</v>
+      </c>
+      <c r="R36" t="n">
+        <v>30.68</v>
+      </c>
+      <c r="S36" t="n">
+        <v>42.26</v>
+      </c>
+      <c r="T36" t="n">
+        <v>710.24</v>
+      </c>
+      <c r="U36" t="n">
+        <v>841.99</v>
+      </c>
+      <c r="V36" t="n">
+        <v>25.96</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>554.74</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>580.7</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n">
+        <v>45413</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>State of Industry Report 2024</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>889</v>
+      </c>
+      <c r="D37" t="n">
+        <v>951</v>
+      </c>
+      <c r="F37" t="n">
+        <v>39.29</v>
+      </c>
+      <c r="G37" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="H37" t="n">
+        <v>58.85</v>
+      </c>
+      <c r="I37" t="n">
+        <v>62.89</v>
+      </c>
+      <c r="J37" t="n">
+        <v>757.88</v>
+      </c>
+      <c r="K37" t="n">
+        <v>951.2</v>
+      </c>
+      <c r="V37" t="n">
+        <v>36.29</v>
+      </c>
+      <c r="W37" t="n">
+        <v>43.99</v>
+      </c>
+      <c r="X37" t="n">
+        <v>808.23</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>888.5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>45444</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>State of Industry Report 2024</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>956</v>
+      </c>
+      <c r="D38" t="n">
+        <v>887</v>
+      </c>
+      <c r="F38" t="n">
+        <v>37.68</v>
+      </c>
+      <c r="G38" t="n">
+        <v>21.95</v>
+      </c>
+      <c r="H38" t="n">
+        <v>40.78</v>
+      </c>
+      <c r="I38" t="n">
+        <v>64.23999999999999</v>
+      </c>
+      <c r="J38" t="n">
+        <v>722.76</v>
+      </c>
+      <c r="K38" t="n">
+        <v>887.41</v>
+      </c>
+      <c r="V38" t="n">
+        <v>40.03</v>
+      </c>
+      <c r="W38" t="n">
+        <v>70.53</v>
+      </c>
+      <c r="X38" t="n">
+        <v>845.02</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>955.59</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>45474</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>State of Industry Report 2025</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1076</v>
+      </c>
+      <c r="D39" t="n">
+        <v>935</v>
+      </c>
+      <c r="F39" t="n">
+        <v>38.57</v>
+      </c>
+      <c r="G39" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="H39" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="I39" t="n">
+        <v>56.61</v>
+      </c>
+      <c r="J39" t="n">
+        <v>783.38</v>
+      </c>
+      <c r="K39" t="n">
+        <v>934.96</v>
+      </c>
+      <c r="L39" t="n">
+        <v>147.82</v>
+      </c>
+      <c r="M39" t="n">
+        <v>41.53</v>
+      </c>
+      <c r="N39" t="n">
+        <v>886.47</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1075.83</v>
+      </c>
+      <c r="P39" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>56.61</v>
+      </c>
+      <c r="R39" t="n">
+        <v>38.57</v>
+      </c>
+      <c r="S39" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="T39" t="n">
+        <v>783.38</v>
+      </c>
+      <c r="U39" t="n">
+        <v>934.96</v>
+      </c>
+      <c r="V39" t="n">
+        <v>41.53</v>
+      </c>
+      <c r="W39" t="n">
+        <v>147.82</v>
+      </c>
+      <c r="X39" t="n">
+        <v>886.47</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1075.83</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n">
+        <v>45505</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>State of Industry Report 2025</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>806</v>
+      </c>
+      <c r="D40" t="n">
+        <v>874</v>
+      </c>
+      <c r="F40" t="n">
+        <v>36.32</v>
+      </c>
+      <c r="G40" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="H40" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="I40" t="n">
+        <v>59.08</v>
+      </c>
+      <c r="J40" t="n">
+        <v>755.49</v>
+      </c>
+      <c r="K40" t="n">
+        <v>873.99</v>
+      </c>
+      <c r="V40" t="n">
+        <v>39.83</v>
+      </c>
+      <c r="W40" t="n">
+        <v>13.42</v>
+      </c>
+      <c r="X40" t="n">
+        <v>752.73</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>805.98</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n">
+        <v>45536</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>State of Industry Report 2025</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>720</v>
+      </c>
+      <c r="D41" t="n">
+        <v>851</v>
+      </c>
+      <c r="F41" t="n">
+        <v>35.02</v>
+      </c>
+      <c r="G41" t="n">
+        <v>21.26</v>
+      </c>
+      <c r="H41" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="I41" t="n">
+        <v>50.33</v>
+      </c>
+      <c r="J41" t="n">
+        <v>733.65</v>
+      </c>
+      <c r="K41" t="n">
+        <v>851</v>
+      </c>
+      <c r="L41" t="n">
+        <v>27.59</v>
+      </c>
+      <c r="M41" t="n">
+        <v>27.84</v>
+      </c>
+      <c r="N41" t="n">
+        <v>664.13</v>
+      </c>
+      <c r="O41" t="n">
+        <v>719.5599999999999</v>
+      </c>
+      <c r="P41" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>50.33</v>
+      </c>
+      <c r="R41" t="n">
+        <v>35.02</v>
+      </c>
+      <c r="S41" t="n">
+        <v>21.26</v>
+      </c>
+      <c r="T41" t="n">
+        <v>733.65</v>
+      </c>
+      <c r="U41" t="n">
+        <v>851</v>
+      </c>
+      <c r="V41" t="n">
+        <v>27.84</v>
+      </c>
+      <c r="W41" t="n">
+        <v>27.59</v>
+      </c>
+      <c r="X41" t="n">
+        <v>664.13</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>719.5599999999999</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n">
+        <v>45566</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>State of Industry Report 2025</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>802</v>
+      </c>
+      <c r="D42" t="n">
+        <v>912</v>
+      </c>
+      <c r="F42" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="G42" t="n">
+        <v>23.51</v>
+      </c>
+      <c r="H42" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="I42" t="n">
+        <v>45.07</v>
+      </c>
+      <c r="J42" t="n">
+        <v>791.28</v>
+      </c>
+      <c r="K42" t="n">
+        <v>911.66</v>
+      </c>
+      <c r="L42" t="n">
+        <v>12.57</v>
+      </c>
+      <c r="M42" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="N42" t="n">
+        <v>763.25</v>
+      </c>
+      <c r="O42" t="n">
+        <v>801.9299999999999</v>
+      </c>
+      <c r="V42" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="W42" t="n">
+        <v>13.88</v>
+      </c>
+      <c r="X42" t="n">
+        <v>763.25</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>801.9299999999999</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n">
+        <v>45597</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>State of Industry Report 2025</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="G43" t="n">
+        <v>19.88</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="I43" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="J43" t="n">
+        <v>967.4299999999999</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1072.32</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X43" t="n">
+        <v>368.36</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>369.82</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n">
+        <v>45627</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>State of Industry Report 2025</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="G44" t="n">
+        <v>26.42</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>40.63</v>
+      </c>
+      <c r="J44" t="n">
+        <v>740.84</v>
+      </c>
+      <c r="K44" t="n">
+        <v>811.08</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" t="n">
+        <v>187.5</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>187.5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="n">
+        <v>45658</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>State of Industry Report 2025</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>31.41</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>24.58</v>
+      </c>
+      <c r="J45" t="n">
+        <v>871.4400000000001</v>
+      </c>
+      <c r="K45" t="n">
+        <v>927.42</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" t="n">
+        <v>42.08</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>42.08</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="n">
         <v>45689</v>
       </c>
-      <c r="B29" t="n">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>State of Industry Report 2025</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G46" t="n">
+        <v>34.07</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="J46" t="n">
+        <v>822.2</v>
+      </c>
+      <c r="K46" t="n">
+        <v>887.36</v>
+      </c>
+      <c r="L46" t="n">
         <v>0.02</v>
       </c>
-      <c r="C29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" t="n">
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
         <v>119.37</v>
       </c>
-      <c r="E29" t="n">
+      <c r="O46" t="n">
         <v>119.39</v>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>KE PROVISIONAL REQUEST FOR MONTHLY FUEL COST VARIATiON FOR FEBRUARY 2025.PDF</t>
-        </is>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="X46" t="n">
+        <v>119.37</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>119.39</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>State of Industry Report 2025</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>20.31</v>
+      </c>
+      <c r="G47" t="n">
+        <v>36.92</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="J47" t="n">
+        <v>981.96</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1086.99</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="n">
+        <v>45748</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>State of Industry Report 2025</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>27.09</v>
+      </c>
+      <c r="G48" t="n">
+        <v>45.55</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>43</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1017.81</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1133.85</v>
       </c>
     </row>
   </sheetData>
@@ -14666,7 +16895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F97"/>
+  <dimension ref="A1:F101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17491,6 +19720,126 @@
         </is>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>https://nepra.org.pk/publications/State%20of%20Industry%20Reports/State%20of%20Industry%20Report%202022.pdf</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>NEPRA SOIR</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>State of Industry Report 2022</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>2021-07 2021-08 2021-09 2021-10 2021-11 2021-12 2022-01 2022-02 2022-03 2022-04 2022-05 2022-06</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>https://nepra.org.pk/publications/State%20of%20Industry%20Reports/State%20of%20Industry%20Report%202023.pdf</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>NEPRA SOIR</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>State of Industry Report 2023</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>2022-07 2022-08 2022-09 2022-10 2022-11 2022-12 2023-01 2023-02 2023-03 2023-04 2023-05 2023-06</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>https://nepra.org.pk/publications/State%20of%20Industry%20Reports/State%20of%20Industry%20Report%202024.pdf</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>NEPRA SOIR</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>State of Industry Report 2024</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>2023-07 2023-08 2023-09 2023-10 2023-11 2023-12 2024-01 2024-02 2024-03 2024-04 2024-05 2024-06</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>https://nepra.org.pk/publications/State%20of%20Industry%20Reports/State%20of%20Industry%20Report%202025.pdf</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>NEPRA SOIR</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>State of Industry Report 2025</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>2024-07 2024-08 2024-09 2024-10 2024-11 2024-12 2025-01 2025-02 2025-03 2025-04</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/pakistan_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/pakistan_power_generation_daily.xlsx
@@ -24,8 +24,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="mmm/yy"/>
+    <numFmt numFmtId="165" formatCode="mmm/yy"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -65,12 +65,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -159,6 +160,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Pakistan power generation by fuel, national grid + K-Electric where filed (CPPA-G / NEPRA FCA filings; KE from NEPRA KE decisions) (to Aug/26)</a:t>
             </a:r>
           </a:p>
@@ -821,7 +823,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
@@ -843,7 +844,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>44228</v>
       </c>
       <c r="B2" t="n">
@@ -965,7 +965,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>44256</v>
       </c>
       <c r="B3" t="n">
@@ -991,7 +991,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>44287</v>
       </c>
       <c r="B4" t="n">
@@ -1017,7 +1017,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>44317</v>
       </c>
       <c r="B5" t="n">
@@ -1043,7 +1043,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>44348</v>
       </c>
       <c r="B6" t="n">
@@ -1069,7 +1069,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>44378</v>
       </c>
       <c r="B7" t="n">
@@ -1095,7 +1095,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>44409</v>
       </c>
       <c r="B8" t="n">
@@ -1121,7 +1121,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>44440</v>
       </c>
       <c r="B9" t="n">
@@ -1147,7 +1147,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>44470</v>
       </c>
       <c r="B10" t="n">
@@ -1173,7 +1173,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>44501</v>
       </c>
       <c r="B11" t="n">
@@ -1199,7 +1199,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>44531</v>
       </c>
       <c r="B12" t="n">
@@ -1225,7 +1225,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B13" t="n">
@@ -1251,7 +1251,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>44621</v>
       </c>
       <c r="B14" t="n">
@@ -1277,7 +1277,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>44652</v>
       </c>
       <c r="B15" t="n">
@@ -1303,7 +1303,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>44682</v>
       </c>
       <c r="B16" t="n">
@@ -1329,7 +1329,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>44713</v>
       </c>
       <c r="B17" t="n">
@@ -1355,7 +1355,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>44743</v>
       </c>
       <c r="B18" t="n">
@@ -1381,7 +1381,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>44774</v>
       </c>
       <c r="B19" t="n">
@@ -1407,7 +1407,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>44835</v>
       </c>
       <c r="B20" t="n">
@@ -1433,7 +1433,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>44896</v>
       </c>
       <c r="B21" t="n">
@@ -1459,7 +1459,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B22" t="n">
@@ -1485,7 +1485,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>44958</v>
       </c>
       <c r="B23" t="n">
@@ -1511,7 +1511,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>44986</v>
       </c>
       <c r="B24" t="n">
@@ -1537,7 +1537,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>45017</v>
       </c>
       <c r="B25" t="n">
@@ -1563,7 +1563,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>45047</v>
       </c>
       <c r="B26" t="n">
@@ -1589,7 +1589,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>45078</v>
       </c>
       <c r="B27" t="n">
@@ -1615,7 +1615,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>45108</v>
       </c>
       <c r="B28" t="n">
@@ -1641,7 +1641,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>45139</v>
       </c>
       <c r="B29" t="n">
@@ -1667,7 +1667,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>45170</v>
       </c>
       <c r="B30" t="n">
@@ -1693,7 +1693,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>45200</v>
       </c>
       <c r="B31" t="n">
@@ -1719,7 +1719,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="5" t="n">
         <v>45231</v>
       </c>
       <c r="B32" t="n">
@@ -1745,7 +1745,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="5" t="n">
         <v>45261</v>
       </c>
       <c r="B33" t="n">
@@ -1771,7 +1771,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B34" t="n">
@@ -1797,7 +1797,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="5" t="n">
         <v>45323</v>
       </c>
       <c r="B35" t="n">
@@ -1823,7 +1823,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="5" t="n">
         <v>45352</v>
       </c>
       <c r="B36" t="n">
@@ -1849,7 +1849,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B37" t="n">
@@ -1875,7 +1875,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B38" t="n">
@@ -1901,7 +1901,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B39" t="n">
@@ -1927,7 +1927,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B40" t="n">
@@ -1953,7 +1953,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B41" t="n">
@@ -1979,7 +1979,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B42" t="n">
@@ -2005,7 +2005,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B43" t="n">
@@ -2031,7 +2031,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="5" t="n">
         <v>45627</v>
       </c>
       <c r="B44" t="n">
@@ -2057,7 +2057,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B45" t="n">
@@ -2083,7 +2083,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="5" t="n">
         <v>45689</v>
       </c>
       <c r="B46" t="n">
@@ -2109,7 +2109,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="5" t="n">
         <v>45717</v>
       </c>
       <c r="B47" t="n">
@@ -2135,7 +2135,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="5" t="n">
         <v>45748</v>
       </c>
       <c r="B48" t="n">
@@ -2161,7 +2161,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="5" t="n">
         <v>45778</v>
       </c>
       <c r="B49" t="n">
@@ -2187,7 +2187,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="5" t="n">
         <v>45809</v>
       </c>
       <c r="B50" t="n">
@@ -2213,7 +2213,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="5" t="n">
         <v>45839</v>
       </c>
       <c r="B51" t="n">
@@ -2239,7 +2239,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="5" t="n">
         <v>45870</v>
       </c>
       <c r="B52" t="n">
@@ -2265,7 +2265,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="5" t="n">
         <v>45901</v>
       </c>
       <c r="B53" t="n">
@@ -2291,7 +2291,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="5" t="n">
         <v>45931</v>
       </c>
       <c r="B54" t="n">
@@ -2317,7 +2317,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="5" t="n">
         <v>45962</v>
       </c>
       <c r="B55" t="n">
@@ -2343,7 +2343,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="B56" t="n">
@@ -2369,7 +2369,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="B57" t="n">
@@ -2395,7 +2395,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="5" t="n">
         <v>46054</v>
       </c>
       <c r="B58" t="n">
@@ -2421,7 +2421,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="5" t="n">
         <v>46082</v>
       </c>
       <c r="B59" t="n">
@@ -2447,7 +2447,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="5" t="n">
         <v>46113</v>
       </c>
       <c r="B60" t="n">
@@ -2473,7 +2473,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="5" t="n">
         <v>46143</v>
       </c>
       <c r="B61" t="n">
@@ -2499,7 +2499,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="5" t="n">
         <v>46174</v>
       </c>
       <c r="B62" t="n">
@@ -2525,7 +2525,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="5" t="n">
         <v>46204</v>
       </c>
       <c r="B63" t="n">
@@ -2551,7 +2551,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="5" t="n">
         <v>46235</v>
       </c>
       <c r="B64" t="n">

--- a/output/Data and Chart Outputs/pakistan_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/pakistan_power_generation_daily.xlsx
@@ -24,8 +24,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="mmm/yy"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="mmm/yy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -65,13 +65,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -823,6 +822,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
@@ -844,6 +844,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
@@ -939,7 +940,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44228</v>
       </c>
       <c r="B2" t="n">
@@ -965,7 +966,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B3" t="n">
@@ -991,7 +992,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B4" t="n">
@@ -1017,7 +1018,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="B5" t="n">
@@ -1043,7 +1044,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="B6" t="n">
@@ -1069,7 +1070,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B7" t="n">
@@ -1095,7 +1096,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="B8" t="n">
@@ -1121,7 +1122,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="B9" t="n">
@@ -1147,7 +1148,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B10" t="n">
@@ -1173,7 +1174,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B11" t="n">
@@ -1199,7 +1200,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B12" t="n">
@@ -1225,7 +1226,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B13" t="n">
@@ -1251,7 +1252,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="B14" t="n">
@@ -1277,7 +1278,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B15" t="n">
@@ -1303,7 +1304,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="B16" t="n">
@@ -1329,7 +1330,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="B17" t="n">
@@ -1355,7 +1356,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B18" t="n">
@@ -1381,7 +1382,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B19" t="n">
@@ -1407,7 +1408,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B20" t="n">
@@ -1433,7 +1434,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B21" t="n">
@@ -1459,7 +1460,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B22" t="n">
@@ -1485,7 +1486,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>44958</v>
       </c>
       <c r="B23" t="n">
@@ -1511,7 +1512,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B24" t="n">
@@ -1537,7 +1538,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B25" t="n">
@@ -1563,7 +1564,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B26" t="n">
@@ -1589,7 +1590,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B27" t="n">
@@ -1615,7 +1616,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B28" t="n">
@@ -1641,7 +1642,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B29" t="n">
@@ -1667,7 +1668,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B30" t="n">
@@ -1693,7 +1694,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B31" t="n">
@@ -1719,7 +1720,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B32" t="n">
@@ -1745,7 +1746,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B33" t="n">
@@ -1771,7 +1772,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B34" t="n">
@@ -1797,7 +1798,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="3" t="n">
         <v>45323</v>
       </c>
       <c r="B35" t="n">
@@ -1823,7 +1824,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B36" t="n">
@@ -1849,7 +1850,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B37" t="n">
@@ -1875,7 +1876,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B38" t="n">
@@ -1901,7 +1902,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B39" t="n">
@@ -1927,7 +1928,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B40" t="n">
@@ -1953,7 +1954,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B41" t="n">
@@ -1979,7 +1980,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B42" t="n">
@@ -2005,7 +2006,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B43" t="n">
@@ -2031,7 +2032,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="n">
+      <c r="A44" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B44" t="n">
@@ -2057,7 +2058,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B45" t="n">
@@ -2083,7 +2084,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="3" t="n">
         <v>45689</v>
       </c>
       <c r="B46" t="n">
@@ -2109,7 +2110,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B47" t="n">
@@ -2135,7 +2136,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B48" t="n">
@@ -2161,7 +2162,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B49" t="n">
@@ -2187,7 +2188,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="n">
+      <c r="A50" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B50" t="n">
@@ -2213,7 +2214,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n">
+      <c r="A51" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B51" t="n">
@@ -2239,7 +2240,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="n">
+      <c r="A52" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B52" t="n">
@@ -2265,7 +2266,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B53" t="n">
@@ -2291,7 +2292,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="n">
+      <c r="A54" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B54" t="n">
@@ -2317,7 +2318,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n">
+      <c r="A55" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B55" t="n">
@@ -2343,7 +2344,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="n">
+      <c r="A56" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B56" t="n">
@@ -2369,7 +2370,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n">
+      <c r="A57" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B57" t="n">
@@ -2395,7 +2396,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="n">
+      <c r="A58" s="3" t="n">
         <v>46054</v>
       </c>
       <c r="B58" t="n">
@@ -2421,7 +2422,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="n">
+      <c r="A59" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B59" t="n">
@@ -2447,7 +2448,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="n">
+      <c r="A60" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B60" t="n">
@@ -2473,7 +2474,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="n">
+      <c r="A61" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B61" t="n">
@@ -2499,7 +2500,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="n">
+      <c r="A62" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B62" t="n">
@@ -2525,7 +2526,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="n">
+      <c r="A63" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B63" t="n">
@@ -2551,7 +2552,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="n">
+      <c r="A64" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="B64" t="n">
